--- a/Ejemplo - proyeccion por flujo de caja.xlsx
+++ b/Ejemplo - proyeccion por flujo de caja.xlsx
@@ -3334,6 +3334,14 @@
       </c>
     </row>
     <row r="8">
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t>Años con ingreso total</t>
+        </is>
+      </c>
+      <c r="G8" s="9">
+        <v>15</v>
+      </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
           <t>Alquiler mensual del inmueble</t>
@@ -3600,7 +3608,7 @@
         <v>Acumulación</v>
       </c>
       <c r="F16" s="10">
-        <f>IF(D16&lt;=$G$7,$G$1*12*(1+$D$3)^(D16-1),0)</f>
+        <f>IF(D16&lt;=$G$8,$G$1*12*(1+$D$3)^(D16-1),0)</f>
         <v>112000</v>
       </c>
       <c r="G16" s="10">
@@ -3725,7 +3733,7 @@
         <v>Acumulación</v>
       </c>
       <c r="F17" s="10">
-        <f>IF(D17&lt;=$G$7,$G$1*12*(1+$D$3)^(D17-1),0)</f>
+        <f>IF(D17&lt;=$G$8,$G$1*12*(1+$D$3)^(D17-1),0)</f>
         <v>116368</v>
       </c>
       <c r="G17" s="10">
@@ -3851,7 +3859,7 @@
         <v>Acumulación</v>
       </c>
       <c r="F18" s="10">
-        <f>IF(D18&lt;=$G$7,$G$1*12*(1+$D$3)^(D18-1),0)</f>
+        <f>IF(D18&lt;=$G$8,$G$1*12*(1+$D$3)^(D18-1),0)</f>
         <v>120906</v>
       </c>
       <c r="G18" s="10">
@@ -3977,7 +3985,7 @@
         <v>Acumulación</v>
       </c>
       <c r="F19" s="10">
-        <f>IF(D19&lt;=$G$7,$G$1*12*(1+$D$3)^(D19-1),0)</f>
+        <f>IF(D19&lt;=$G$8,$G$1*12*(1+$D$3)^(D19-1),0)</f>
         <v>125622</v>
       </c>
       <c r="G19" s="10">
@@ -4103,7 +4111,7 @@
         <v>Acumulación</v>
       </c>
       <c r="F20" s="10">
-        <f>IF(D20&lt;=$G$7,$G$1*12*(1+$D$3)^(D20-1),0)</f>
+        <f>IF(D20&lt;=$G$8,$G$1*12*(1+$D$3)^(D20-1),0)</f>
         <v>130521</v>
       </c>
       <c r="G20" s="10">
@@ -4229,7 +4237,7 @@
         <v>Acumulación</v>
       </c>
       <c r="F21" s="10">
-        <f>IF(D21&lt;=$G$7,$G$1*12*(1+$D$3)^(D21-1),0)</f>
+        <f>IF(D21&lt;=$G$8,$G$1*12*(1+$D$3)^(D21-1),0)</f>
         <v>135611</v>
       </c>
       <c r="G21" s="10">
@@ -4355,7 +4363,7 @@
         <v>Acumulación</v>
       </c>
       <c r="F22" s="10">
-        <f>IF(D22&lt;=$G$7,$G$1*12*(1+$D$3)^(D22-1),0)</f>
+        <f>IF(D22&lt;=$G$8,$G$1*12*(1+$D$3)^(D22-1),0)</f>
         <v>140900</v>
       </c>
       <c r="G22" s="10">
@@ -4481,7 +4489,7 @@
         <v>Acumulación</v>
       </c>
       <c r="F23" s="10">
-        <f>IF(D23&lt;=$G$7,$G$1*12*(1+$D$3)^(D23-1),0)</f>
+        <f>IF(D23&lt;=$G$8,$G$1*12*(1+$D$3)^(D23-1),0)</f>
         <v>146395</v>
       </c>
       <c r="G23" s="10">
@@ -4607,7 +4615,7 @@
         <v>Acumulación</v>
       </c>
       <c r="F24" s="10">
-        <f>IF(D24&lt;=$G$7,$G$1*12*(1+$D$3)^(D24-1),0)</f>
+        <f>IF(D24&lt;=$G$8,$G$1*12*(1+$D$3)^(D24-1),0)</f>
         <v>152105</v>
       </c>
       <c r="G24" s="10">
@@ -4733,7 +4741,7 @@
         <v>Acumulación</v>
       </c>
       <c r="F25" s="10">
-        <f>IF(D25&lt;=$G$7,$G$1*12*(1+$D$3)^(D25-1),0)</f>
+        <f>IF(D25&lt;=$G$8,$G$1*12*(1+$D$3)^(D25-1),0)</f>
         <v>158037</v>
       </c>
       <c r="G25" s="10">
@@ -4859,7 +4867,7 @@
         <v>Acumulación</v>
       </c>
       <c r="F26" s="10">
-        <f>IF(D26&lt;=$G$7,$G$1*12*(1+$D$3)^(D26-1),0)</f>
+        <f>IF(D26&lt;=$G$8,$G$1*12*(1+$D$3)^(D26-1),0)</f>
         <v>164200</v>
       </c>
       <c r="G26" s="10">
@@ -4985,7 +4993,7 @@
         <v>Acumulación</v>
       </c>
       <c r="F27" s="10">
-        <f>IF(D27&lt;=$G$7,$G$1*12*(1+$D$3)^(D27-1),0)</f>
+        <f>IF(D27&lt;=$G$8,$G$1*12*(1+$D$3)^(D27-1),0)</f>
         <v>170604</v>
       </c>
       <c r="G27" s="10">
@@ -5111,7 +5119,7 @@
         <v>Acumulación</v>
       </c>
       <c r="F28" s="10">
-        <f>IF(D28&lt;=$G$7,$G$1*12*(1+$D$3)^(D28-1),0)</f>
+        <f>IF(D28&lt;=$G$8,$G$1*12*(1+$D$3)^(D28-1),0)</f>
         <v>177257</v>
       </c>
       <c r="G28" s="10">
@@ -5237,7 +5245,7 @@
         <v>Acumulación</v>
       </c>
       <c r="F29" s="10">
-        <f>IF(D29&lt;=$G$7,$G$1*12*(1+$D$3)^(D29-1),0)</f>
+        <f>IF(D29&lt;=$G$8,$G$1*12*(1+$D$3)^(D29-1),0)</f>
         <v>184171</v>
       </c>
       <c r="G29" s="10">
@@ -5363,7 +5371,7 @@
         <v>Acumulación</v>
       </c>
       <c r="F30" s="10">
-        <f>IF(D30&lt;=$G$7,$G$1*12*(1+$D$3)^(D30-1),0)</f>
+        <f>IF(D30&lt;=$G$8,$G$1*12*(1+$D$3)^(D30-1),0)</f>
         <v>191353</v>
       </c>
       <c r="G30" s="10">
@@ -5489,7 +5497,7 @@
         <v>Retiro</v>
       </c>
       <c r="F31" s="10">
-        <f>IF(D31&lt;=$G$7,$G$1*12*(1+$D$3)^(D31-1),0)</f>
+        <f>IF(D31&lt;=$G$8,$G$1*12*(1+$D$3)^(D31-1),0)</f>
         <v>0</v>
       </c>
       <c r="G31" s="10">
@@ -5615,7 +5623,7 @@
         <v>Retiro</v>
       </c>
       <c r="F32" s="10">
-        <f>IF(D32&lt;=$G$7,$G$1*12*(1+$D$3)^(D32-1),0)</f>
+        <f>IF(D32&lt;=$G$8,$G$1*12*(1+$D$3)^(D32-1),0)</f>
         <v>0</v>
       </c>
       <c r="G32" s="10">
@@ -5741,7 +5749,7 @@
         <v>Retiro</v>
       </c>
       <c r="F33" s="10">
-        <f>IF(D33&lt;=$G$7,$G$1*12*(1+$D$3)^(D33-1),0)</f>
+        <f>IF(D33&lt;=$G$8,$G$1*12*(1+$D$3)^(D33-1),0)</f>
         <v>0</v>
       </c>
       <c r="G33" s="10">
@@ -5867,7 +5875,7 @@
         <v>Retiro</v>
       </c>
       <c r="F34" s="10">
-        <f>IF(D34&lt;=$G$7,$G$1*12*(1+$D$3)^(D34-1),0)</f>
+        <f>IF(D34&lt;=$G$8,$G$1*12*(1+$D$3)^(D34-1),0)</f>
         <v>0</v>
       </c>
       <c r="G34" s="10">
@@ -5993,7 +6001,7 @@
         <v>Retiro</v>
       </c>
       <c r="F35" s="10">
-        <f>IF(D35&lt;=$G$7,$G$1*12*(1+$D$3)^(D35-1),0)</f>
+        <f>IF(D35&lt;=$G$8,$G$1*12*(1+$D$3)^(D35-1),0)</f>
         <v>0</v>
       </c>
       <c r="G35" s="10">
@@ -6119,7 +6127,7 @@
         <v>Retiro</v>
       </c>
       <c r="F36" s="10">
-        <f>IF(D36&lt;=$G$7,$G$1*12*(1+$D$3)^(D36-1),0)</f>
+        <f>IF(D36&lt;=$G$8,$G$1*12*(1+$D$3)^(D36-1),0)</f>
         <v>0</v>
       </c>
       <c r="G36" s="10">
@@ -6245,7 +6253,7 @@
         <v>Retiro</v>
       </c>
       <c r="F37" s="10">
-        <f>IF(D37&lt;=$G$7,$G$1*12*(1+$D$3)^(D37-1),0)</f>
+        <f>IF(D37&lt;=$G$8,$G$1*12*(1+$D$3)^(D37-1),0)</f>
         <v>0</v>
       </c>
       <c r="G37" s="10">
@@ -6371,7 +6379,7 @@
         <v>Retiro</v>
       </c>
       <c r="F38" s="10">
-        <f>IF(D38&lt;=$G$7,$G$1*12*(1+$D$3)^(D38-1),0)</f>
+        <f>IF(D38&lt;=$G$8,$G$1*12*(1+$D$3)^(D38-1),0)</f>
         <v>0</v>
       </c>
       <c r="G38" s="10">
@@ -6497,7 +6505,7 @@
         <v>Retiro</v>
       </c>
       <c r="F39" s="10">
-        <f>IF(D39&lt;=$G$7,$G$1*12*(1+$D$3)^(D39-1),0)</f>
+        <f>IF(D39&lt;=$G$8,$G$1*12*(1+$D$3)^(D39-1),0)</f>
         <v>0</v>
       </c>
       <c r="G39" s="10">
@@ -6623,7 +6631,7 @@
         <v>Retiro</v>
       </c>
       <c r="F40" s="10">
-        <f>IF(D40&lt;=$G$7,$G$1*12*(1+$D$3)^(D40-1),0)</f>
+        <f>IF(D40&lt;=$G$8,$G$1*12*(1+$D$3)^(D40-1),0)</f>
         <v>0</v>
       </c>
       <c r="G40" s="10">
@@ -6749,7 +6757,7 @@
         <v>Retiro</v>
       </c>
       <c r="F41" s="10">
-        <f>IF(D41&lt;=$G$7,$G$1*12*(1+$D$3)^(D41-1),0)</f>
+        <f>IF(D41&lt;=$G$8,$G$1*12*(1+$D$3)^(D41-1),0)</f>
         <v>0</v>
       </c>
       <c r="G41" s="10">
@@ -6875,7 +6883,7 @@
         <v>Retiro</v>
       </c>
       <c r="F42" s="10">
-        <f>IF(D42&lt;=$G$7,$G$1*12*(1+$D$3)^(D42-1),0)</f>
+        <f>IF(D42&lt;=$G$8,$G$1*12*(1+$D$3)^(D42-1),0)</f>
         <v>0</v>
       </c>
       <c r="G42" s="10">
@@ -7001,7 +7009,7 @@
         <v>Retiro</v>
       </c>
       <c r="F43" s="10">
-        <f>IF(D43&lt;=$G$7,$G$1*12*(1+$D$3)^(D43-1),0)</f>
+        <f>IF(D43&lt;=$G$8,$G$1*12*(1+$D$3)^(D43-1),0)</f>
         <v>0</v>
       </c>
       <c r="G43" s="10">
@@ -7127,7 +7135,7 @@
         <v>Retiro</v>
       </c>
       <c r="F44" s="10">
-        <f>IF(D44&lt;=$G$7,$G$1*12*(1+$D$3)^(D44-1),0)</f>
+        <f>IF(D44&lt;=$G$8,$G$1*12*(1+$D$3)^(D44-1),0)</f>
         <v>0</v>
       </c>
       <c r="G44" s="10">
@@ -7253,7 +7261,7 @@
         <v>Retiro</v>
       </c>
       <c r="F45" s="10">
-        <f>IF(D45&lt;=$G$7,$G$1*12*(1+$D$3)^(D45-1),0)</f>
+        <f>IF(D45&lt;=$G$8,$G$1*12*(1+$D$3)^(D45-1),0)</f>
         <v>0</v>
       </c>
       <c r="G45" s="10">
@@ -7379,7 +7387,7 @@
         <v>Retiro</v>
       </c>
       <c r="F46" s="10">
-        <f>IF(D46&lt;=$G$7,$G$1*12*(1+$D$3)^(D46-1),0)</f>
+        <f>IF(D46&lt;=$G$8,$G$1*12*(1+$D$3)^(D46-1),0)</f>
         <v>0</v>
       </c>
       <c r="G46" s="10">
@@ -7505,7 +7513,7 @@
         <v>Retiro</v>
       </c>
       <c r="F47" s="10">
-        <f>IF(D47&lt;=$G$7,$G$1*12*(1+$D$3)^(D47-1),0)</f>
+        <f>IF(D47&lt;=$G$8,$G$1*12*(1+$D$3)^(D47-1),0)</f>
         <v>0</v>
       </c>
       <c r="G47" s="10">
@@ -7631,7 +7639,7 @@
         <v>Retiro</v>
       </c>
       <c r="F48" s="10">
-        <f>IF(D48&lt;=$G$7,$G$1*12*(1+$D$3)^(D48-1),0)</f>
+        <f>IF(D48&lt;=$G$8,$G$1*12*(1+$D$3)^(D48-1),0)</f>
         <v>0</v>
       </c>
       <c r="G48" s="10">
@@ -7757,7 +7765,7 @@
         <v>Retiro</v>
       </c>
       <c r="F49" s="10">
-        <f>IF(D49&lt;=$G$7,$G$1*12*(1+$D$3)^(D49-1),0)</f>
+        <f>IF(D49&lt;=$G$8,$G$1*12*(1+$D$3)^(D49-1),0)</f>
         <v>0</v>
       </c>
       <c r="G49" s="10">
@@ -7883,7 +7891,7 @@
         <v>Retiro</v>
       </c>
       <c r="F50" s="10">
-        <f>IF(D50&lt;=$G$7,$G$1*12*(1+$D$3)^(D50-1),0)</f>
+        <f>IF(D50&lt;=$G$8,$G$1*12*(1+$D$3)^(D50-1),0)</f>
         <v>0</v>
       </c>
       <c r="G50" s="10">
@@ -8009,7 +8017,7 @@
         <v>Retiro</v>
       </c>
       <c r="F51" s="10">
-        <f>IF(D51&lt;=$G$7,$G$1*12*(1+$D$3)^(D51-1),0)</f>
+        <f>IF(D51&lt;=$G$8,$G$1*12*(1+$D$3)^(D51-1),0)</f>
         <v>0</v>
       </c>
       <c r="G51" s="10">
@@ -8135,7 +8143,7 @@
         <v>Retiro</v>
       </c>
       <c r="F52" s="10">
-        <f>IF(D52&lt;=$G$7,$G$1*12*(1+$D$3)^(D52-1),0)</f>
+        <f>IF(D52&lt;=$G$8,$G$1*12*(1+$D$3)^(D52-1),0)</f>
         <v>0</v>
       </c>
       <c r="G52" s="10">
@@ -8261,7 +8269,7 @@
         <v>Retiro</v>
       </c>
       <c r="F53" s="10">
-        <f>IF(D53&lt;=$G$7,$G$1*12*(1+$D$3)^(D53-1),0)</f>
+        <f>IF(D53&lt;=$G$8,$G$1*12*(1+$D$3)^(D53-1),0)</f>
         <v>0</v>
       </c>
       <c r="G53" s="10">
@@ -8387,7 +8395,7 @@
         <v>Retiro</v>
       </c>
       <c r="F54" s="10">
-        <f>IF(D54&lt;=$G$7,$G$1*12*(1+$D$3)^(D54-1),0)</f>
+        <f>IF(D54&lt;=$G$8,$G$1*12*(1+$D$3)^(D54-1),0)</f>
         <v>0</v>
       </c>
       <c r="G54" s="10">
@@ -8513,7 +8521,7 @@
         <v>Retiro</v>
       </c>
       <c r="F55" s="10">
-        <f>IF(D55&lt;=$G$7,$G$1*12*(1+$D$3)^(D55-1),0)</f>
+        <f>IF(D55&lt;=$G$8,$G$1*12*(1+$D$3)^(D55-1),0)</f>
         <v>0</v>
       </c>
       <c r="G55" s="10">
@@ -8639,7 +8647,7 @@
         <v>Retiro</v>
       </c>
       <c r="F56" s="10">
-        <f>IF(D56&lt;=$G$7,$G$1*12*(1+$D$3)^(D56-1),0)</f>
+        <f>IF(D56&lt;=$G$8,$G$1*12*(1+$D$3)^(D56-1),0)</f>
         <v>0</v>
       </c>
       <c r="G56" s="10">
@@ -8765,7 +8773,7 @@
         <v>Retiro</v>
       </c>
       <c r="F57" s="10">
-        <f>IF(D57&lt;=$G$7,$G$1*12*(1+$D$3)^(D57-1),0)</f>
+        <f>IF(D57&lt;=$G$8,$G$1*12*(1+$D$3)^(D57-1),0)</f>
         <v>0</v>
       </c>
       <c r="G57" s="10">
@@ -8891,7 +8899,7 @@
         <v>Retiro</v>
       </c>
       <c r="F58" s="10">
-        <f>IF(D58&lt;=$G$7,$G$1*12*(1+$D$3)^(D58-1),0)</f>
+        <f>IF(D58&lt;=$G$8,$G$1*12*(1+$D$3)^(D58-1),0)</f>
         <v>0</v>
       </c>
       <c r="G58" s="10">
@@ -9017,7 +9025,7 @@
         <v>Retiro</v>
       </c>
       <c r="F59" s="10">
-        <f>IF(D59&lt;=$G$7,$G$1*12*(1+$D$3)^(D59-1),0)</f>
+        <f>IF(D59&lt;=$G$8,$G$1*12*(1+$D$3)^(D59-1),0)</f>
         <v>0</v>
       </c>
       <c r="G59" s="10">
@@ -9143,7 +9151,7 @@
         <v>Retiro</v>
       </c>
       <c r="F60" s="10">
-        <f>IF(D60&lt;=$G$7,$G$1*12*(1+$D$3)^(D60-1),0)</f>
+        <f>IF(D60&lt;=$G$8,$G$1*12*(1+$D$3)^(D60-1),0)</f>
         <v>0</v>
       </c>
       <c r="G60" s="10">
@@ -9269,7 +9277,7 @@
         <v>Retiro</v>
       </c>
       <c r="F61" s="10">
-        <f>IF(D61&lt;=$G$7,$G$1*12*(1+$D$3)^(D61-1),0)</f>
+        <f>IF(D61&lt;=$G$8,$G$1*12*(1+$D$3)^(D61-1),0)</f>
         <v>0</v>
       </c>
       <c r="G61" s="10">
@@ -9395,7 +9403,7 @@
         <v>Retiro</v>
       </c>
       <c r="F62" s="10">
-        <f>IF(D62&lt;=$G$7,$G$1*12*(1+$D$3)^(D62-1),0)</f>
+        <f>IF(D62&lt;=$G$8,$G$1*12*(1+$D$3)^(D62-1),0)</f>
         <v>0</v>
       </c>
       <c r="G62" s="10">
@@ -9521,7 +9529,7 @@
         <v>Retiro</v>
       </c>
       <c r="F63" s="10">
-        <f>IF(D63&lt;=$G$7,$G$1*12*(1+$D$3)^(D63-1),0)</f>
+        <f>IF(D63&lt;=$G$8,$G$1*12*(1+$D$3)^(D63-1),0)</f>
         <v>0</v>
       </c>
       <c r="G63" s="10">
@@ -9647,7 +9655,7 @@
         <v>Retiro</v>
       </c>
       <c r="F64" s="10">
-        <f>IF(D64&lt;=$G$7,$G$1*12*(1+$D$3)^(D64-1),0)</f>
+        <f>IF(D64&lt;=$G$8,$G$1*12*(1+$D$3)^(D64-1),0)</f>
         <v>0</v>
       </c>
       <c r="G64" s="10">
@@ -9773,7 +9781,7 @@
         <v>Retiro</v>
       </c>
       <c r="F65" s="10">
-        <f>IF(D65&lt;=$G$7,$G$1*12*(1+$D$3)^(D65-1),0)</f>
+        <f>IF(D65&lt;=$G$8,$G$1*12*(1+$D$3)^(D65-1),0)</f>
         <v>0</v>
       </c>
       <c r="G65" s="10">
@@ -9899,7 +9907,7 @@
         <v>Retiro</v>
       </c>
       <c r="F66" s="10">
-        <f>IF(D66&lt;=$G$7,$G$1*12*(1+$D$3)^(D66-1),0)</f>
+        <f>IF(D66&lt;=$G$8,$G$1*12*(1+$D$3)^(D66-1),0)</f>
         <v>0</v>
       </c>
       <c r="G66" s="10">

--- a/Ejemplo - proyeccion por flujo de caja.xlsx
+++ b/Ejemplo - proyeccion por flujo de caja.xlsx
@@ -3727,439 +3727,439 @@
     <row r="78">
       <c r="B78" s="16" t="inlineStr">
         <is>
-          <t>Gastos extraordinarios anuales (US$ de hoy)</t>
-        </is>
-      </c>
-      <c r="C78" s="22">
-        <v>0</v>
-      </c>
+          <t>Gasto familiar por moneda</t>
+        </is>
+      </c>
+      <c r="C78" s="16"/>
       <c r="D78" s="16"/>
       <c r="E78" s="30" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>30% en dólares · 70% en colones (cada parte con la inflación de su moneda)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="B79" s="16" t="inlineStr">
         <is>
-          <t>Gasto familiar por moneda</t>
+          <t>Comentarios del cliente</t>
         </is>
       </c>
       <c r="C79" s="16"/>
       <c r="D79" s="16"/>
-      <c r="E79" s="30" t="inlineStr">
-        <is>
-          <t>30% en dólares · 70% en colones (cada parte con la inflación de su moneda)</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="B80" s="16" t="inlineStr">
-        <is>
-          <t>Comentarios del cliente</t>
-        </is>
-      </c>
-      <c r="C80" s="16"/>
-      <c r="D80" s="16"/>
-      <c r="E80" s="16"/>
-    </row>
-    <row r="82" ht="22" customHeight="1">
-      <c r="B82" s="13" t="inlineStr">
+      <c r="E79" s="16"/>
+    </row>
+    <row r="81" ht="22" customHeight="1">
+      <c r="B81" s="13" t="inlineStr">
         <is>
           <t>Retiro, pensión, fondos y flujos previstos</t>
         </is>
       </c>
-      <c r="C82" s="13"/>
-      <c r="D82" s="13"/>
-      <c r="E82" s="13"/>
+      <c r="C81" s="13"/>
+      <c r="D81" s="13"/>
+      <c r="E81" s="13"/>
+    </row>
+    <row r="82">
+      <c r="B82" s="16" t="inlineStr">
+        <is>
+          <t>Gasto en el retiro (% del gasto actual)</t>
+        </is>
+      </c>
+      <c r="C82" s="24">
+        <v>1</v>
+      </c>
+      <c r="D82" s="16"/>
+      <c r="E82" s="16"/>
     </row>
     <row r="83">
       <c r="B83" s="16" t="inlineStr">
         <is>
-          <t>Gasto en el retiro (% del gasto actual)</t>
-        </is>
-      </c>
-      <c r="C83" s="24">
-        <v>1</v>
-      </c>
+          <t>Régimen de pensión</t>
+        </is>
+      </c>
+      <c r="C83" s="16"/>
       <c r="D83" s="16"/>
-      <c r="E83" s="16"/>
+      <c r="E83" s="30" t="inlineStr">
+        <is>
+          <t>Magisterio Nacional</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="B84" s="16" t="inlineStr">
         <is>
-          <t>Régimen de pensión</t>
-        </is>
-      </c>
-      <c r="C84" s="16"/>
+          <t>Pensión mensual estimada (valor de hoy)</t>
+        </is>
+      </c>
+      <c r="C84" s="22">
+        <v>800000</v>
+      </c>
       <c r="D84" s="16"/>
       <c r="E84" s="30" t="inlineStr">
         <is>
-          <t>Magisterio Nacional</t>
+          <t>CRC</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="B85" s="16" t="inlineStr">
         <is>
-          <t>Pensión mensual estimada (valor de hoy)</t>
-        </is>
-      </c>
-      <c r="C85" s="22">
-        <v>800000</v>
+          <t>Edad de inicio de la pensión</t>
+        </is>
+      </c>
+      <c r="C85" s="32">
+        <v>65</v>
       </c>
       <c r="D85" s="16"/>
-      <c r="E85" s="30" t="inlineStr">
-        <is>
-          <t>CRC</t>
-        </is>
-      </c>
+      <c r="E85" s="16"/>
     </row>
     <row r="86">
       <c r="B86" s="16" t="inlineStr">
         <is>
-          <t>Edad de inicio de la pensión</t>
-        </is>
-      </c>
-      <c r="C86" s="32">
-        <v>65</v>
+          <t>Otros ingresos recurrentes mensuales (valor de hoy)</t>
+        </is>
+      </c>
+      <c r="C86" s="22">
+        <v>500000</v>
       </c>
       <c r="D86" s="16"/>
-      <c r="E86" s="16"/>
+      <c r="E86" s="30" t="inlineStr">
+        <is>
+          <t>CRC · desde 2030 · durante toda la proyección</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="B87" s="16" t="inlineStr">
         <is>
-          <t>Otros ingresos recurrentes mensuales (valor de hoy)</t>
+          <t>ROP: saldo actual</t>
         </is>
       </c>
       <c r="C87" s="22">
-        <v>500000</v>
+        <v>12000000</v>
       </c>
       <c r="D87" s="16"/>
       <c r="E87" s="30" t="inlineStr">
         <is>
-          <t>CRC · desde 2030 · durante toda la proyección</t>
+          <t>CRC · pensión: retiro programado</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="B88" s="16" t="inlineStr">
         <is>
-          <t>ROP: saldo actual</t>
-        </is>
-      </c>
-      <c r="C88" s="22">
-        <v>12000000</v>
-      </c>
+          <t>ROP: aporte mensual</t>
+        </is>
+      </c>
+      <c r="C88" s="16"/>
       <c r="D88" s="16"/>
       <c r="E88" s="30" t="inlineStr">
         <is>
-          <t>CRC · pensión: retiro programado</t>
+          <t>No lo indicó: se estima con el salario</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="B89" s="16" t="inlineStr">
         <is>
-          <t>ROP: aporte mensual</t>
-        </is>
-      </c>
-      <c r="C89" s="16"/>
+          <t>FCL: saldo actual</t>
+        </is>
+      </c>
+      <c r="C89" s="22">
+        <v>12000000</v>
+      </c>
       <c r="D89" s="16"/>
       <c r="E89" s="30" t="inlineStr">
         <is>
-          <t>No lo indicó: se estima con el salario</t>
+          <t>CRC · traslado al momento del retiro</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="B90" s="16" t="inlineStr">
         <is>
-          <t>FCL: saldo actual</t>
-        </is>
-      </c>
-      <c r="C90" s="22">
-        <v>12000000</v>
-      </c>
+          <t>FCL: aporte mensual</t>
+        </is>
+      </c>
+      <c r="C90" s="16"/>
       <c r="D90" s="16"/>
       <c r="E90" s="30" t="inlineStr">
         <is>
-          <t>CRC · traslado al momento del retiro</t>
+          <t>No lo indicó: se estima con el salario</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="B91" s="16" t="inlineStr">
         <is>
-          <t>FCL: aporte mensual</t>
-        </is>
-      </c>
-      <c r="C91" s="16"/>
+          <t>Pensión voluntaria: saldo actual</t>
+        </is>
+      </c>
+      <c r="C91" s="22">
+        <v>12000000</v>
+      </c>
       <c r="D91" s="16"/>
       <c r="E91" s="30" t="inlineStr">
         <is>
-          <t>No lo indicó: se estima con el salario</t>
+          <t>CRC · pensión mensual desde la edad de pensión</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="B92" s="16" t="inlineStr">
         <is>
-          <t>Pensión voluntaria: saldo actual</t>
+          <t>Pensión voluntaria: aporte mensual</t>
         </is>
       </c>
       <c r="C92" s="22">
-        <v>12000000</v>
+        <v>150000</v>
       </c>
       <c r="D92" s="16"/>
       <c r="E92" s="30" t="inlineStr">
         <is>
-          <t>CRC · pensión mensual desde la edad de pensión</t>
+          <t>CRC</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="B93" s="16" t="inlineStr">
         <is>
-          <t>Pensión voluntaria: aporte mensual</t>
+          <t>Ingreso extraordinario 1: Bono por antigüedad (valor de hoy)</t>
         </is>
       </c>
       <c r="C93" s="22">
-        <v>150000</v>
+        <v>40000</v>
       </c>
       <c r="D93" s="16"/>
       <c r="E93" s="30" t="inlineStr">
         <is>
-          <t>CRC</t>
+          <t>USD · año 2028</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="B94" s="16" t="inlineStr">
         <is>
-          <t>Ingreso extraordinario 1: Bono por antigüedad (valor de hoy)</t>
+          <t>Ingreso extraordinario 2: Herencia esperada (valor de hoy)</t>
         </is>
       </c>
       <c r="C94" s="22">
-        <v>40000</v>
+        <v>120000</v>
       </c>
       <c r="D94" s="16"/>
       <c r="E94" s="30" t="inlineStr">
         <is>
-          <t>USD · año 2028</t>
+          <t>USD · año 2032</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="B95" s="16" t="inlineStr">
         <is>
-          <t>Ingreso extraordinario 2: Herencia esperada (valor de hoy)</t>
+          <t>Desinversión: Venta del inmueble 1</t>
         </is>
       </c>
       <c r="C95" s="22">
-        <v>120000</v>
+        <v>180000</v>
       </c>
       <c r="D95" s="16"/>
       <c r="E95" s="30" t="inlineStr">
         <is>
-          <t>USD · año 2032</t>
+          <t>USD · año 2031 · monto que entra al portafolio</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="B96" s="16" t="inlineStr">
         <is>
-          <t>Desinversión: Venta del inmueble 1</t>
+          <t>Desinversión: Venta de un lote</t>
         </is>
       </c>
       <c r="C96" s="22">
-        <v>180000</v>
+        <v>150000</v>
       </c>
       <c r="D96" s="16"/>
       <c r="E96" s="30" t="inlineStr">
         <is>
-          <t>USD · año 2031 · monto que entra al portafolio</t>
+          <t>USD · año 2033 · monto que entra al portafolio</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="B97" s="16" t="inlineStr">
         <is>
-          <t>Desinversión: Venta de un lote</t>
+          <t>Gasto de dependiente 1 (valor de hoy, por año)</t>
         </is>
       </c>
       <c r="C97" s="22">
-        <v>150000</v>
+        <v>12000</v>
       </c>
       <c r="D97" s="16"/>
       <c r="E97" s="30" t="inlineStr">
         <is>
-          <t>USD · año 2033 · monto que entra al portafolio</t>
+          <t>USD · Cónyuge o pareja · salud · desde 2030 por 5 años</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="B98" s="16" t="inlineStr">
         <is>
-          <t>Gasto de dependiente 1 (valor de hoy, por año)</t>
+          <t>Meta 1 (valor de hoy)</t>
         </is>
       </c>
       <c r="C98" s="22">
-        <v>12000</v>
+        <v>40000</v>
       </c>
       <c r="D98" s="16"/>
       <c r="E98" s="30" t="inlineStr">
         <is>
-          <t>USD · Cónyuge o pareja · salud · desde 2030 por 5 años</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="B99" s="16" t="inlineStr">
-        <is>
-          <t>Meta 1 (valor de hoy)</t>
-        </is>
-      </c>
-      <c r="C99" s="22">
-        <v>40000</v>
-      </c>
-      <c r="D99" s="16"/>
-      <c r="E99" s="30" t="inlineStr">
-        <is>
           <t>USD · Vivienda o propiedad · año 2031 · deseable · salida del portafolio</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="22" customHeight="1">
-      <c r="B101" s="13" t="inlineStr">
+    <row r="100" ht="22" customHeight="1">
+      <c r="B100" s="13" t="inlineStr">
         <is>
           <t>Perfil de permanencia y aportes</t>
         </is>
       </c>
-      <c r="C101" s="13"/>
-      <c r="D101" s="13"/>
-      <c r="E101" s="13"/>
+      <c r="C100" s="13"/>
+      <c r="D100" s="13"/>
+      <c r="E100" s="13"/>
+    </row>
+    <row r="101">
+      <c r="B101" s="16" t="inlineStr">
+        <is>
+          <t>Años hasta el primer retiro</t>
+        </is>
+      </c>
+      <c r="C101" s="32">
+        <v>5</v>
+      </c>
+      <c r="D101" s="16"/>
+      <c r="E101" s="16"/>
     </row>
     <row r="102">
       <c r="B102" s="16" t="inlineStr">
         <is>
-          <t>Años hasta el primer retiro</t>
-        </is>
-      </c>
-      <c r="C102" s="32">
-        <v>5</v>
+          <t>Monto del primer retiro (valor de hoy)</t>
+        </is>
+      </c>
+      <c r="C102" s="22">
+        <v>50000</v>
       </c>
       <c r="D102" s="16"/>
-      <c r="E102" s="16"/>
+      <c r="E102" s="30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="B103" s="16" t="inlineStr">
         <is>
-          <t>Monto del primer retiro (valor de hoy)</t>
-        </is>
-      </c>
-      <c r="C103" s="22">
-        <v>50000</v>
-      </c>
+          <t>Destino del patrimonio</t>
+        </is>
+      </c>
+      <c r="C103" s="16"/>
       <c r="D103" s="16"/>
       <c r="E103" s="30" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="B104" s="16" t="inlineStr">
-        <is>
-          <t>Destino del patrimonio</t>
-        </is>
-      </c>
-      <c r="C104" s="16"/>
-      <c r="D104" s="16"/>
-      <c r="E104" s="30" t="inlineStr">
-        <is>
           <t>Utilizarlo durante su vida</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="22" customHeight="1">
-      <c r="B106" s="13" t="inlineStr">
+    <row r="105" ht="22" customHeight="1">
+      <c r="B105" s="13" t="inlineStr">
         <is>
           <t>Hogar, patrimonio y protección</t>
         </is>
       </c>
-      <c r="C106" s="13"/>
-      <c r="D106" s="13"/>
-      <c r="E106" s="13"/>
+      <c r="C105" s="13"/>
+      <c r="D105" s="13"/>
+      <c r="E105" s="13"/>
+    </row>
+    <row r="106">
+      <c r="B106" s="16" t="inlineStr">
+        <is>
+          <t>Hijos</t>
+        </is>
+      </c>
+      <c r="C106" s="16"/>
+      <c r="D106" s="16"/>
+      <c r="E106" s="30" t="inlineStr">
+        <is>
+          <t>No tiene</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="B107" s="16" t="inlineStr">
         <is>
-          <t>Hijos</t>
-        </is>
-      </c>
-      <c r="C107" s="16"/>
+          <t>Otros dependientes</t>
+        </is>
+      </c>
+      <c r="C107" s="32">
+        <v>1</v>
+      </c>
       <c r="D107" s="16"/>
       <c r="E107" s="30" t="inlineStr">
         <is>
-          <t>No tiene</t>
+          <t>otros 1</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="B108" s="16" t="inlineStr">
         <is>
-          <t>Otros dependientes</t>
-        </is>
-      </c>
-      <c r="C108" s="32">
-        <v>1</v>
-      </c>
+          <t>Fuentes del ingreso</t>
+        </is>
+      </c>
+      <c r="C108" s="16"/>
       <c r="D108" s="16"/>
       <c r="E108" s="30" t="inlineStr">
         <is>
-          <t>otros 1</t>
+          <t>Salario · Empresa propia</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="B109" s="16" t="inlineStr">
         <is>
-          <t>Fuentes del ingreso</t>
+          <t>Vivienda principal</t>
         </is>
       </c>
       <c r="C109" s="16"/>
       <c r="D109" s="16"/>
       <c r="E109" s="30" t="inlineStr">
         <is>
-          <t>Salario · Empresa propia</t>
+          <t>Propia, con hipoteca</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="B110" s="16" t="inlineStr">
         <is>
-          <t>Vivienda principal</t>
-        </is>
-      </c>
-      <c r="C110" s="16"/>
+          <t>Saldo de la hipoteca</t>
+        </is>
+      </c>
+      <c r="C110" s="22">
+        <v>120000</v>
+      </c>
       <c r="D110" s="16"/>
       <c r="E110" s="30" t="inlineStr">
         <is>
-          <t>Propia, con hipoteca</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="B111" s="16" t="inlineStr">
         <is>
-          <t>Saldo de la hipoteca</t>
+          <t>Cuota mensual de la hipoteca</t>
         </is>
       </c>
       <c r="C111" s="22">
-        <v>120000</v>
+        <v>1200</v>
       </c>
       <c r="D111" s="16"/>
       <c r="E111" s="30" t="inlineStr">
@@ -4171,27 +4171,23 @@
     <row r="112">
       <c r="B112" s="16" t="inlineStr">
         <is>
-          <t>Cuota mensual de la hipoteca</t>
-        </is>
-      </c>
-      <c r="C112" s="22">
-        <v>1200</v>
+          <t>Tasa de interés anual de la hipoteca</t>
+        </is>
+      </c>
+      <c r="C112" s="24">
+        <v>0.085</v>
       </c>
       <c r="D112" s="16"/>
-      <c r="E112" s="30" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
+      <c r="E112" s="16"/>
     </row>
     <row r="113">
       <c r="B113" s="16" t="inlineStr">
         <is>
-          <t>Tasa de interés anual de la hipoteca</t>
-        </is>
-      </c>
-      <c r="C113" s="24">
-        <v>0.085</v>
+          <t>Plazo restante de la hipoteca (años)</t>
+        </is>
+      </c>
+      <c r="C113" s="32">
+        <v>15</v>
       </c>
       <c r="D113" s="16"/>
       <c r="E113" s="16"/>
@@ -4199,111 +4195,115 @@
     <row r="114">
       <c r="B114" s="16" t="inlineStr">
         <is>
-          <t>Plazo restante de la hipoteca (años)</t>
-        </is>
-      </c>
-      <c r="C114" s="32">
-        <v>15</v>
+          <t>Apartamento en Santa Ana (valor)</t>
+        </is>
+      </c>
+      <c r="C114" s="22">
+        <v>180000</v>
       </c>
       <c r="D114" s="16"/>
-      <c r="E114" s="16"/>
+      <c r="E114" s="30" t="inlineStr">
+        <is>
+          <t>USD · renta neta 1 100 USD · deuda 0 USD · estima venderlo en 2031 · invertiría todo aquí</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="B115" s="16" t="inlineStr">
         <is>
-          <t>Apartamento en Santa Ana (valor)</t>
-        </is>
-      </c>
-      <c r="C115" s="22">
-        <v>180000</v>
-      </c>
+          <t>Empresa propia</t>
+        </is>
+      </c>
+      <c r="C115" s="16"/>
       <c r="D115" s="16"/>
       <c r="E115" s="30" t="inlineStr">
         <is>
-          <t>USD · renta neta 1 100 USD · deuda 0 USD · estima venderlo en 2031 · invertiría todo aquí</t>
+          <t>Estima traspasarla en 10 años · participación 100%</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="B116" s="16" t="inlineStr">
         <is>
-          <t>Empresa propia</t>
-        </is>
-      </c>
-      <c r="C116" s="16"/>
+          <t>Capital privado: valor estimado (100%)</t>
+        </is>
+      </c>
+      <c r="C116" s="22">
+        <v>800000</v>
+      </c>
       <c r="D116" s="16"/>
       <c r="E116" s="30" t="inlineStr">
         <is>
-          <t>Estima traspasarla en 10 años · participación 100%</t>
+          <t>USD · participación 15%</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="B117" s="16" t="inlineStr">
         <is>
-          <t>Capital privado: valor estimado (100%)</t>
-        </is>
-      </c>
-      <c r="C117" s="22">
-        <v>800000</v>
-      </c>
+          <t>Estructuras jurídicas</t>
+        </is>
+      </c>
+      <c r="C117" s="16"/>
       <c r="D117" s="16"/>
       <c r="E117" s="30" t="inlineStr">
         <is>
-          <t>USD · participación 15%</t>
+          <t>No indicó</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="B118" s="16" t="inlineStr">
         <is>
-          <t>Estructuras jurídicas</t>
-        </is>
-      </c>
-      <c r="C118" s="16"/>
+          <t>Valor estimado de la empresa</t>
+        </is>
+      </c>
+      <c r="C118" s="22">
+        <v>900000</v>
+      </c>
       <c r="D118" s="16"/>
       <c r="E118" s="30" t="inlineStr">
         <is>
-          <t>No indicó</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="B119" s="16" t="inlineStr">
         <is>
-          <t>Valor estimado de la empresa</t>
+          <t>Deuda 1: Préstamo personal</t>
         </is>
       </c>
       <c r="C119" s="22">
-        <v>900000</v>
+        <v>5400000</v>
       </c>
       <c r="D119" s="16"/>
       <c r="E119" s="30" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>CRC · cuota 157 500 CRC al mes · tasa 11% · hasta 2029</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="B120" s="16" t="inlineStr">
         <is>
-          <t>Deuda 1: Préstamo personal</t>
+          <t>Deuda 2: Tarjeta de crédito</t>
         </is>
       </c>
       <c r="C120" s="22">
-        <v>5400000</v>
+        <v>3000</v>
       </c>
       <c r="D120" s="16"/>
       <c r="E120" s="30" t="inlineStr">
         <is>
-          <t>CRC · cuota 157 500 CRC al mes · tasa 11% · hasta 2029</t>
+          <t>USD · cuota 150 USD al mes · tasa 32% · hasta 2027</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="B121" s="16" t="inlineStr">
         <is>
-          <t>Deuda 2: Tarjeta de crédito</t>
+          <t>Donaciones al año (valor de hoy)</t>
         </is>
       </c>
       <c r="C121" s="22">
@@ -4312,90 +4312,86 @@
       <c r="D121" s="16"/>
       <c r="E121" s="30" t="inlineStr">
         <is>
-          <t>USD · cuota 150 USD al mes · tasa 32% · hasta 2027</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="B122" s="16" t="inlineStr">
         <is>
-          <t>Donaciones al año (valor de hoy)</t>
+          <t>Gasto extraordinario 1: Seguro y marchamo de vehículos</t>
         </is>
       </c>
       <c r="C122" s="22">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="D122" s="16"/>
       <c r="E122" s="30" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>USD de hoy · cada año desde 2027</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="B123" s="16" t="inlineStr">
         <is>
-          <t>Gasto extraordinario 1: Seguro y marchamo de vehículos</t>
+          <t>Gasto extraordinario 2: Remodelación de la casa</t>
         </is>
       </c>
       <c r="C123" s="22">
-        <v>6000</v>
+        <v>15750000</v>
       </c>
       <c r="D123" s="16"/>
       <c r="E123" s="30" t="inlineStr">
         <is>
-          <t>USD de hoy · cada año desde 2027</t>
+          <t>CRC de hoy · en 2030</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="B124" s="16" t="inlineStr">
         <is>
-          <t>Gasto extraordinario 2: Remodelación de la casa</t>
-        </is>
-      </c>
-      <c r="C124" s="22">
-        <v>15750000</v>
-      </c>
+          <t>Seguros vigentes</t>
+        </is>
+      </c>
+      <c r="C124" s="16"/>
       <c r="D124" s="16"/>
       <c r="E124" s="30" t="inlineStr">
         <is>
-          <t>CRC de hoy · en 2030</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="B125" s="16" t="inlineStr">
-        <is>
-          <t>Seguros vigentes</t>
-        </is>
-      </c>
-      <c r="C125" s="16"/>
-      <c r="D125" s="16"/>
-      <c r="E125" s="30" t="inlineStr">
-        <is>
           <t>Ninguno</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="22" customHeight="1">
-      <c r="B127" s="13" t="inlineStr">
+    <row r="126" ht="22" customHeight="1">
+      <c r="B126" s="13" t="inlineStr">
         <is>
           <t>Patrimonio total (US$, sin la vivienda principal)</t>
         </is>
       </c>
-      <c r="C127" s="13"/>
-      <c r="D127" s="13"/>
-      <c r="E127" s="13"/>
+      <c r="C126" s="13"/>
+      <c r="D126" s="13"/>
+      <c r="E126" s="13"/>
+    </row>
+    <row r="127">
+      <c r="B127" s="16" t="inlineStr">
+        <is>
+          <t>Inversiones líquidas (este portafolio)</t>
+        </is>
+      </c>
+      <c r="C127" s="22">
+        <v>250000</v>
+      </c>
+      <c r="D127" s="16"/>
+      <c r="E127" s="16"/>
     </row>
     <row r="128">
       <c r="B128" s="16" t="inlineStr">
         <is>
-          <t>Inversiones líquidas (este portafolio)</t>
+          <t>Fondos de pensión (ROP, FCL y voluntaria)</t>
         </is>
       </c>
       <c r="C128" s="22">
-        <v>250000</v>
+        <v>80000</v>
       </c>
       <c r="D128" s="16"/>
       <c r="E128" s="16"/>
@@ -4403,11 +4399,11 @@
     <row r="129">
       <c r="B129" s="16" t="inlineStr">
         <is>
-          <t>Fondos de pensión (ROP, FCL y voluntaria)</t>
+          <t>Inversiones inmobiliarias</t>
         </is>
       </c>
       <c r="C129" s="22">
-        <v>80000</v>
+        <v>180000</v>
       </c>
       <c r="D129" s="16"/>
       <c r="E129" s="16"/>
@@ -4415,11 +4411,11 @@
     <row r="130">
       <c r="B130" s="16" t="inlineStr">
         <is>
-          <t>Inversiones inmobiliarias</t>
+          <t>Empresa (según su participación)</t>
         </is>
       </c>
       <c r="C130" s="22">
-        <v>180000</v>
+        <v>900000</v>
       </c>
       <c r="D130" s="16"/>
       <c r="E130" s="16"/>
@@ -4427,11 +4423,11 @@
     <row r="131">
       <c r="B131" s="16" t="inlineStr">
         <is>
-          <t>Empresa (según su participación)</t>
+          <t>Capital privado</t>
         </is>
       </c>
       <c r="C131" s="22">
-        <v>900000</v>
+        <v>120000</v>
       </c>
       <c r="D131" s="16"/>
       <c r="E131" s="16"/>
@@ -4439,11 +4435,11 @@
     <row r="132">
       <c r="B132" s="16" t="inlineStr">
         <is>
-          <t>Capital privado</t>
+          <t>Total de activos</t>
         </is>
       </c>
       <c r="C132" s="22">
-        <v>120000</v>
+        <v>1530000</v>
       </c>
       <c r="D132" s="16"/>
       <c r="E132" s="16"/>
@@ -4451,11 +4447,11 @@
     <row r="133">
       <c r="B133" s="16" t="inlineStr">
         <is>
-          <t>Total de activos</t>
+          <t>Deudas</t>
         </is>
       </c>
       <c r="C133" s="22">
-        <v>1530000</v>
+        <v>-135000</v>
       </c>
       <c r="D133" s="16"/>
       <c r="E133" s="16"/>
@@ -4463,11 +4459,11 @@
     <row r="134">
       <c r="B134" s="16" t="inlineStr">
         <is>
-          <t>Deudas</t>
+          <t>Patrimonio neto</t>
         </is>
       </c>
       <c r="C134" s="22">
-        <v>-135000</v>
+        <v>1395000</v>
       </c>
       <c r="D134" s="16"/>
       <c r="E134" s="16"/>
@@ -4475,61 +4471,61 @@
     <row r="135">
       <c r="B135" s="16" t="inlineStr">
         <is>
-          <t>Patrimonio neto</t>
-        </is>
-      </c>
-      <c r="C135" s="22">
-        <v>1395000</v>
-      </c>
+          <t>Peso del portafolio declarado por el cliente</t>
+        </is>
+      </c>
+      <c r="C135" s="16"/>
       <c r="D135" s="16"/>
-      <c r="E135" s="16"/>
+      <c r="E135" s="30" t="inlineStr">
+        <is>
+          <t>40% del patrimonio total</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="B136" s="16" t="inlineStr">
         <is>
-          <t>Peso del portafolio declarado por el cliente</t>
+          <t>Peso del portafolio calculado (control)</t>
         </is>
       </c>
       <c r="C136" s="16"/>
       <c r="D136" s="16"/>
       <c r="E136" s="30" t="inlineStr">
         <is>
-          <t>40% del patrimonio total</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="B137" s="16" t="inlineStr">
-        <is>
-          <t>Peso del portafolio calculado (control)</t>
-        </is>
-      </c>
-      <c r="C137" s="16"/>
-      <c r="D137" s="16"/>
-      <c r="E137" s="30" t="inlineStr">
-        <is>
           <t>16% de los activos declarados · no interviene en la proyección</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="22" customHeight="1">
-      <c r="B139" s="13" t="inlineStr">
+    <row r="138" ht="22" customHeight="1">
+      <c r="B138" s="13" t="inlineStr">
         <is>
           <t>Supuestos aplicados</t>
         </is>
       </c>
-      <c r="C139" s="13"/>
-      <c r="D139" s="13"/>
-      <c r="E139" s="13"/>
+      <c r="C138" s="13"/>
+      <c r="D138" s="13"/>
+      <c r="E138" s="13"/>
+    </row>
+    <row r="139">
+      <c r="B139" s="16" t="inlineStr">
+        <is>
+          <t>Tipo de cambio ₡/US$</t>
+        </is>
+      </c>
+      <c r="C139" s="22">
+        <v>450</v>
+      </c>
+      <c r="D139" s="16"/>
+      <c r="E139" s="16"/>
     </row>
     <row r="140">
       <c r="B140" s="16" t="inlineStr">
         <is>
-          <t>Tipo de cambio ₡/US$</t>
-        </is>
-      </c>
-      <c r="C140" s="22">
-        <v>450</v>
+          <t>Inflación local (Costa Rica)</t>
+        </is>
+      </c>
+      <c r="C140" s="24">
+        <v>0.039</v>
       </c>
       <c r="D140" s="16"/>
       <c r="E140" s="16"/>
@@ -4537,7 +4533,7 @@
     <row r="141">
       <c r="B141" s="16" t="inlineStr">
         <is>
-          <t>Inflación local (Costa Rica)</t>
+          <t>Inflación internacional (EE. UU.)</t>
         </is>
       </c>
       <c r="C141" s="24">
@@ -4549,11 +4545,11 @@
     <row r="142">
       <c r="B142" s="16" t="inlineStr">
         <is>
-          <t>Inflación internacional (EE. UU.)</t>
+          <t>Inflación de la pensión del IVM</t>
         </is>
       </c>
       <c r="C142" s="24">
-        <v>0.039</v>
+        <v>0.01</v>
       </c>
       <c r="D142" s="16"/>
       <c r="E142" s="16"/>
@@ -4561,11 +4557,11 @@
     <row r="143">
       <c r="B143" s="16" t="inlineStr">
         <is>
-          <t>Inflación de la pensión del IVM</t>
+          <t>Inflación del ROP</t>
         </is>
       </c>
       <c r="C143" s="24">
-        <v>0.01</v>
+        <v>0.039</v>
       </c>
       <c r="D143" s="16"/>
       <c r="E143" s="16"/>
@@ -4573,7 +4569,7 @@
     <row r="144">
       <c r="B144" s="16" t="inlineStr">
         <is>
-          <t>Inflación del ROP</t>
+          <t>Inflación de la pensión voluntaria</t>
         </is>
       </c>
       <c r="C144" s="24">
@@ -4585,11 +4581,11 @@
     <row r="145">
       <c r="B145" s="16" t="inlineStr">
         <is>
-          <t>Inflación de la pensión voluntaria</t>
-        </is>
-      </c>
-      <c r="C145" s="24">
-        <v>0.039</v>
+          <t>Año de inicio</t>
+        </is>
+      </c>
+      <c r="C145" s="32">
+        <v>2026</v>
       </c>
       <c r="D145" s="16"/>
       <c r="E145" s="16"/>
@@ -4597,11 +4593,11 @@
     <row r="146">
       <c r="B146" s="16" t="inlineStr">
         <is>
-          <t>Año de inicio</t>
+          <t>Edad final de la proyección</t>
         </is>
       </c>
       <c r="C146" s="32">
-        <v>2026</v>
+        <v>95</v>
       </c>
       <c r="D146" s="16"/>
       <c r="E146" s="16"/>
@@ -4609,11 +4605,11 @@
     <row r="147">
       <c r="B147" s="16" t="inlineStr">
         <is>
-          <t>Edad final de la proyección</t>
-        </is>
-      </c>
-      <c r="C147" s="32">
-        <v>95</v>
+          <t>Rendimiento de los fondos de pensión</t>
+        </is>
+      </c>
+      <c r="C147" s="24">
+        <v>0.06</v>
       </c>
       <c r="D147" s="16"/>
       <c r="E147" s="16"/>
@@ -4621,11 +4617,11 @@
     <row r="148">
       <c r="B148" s="16" t="inlineStr">
         <is>
-          <t>Rendimiento de los fondos de pensión</t>
+          <t>Aporte al ROP (% del salario, estimado)</t>
         </is>
       </c>
       <c r="C148" s="24">
-        <v>0.06</v>
+        <v>0.0425</v>
       </c>
       <c r="D148" s="16"/>
       <c r="E148" s="16"/>
@@ -4633,11 +4629,11 @@
     <row r="149">
       <c r="B149" s="16" t="inlineStr">
         <is>
-          <t>Aporte al ROP (% del salario, estimado)</t>
+          <t>Aporte al FCL (% del salario, estimado)</t>
         </is>
       </c>
       <c r="C149" s="24">
-        <v>0.0425</v>
+        <v>0.015</v>
       </c>
       <c r="D149" s="16"/>
       <c r="E149" s="16"/>
@@ -4645,106 +4641,94 @@
     <row r="150">
       <c r="B150" s="16" t="inlineStr">
         <is>
-          <t>Aporte al FCL (% del salario, estimado)</t>
-        </is>
-      </c>
-      <c r="C150" s="24">
-        <v>0.015</v>
-      </c>
+          <t>Expectativa de vida (renta temporal)</t>
+        </is>
+      </c>
+      <c r="C150" s="16"/>
       <c r="D150" s="16"/>
-      <c r="E150" s="16"/>
+      <c r="E150" s="30" t="inlineStr">
+        <is>
+          <t>N/A · su ROP no es renta temporal</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="B151" s="16" t="inlineStr">
         <is>
-          <t>Expectativa de vida (renta temporal)</t>
-        </is>
-      </c>
-      <c r="C151" s="16"/>
+          <t>Edad final del retiro programado</t>
+        </is>
+      </c>
+      <c r="C151" s="32">
+        <v>100</v>
+      </c>
       <c r="D151" s="16"/>
-      <c r="E151" s="30" t="inlineStr">
-        <is>
-          <t>N/A · su ROP no es renta temporal</t>
-        </is>
-      </c>
+      <c r="E151" s="16"/>
     </row>
     <row r="152">
       <c r="B152" s="16" t="inlineStr">
         <is>
-          <t>Edad final del retiro programado</t>
-        </is>
-      </c>
-      <c r="C152" s="32">
-        <v>100</v>
-      </c>
+          <t>Edad de independencia financiera</t>
+        </is>
+      </c>
+      <c r="C152" s="16"/>
       <c r="D152" s="16"/>
-      <c r="E152" s="16"/>
+      <c r="E152" s="30" t="inlineStr">
+        <is>
+          <t>60 años · dato del cuestionario</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="B153" s="16" t="inlineStr">
         <is>
-          <t>Edad de independencia financiera</t>
+          <t>Gasto en el retiro</t>
         </is>
       </c>
       <c r="C153" s="16"/>
       <c r="D153" s="16"/>
       <c r="E153" s="30" t="inlineStr">
         <is>
-          <t>60 años · dato del cuestionario</t>
+          <t>100% del gasto actual · dato del cuestionario</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="B154" s="16" t="inlineStr">
         <is>
-          <t>Gasto en el retiro</t>
+          <t>Edad de inicio de la pensión</t>
         </is>
       </c>
       <c r="C154" s="16"/>
       <c r="D154" s="16"/>
       <c r="E154" s="30" t="inlineStr">
         <is>
-          <t>100% del gasto actual · dato del cuestionario</t>
+          <t>65 años · dato del cuestionario</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="B155" s="16" t="inlineStr">
         <is>
-          <t>Edad de inicio de la pensión</t>
+          <t>Modalidad del ROP</t>
         </is>
       </c>
       <c r="C155" s="16"/>
       <c r="D155" s="16"/>
       <c r="E155" s="30" t="inlineStr">
         <is>
-          <t>65 años · dato del cuestionario</t>
+          <t>Retiro programado · dato del cuestionario</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="B156" s="16" t="inlineStr">
         <is>
-          <t>Modalidad del ROP</t>
+          <t>Año de retiro de la pensión voluntaria</t>
         </is>
       </c>
       <c r="C156" s="16"/>
       <c r="D156" s="16"/>
       <c r="E156" s="30" t="inlineStr">
-        <is>
-          <t>Retiro programado · dato del cuestionario</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="B157" s="16" t="inlineStr">
-        <is>
-          <t>Año de retiro de la pensión voluntaria</t>
-        </is>
-      </c>
-      <c r="C157" s="16"/>
-      <c r="D157" s="16"/>
-      <c r="E157" s="30" t="inlineStr">
         <is>
           <t>2031 · dato del cuestionario</t>
         </is>
@@ -4759,11 +4743,11 @@
     <mergeCell ref="B54:E54"/>
     <mergeCell ref="B63:E63"/>
     <mergeCell ref="B74:E74"/>
-    <mergeCell ref="B82:E82"/>
-    <mergeCell ref="B101:E101"/>
-    <mergeCell ref="B106:E106"/>
-    <mergeCell ref="B127:E127"/>
-    <mergeCell ref="B139:E139"/>
+    <mergeCell ref="B81:E81"/>
+    <mergeCell ref="B100:E100"/>
+    <mergeCell ref="B105:E105"/>
+    <mergeCell ref="B126:E126"/>
+    <mergeCell ref="B138:E138"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -21051,7 +21035,7 @@
       <c r="E32" s="16"/>
       <c r="F32" s="16"/>
       <c r="G32" s="22">
-        <f>'Proyección'!$AI$7</f>
+        <f>'Proyección'!$AJ$7</f>
         <v>5754263</v>
       </c>
     </row>
@@ -21066,7 +21050,7 @@
       <c r="E33" s="16"/>
       <c r="F33" s="16"/>
       <c r="G33" s="22">
-        <f>'Proyección'!$AI$8</f>
+        <f>'Proyección'!$AJ$8</f>
         <v>288167</v>
       </c>
     </row>
@@ -21081,7 +21065,7 @@
       <c r="E34" s="23"/>
       <c r="F34" s="23"/>
       <c r="G34" s="23">
-        <f>'Proyección'!$AI$7+'Proyección'!$AI$8</f>
+        <f>'Proyección'!$AJ$7+'Proyección'!$AJ$8</f>
         <v>6042430</v>
       </c>
     </row>
@@ -22300,7 +22284,7 @@
       <c r="E50" s="16"/>
       <c r="F50" s="16"/>
       <c r="G50" s="22">
-        <f>-'Proyección'!$AI$9</f>
+        <f>-'Proyección'!$AJ$9</f>
         <v>10525660</v>
       </c>
     </row>
@@ -22315,7 +22299,7 @@
       <c r="E51" s="16"/>
       <c r="F51" s="16"/>
       <c r="G51" s="22">
-        <f>-'Proyección'!$AI$10</f>
+        <f>-'Proyección'!$AJ$10</f>
         <v>971365</v>
       </c>
     </row>
@@ -22330,7 +22314,7 @@
       <c r="E52" s="23"/>
       <c r="F52" s="23"/>
       <c r="G52" s="23">
-        <f>-'Proyección'!$AI$9-'Proyección'!$AI$10</f>
+        <f>-'Proyección'!$AJ$9-'Proyección'!$AJ$10</f>
         <v>11497025</v>
       </c>
     </row>

--- a/Ejemplo - proyeccion por flujo de caja.xlsx
+++ b/Ejemplo - proyeccion por flujo de caja.xlsx
@@ -4211,14 +4211,16 @@
     <row r="115">
       <c r="B115" s="16" t="inlineStr">
         <is>
-          <t>Empresa propia</t>
-        </is>
-      </c>
-      <c r="C115" s="16"/>
+          <t>Empresa 1: EMPRESA (valor estimado, 100%)</t>
+        </is>
+      </c>
+      <c r="C115" s="22">
+        <v>900000</v>
+      </c>
       <c r="D115" s="16"/>
       <c r="E115" s="30" t="inlineStr">
         <is>
-          <t>Estima traspasarla en 10 años · participación 100%</t>
+          <t>USD · participación 100% · estima traspasarla en 10 años</t>
         </is>
       </c>
     </row>
@@ -4255,39 +4257,39 @@
     <row r="118">
       <c r="B118" s="16" t="inlineStr">
         <is>
-          <t>Valor estimado de la empresa</t>
+          <t>Deuda 1: Préstamo personal</t>
         </is>
       </c>
       <c r="C118" s="22">
-        <v>900000</v>
+        <v>5400000</v>
       </c>
       <c r="D118" s="16"/>
       <c r="E118" s="30" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>CRC · cuota 157 500 CRC al mes · tasa 11% · hasta 2029</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="B119" s="16" t="inlineStr">
         <is>
-          <t>Deuda 1: Préstamo personal</t>
+          <t>Deuda 2: Tarjeta de crédito</t>
         </is>
       </c>
       <c r="C119" s="22">
-        <v>5400000</v>
+        <v>3000</v>
       </c>
       <c r="D119" s="16"/>
       <c r="E119" s="30" t="inlineStr">
         <is>
-          <t>CRC · cuota 157 500 CRC al mes · tasa 11% · hasta 2029</t>
+          <t>USD · cuota 150 USD al mes · tasa 32% · hasta 2027</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="B120" s="16" t="inlineStr">
         <is>
-          <t>Deuda 2: Tarjeta de crédito</t>
+          <t>Donaciones al año (valor de hoy)</t>
         </is>
       </c>
       <c r="C120" s="22">
@@ -4296,90 +4298,86 @@
       <c r="D120" s="16"/>
       <c r="E120" s="30" t="inlineStr">
         <is>
-          <t>USD · cuota 150 USD al mes · tasa 32% · hasta 2027</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="B121" s="16" t="inlineStr">
         <is>
-          <t>Donaciones al año (valor de hoy)</t>
+          <t>Gasto extraordinario 1: Seguro y marchamo de vehículos</t>
         </is>
       </c>
       <c r="C121" s="22">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="D121" s="16"/>
       <c r="E121" s="30" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>USD de hoy · cada año desde 2027</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="B122" s="16" t="inlineStr">
         <is>
-          <t>Gasto extraordinario 1: Seguro y marchamo de vehículos</t>
+          <t>Gasto extraordinario 2: Remodelación de la casa</t>
         </is>
       </c>
       <c r="C122" s="22">
-        <v>6000</v>
+        <v>15750000</v>
       </c>
       <c r="D122" s="16"/>
       <c r="E122" s="30" t="inlineStr">
         <is>
-          <t>USD de hoy · cada año desde 2027</t>
+          <t>CRC de hoy · en 2030</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="B123" s="16" t="inlineStr">
         <is>
-          <t>Gasto extraordinario 2: Remodelación de la casa</t>
-        </is>
-      </c>
-      <c r="C123" s="22">
-        <v>15750000</v>
-      </c>
+          <t>Seguros vigentes</t>
+        </is>
+      </c>
+      <c r="C123" s="16"/>
       <c r="D123" s="16"/>
       <c r="E123" s="30" t="inlineStr">
         <is>
-          <t>CRC de hoy · en 2030</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="B124" s="16" t="inlineStr">
-        <is>
-          <t>Seguros vigentes</t>
-        </is>
-      </c>
-      <c r="C124" s="16"/>
-      <c r="D124" s="16"/>
-      <c r="E124" s="30" t="inlineStr">
-        <is>
           <t>Ninguno</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="22" customHeight="1">
-      <c r="B126" s="13" t="inlineStr">
+    <row r="125" ht="22" customHeight="1">
+      <c r="B125" s="13" t="inlineStr">
         <is>
           <t>Patrimonio total (US$, sin la vivienda principal)</t>
         </is>
       </c>
-      <c r="C126" s="13"/>
-      <c r="D126" s="13"/>
-      <c r="E126" s="13"/>
+      <c r="C125" s="13"/>
+      <c r="D125" s="13"/>
+      <c r="E125" s="13"/>
+    </row>
+    <row r="126">
+      <c r="B126" s="16" t="inlineStr">
+        <is>
+          <t>Inversiones líquidas (este portafolio)</t>
+        </is>
+      </c>
+      <c r="C126" s="22">
+        <v>250000</v>
+      </c>
+      <c r="D126" s="16"/>
+      <c r="E126" s="16"/>
     </row>
     <row r="127">
       <c r="B127" s="16" t="inlineStr">
         <is>
-          <t>Inversiones líquidas (este portafolio)</t>
+          <t>Fondos de pensión (ROP, FCL y voluntaria)</t>
         </is>
       </c>
       <c r="C127" s="22">
-        <v>250000</v>
+        <v>80000</v>
       </c>
       <c r="D127" s="16"/>
       <c r="E127" s="16"/>
@@ -4387,11 +4385,11 @@
     <row r="128">
       <c r="B128" s="16" t="inlineStr">
         <is>
-          <t>Fondos de pensión (ROP, FCL y voluntaria)</t>
+          <t>Inversiones inmobiliarias</t>
         </is>
       </c>
       <c r="C128" s="22">
-        <v>80000</v>
+        <v>180000</v>
       </c>
       <c r="D128" s="16"/>
       <c r="E128" s="16"/>
@@ -4399,11 +4397,11 @@
     <row r="129">
       <c r="B129" s="16" t="inlineStr">
         <is>
-          <t>Inversiones inmobiliarias</t>
+          <t>Empresas (según su participación)</t>
         </is>
       </c>
       <c r="C129" s="22">
-        <v>180000</v>
+        <v>900000</v>
       </c>
       <c r="D129" s="16"/>
       <c r="E129" s="16"/>
@@ -4411,11 +4409,11 @@
     <row r="130">
       <c r="B130" s="16" t="inlineStr">
         <is>
-          <t>Empresa (según su participación)</t>
+          <t>Capital privado</t>
         </is>
       </c>
       <c r="C130" s="22">
-        <v>900000</v>
+        <v>120000</v>
       </c>
       <c r="D130" s="16"/>
       <c r="E130" s="16"/>
@@ -4423,11 +4421,11 @@
     <row r="131">
       <c r="B131" s="16" t="inlineStr">
         <is>
-          <t>Capital privado</t>
+          <t>Total de activos</t>
         </is>
       </c>
       <c r="C131" s="22">
-        <v>120000</v>
+        <v>1530000</v>
       </c>
       <c r="D131" s="16"/>
       <c r="E131" s="16"/>
@@ -4435,11 +4433,11 @@
     <row r="132">
       <c r="B132" s="16" t="inlineStr">
         <is>
-          <t>Total de activos</t>
+          <t>Deudas</t>
         </is>
       </c>
       <c r="C132" s="22">
-        <v>1530000</v>
+        <v>-135000</v>
       </c>
       <c r="D132" s="16"/>
       <c r="E132" s="16"/>
@@ -4447,11 +4445,11 @@
     <row r="133">
       <c r="B133" s="16" t="inlineStr">
         <is>
-          <t>Deudas</t>
+          <t>Patrimonio neto</t>
         </is>
       </c>
       <c r="C133" s="22">
-        <v>-135000</v>
+        <v>1395000</v>
       </c>
       <c r="D133" s="16"/>
       <c r="E133" s="16"/>
@@ -4459,61 +4457,61 @@
     <row r="134">
       <c r="B134" s="16" t="inlineStr">
         <is>
-          <t>Patrimonio neto</t>
-        </is>
-      </c>
-      <c r="C134" s="22">
-        <v>1395000</v>
-      </c>
+          <t>Peso del portafolio declarado por el cliente</t>
+        </is>
+      </c>
+      <c r="C134" s="16"/>
       <c r="D134" s="16"/>
-      <c r="E134" s="16"/>
+      <c r="E134" s="30" t="inlineStr">
+        <is>
+          <t>40% del patrimonio total</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="B135" s="16" t="inlineStr">
         <is>
-          <t>Peso del portafolio declarado por el cliente</t>
+          <t>Peso del portafolio calculado (control)</t>
         </is>
       </c>
       <c r="C135" s="16"/>
       <c r="D135" s="16"/>
       <c r="E135" s="30" t="inlineStr">
         <is>
-          <t>40% del patrimonio total</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="B136" s="16" t="inlineStr">
-        <is>
-          <t>Peso del portafolio calculado (control)</t>
-        </is>
-      </c>
-      <c r="C136" s="16"/>
-      <c r="D136" s="16"/>
-      <c r="E136" s="30" t="inlineStr">
-        <is>
           <t>16% de los activos declarados · no interviene en la proyección</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="22" customHeight="1">
-      <c r="B138" s="13" t="inlineStr">
+    <row r="137" ht="22" customHeight="1">
+      <c r="B137" s="13" t="inlineStr">
         <is>
           <t>Supuestos aplicados</t>
         </is>
       </c>
-      <c r="C138" s="13"/>
-      <c r="D138" s="13"/>
-      <c r="E138" s="13"/>
+      <c r="C137" s="13"/>
+      <c r="D137" s="13"/>
+      <c r="E137" s="13"/>
+    </row>
+    <row r="138">
+      <c r="B138" s="16" t="inlineStr">
+        <is>
+          <t>Tipo de cambio ₡/US$</t>
+        </is>
+      </c>
+      <c r="C138" s="22">
+        <v>450</v>
+      </c>
+      <c r="D138" s="16"/>
+      <c r="E138" s="16"/>
     </row>
     <row r="139">
       <c r="B139" s="16" t="inlineStr">
         <is>
-          <t>Tipo de cambio ₡/US$</t>
-        </is>
-      </c>
-      <c r="C139" s="22">
-        <v>450</v>
+          <t>Inflación local (Costa Rica)</t>
+        </is>
+      </c>
+      <c r="C139" s="24">
+        <v>0.039</v>
       </c>
       <c r="D139" s="16"/>
       <c r="E139" s="16"/>
@@ -4521,7 +4519,7 @@
     <row r="140">
       <c r="B140" s="16" t="inlineStr">
         <is>
-          <t>Inflación local (Costa Rica)</t>
+          <t>Inflación internacional (EE. UU.)</t>
         </is>
       </c>
       <c r="C140" s="24">
@@ -4533,11 +4531,11 @@
     <row r="141">
       <c r="B141" s="16" t="inlineStr">
         <is>
-          <t>Inflación internacional (EE. UU.)</t>
+          <t>Inflación de la pensión del IVM</t>
         </is>
       </c>
       <c r="C141" s="24">
-        <v>0.039</v>
+        <v>0.01</v>
       </c>
       <c r="D141" s="16"/>
       <c r="E141" s="16"/>
@@ -4545,11 +4543,11 @@
     <row r="142">
       <c r="B142" s="16" t="inlineStr">
         <is>
-          <t>Inflación de la pensión del IVM</t>
+          <t>Inflación del ROP</t>
         </is>
       </c>
       <c r="C142" s="24">
-        <v>0.01</v>
+        <v>0.039</v>
       </c>
       <c r="D142" s="16"/>
       <c r="E142" s="16"/>
@@ -4557,7 +4555,7 @@
     <row r="143">
       <c r="B143" s="16" t="inlineStr">
         <is>
-          <t>Inflación del ROP</t>
+          <t>Inflación de la pensión voluntaria</t>
         </is>
       </c>
       <c r="C143" s="24">
@@ -4569,11 +4567,11 @@
     <row r="144">
       <c r="B144" s="16" t="inlineStr">
         <is>
-          <t>Inflación de la pensión voluntaria</t>
-        </is>
-      </c>
-      <c r="C144" s="24">
-        <v>0.039</v>
+          <t>Año de inicio</t>
+        </is>
+      </c>
+      <c r="C144" s="32">
+        <v>2026</v>
       </c>
       <c r="D144" s="16"/>
       <c r="E144" s="16"/>
@@ -4581,11 +4579,11 @@
     <row r="145">
       <c r="B145" s="16" t="inlineStr">
         <is>
-          <t>Año de inicio</t>
+          <t>Edad final de la proyección</t>
         </is>
       </c>
       <c r="C145" s="32">
-        <v>2026</v>
+        <v>95</v>
       </c>
       <c r="D145" s="16"/>
       <c r="E145" s="16"/>
@@ -4593,11 +4591,11 @@
     <row r="146">
       <c r="B146" s="16" t="inlineStr">
         <is>
-          <t>Edad final de la proyección</t>
-        </is>
-      </c>
-      <c r="C146" s="32">
-        <v>95</v>
+          <t>Rendimiento de los fondos de pensión</t>
+        </is>
+      </c>
+      <c r="C146" s="24">
+        <v>0.06</v>
       </c>
       <c r="D146" s="16"/>
       <c r="E146" s="16"/>
@@ -4605,11 +4603,11 @@
     <row r="147">
       <c r="B147" s="16" t="inlineStr">
         <is>
-          <t>Rendimiento de los fondos de pensión</t>
+          <t>Aporte al ROP (% del salario, estimado)</t>
         </is>
       </c>
       <c r="C147" s="24">
-        <v>0.06</v>
+        <v>0.0425</v>
       </c>
       <c r="D147" s="16"/>
       <c r="E147" s="16"/>
@@ -4617,11 +4615,11 @@
     <row r="148">
       <c r="B148" s="16" t="inlineStr">
         <is>
-          <t>Aporte al ROP (% del salario, estimado)</t>
+          <t>Aporte al FCL (% del salario, estimado)</t>
         </is>
       </c>
       <c r="C148" s="24">
-        <v>0.0425</v>
+        <v>0.015</v>
       </c>
       <c r="D148" s="16"/>
       <c r="E148" s="16"/>
@@ -4629,106 +4627,94 @@
     <row r="149">
       <c r="B149" s="16" t="inlineStr">
         <is>
-          <t>Aporte al FCL (% del salario, estimado)</t>
-        </is>
-      </c>
-      <c r="C149" s="24">
-        <v>0.015</v>
-      </c>
+          <t>Expectativa de vida (renta temporal)</t>
+        </is>
+      </c>
+      <c r="C149" s="16"/>
       <c r="D149" s="16"/>
-      <c r="E149" s="16"/>
+      <c r="E149" s="30" t="inlineStr">
+        <is>
+          <t>N/A · su ROP no es renta temporal</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="B150" s="16" t="inlineStr">
         <is>
-          <t>Expectativa de vida (renta temporal)</t>
-        </is>
-      </c>
-      <c r="C150" s="16"/>
+          <t>Edad final del retiro programado</t>
+        </is>
+      </c>
+      <c r="C150" s="32">
+        <v>100</v>
+      </c>
       <c r="D150" s="16"/>
-      <c r="E150" s="30" t="inlineStr">
-        <is>
-          <t>N/A · su ROP no es renta temporal</t>
-        </is>
-      </c>
+      <c r="E150" s="16"/>
     </row>
     <row r="151">
       <c r="B151" s="16" t="inlineStr">
         <is>
-          <t>Edad final del retiro programado</t>
-        </is>
-      </c>
-      <c r="C151" s="32">
-        <v>100</v>
-      </c>
+          <t>Edad de independencia financiera</t>
+        </is>
+      </c>
+      <c r="C151" s="16"/>
       <c r="D151" s="16"/>
-      <c r="E151" s="16"/>
+      <c r="E151" s="30" t="inlineStr">
+        <is>
+          <t>60 años · dato del cuestionario</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="B152" s="16" t="inlineStr">
         <is>
-          <t>Edad de independencia financiera</t>
+          <t>Gasto en el retiro</t>
         </is>
       </c>
       <c r="C152" s="16"/>
       <c r="D152" s="16"/>
       <c r="E152" s="30" t="inlineStr">
         <is>
-          <t>60 años · dato del cuestionario</t>
+          <t>100% del gasto actual · dato del cuestionario</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="B153" s="16" t="inlineStr">
         <is>
-          <t>Gasto en el retiro</t>
+          <t>Edad de inicio de la pensión</t>
         </is>
       </c>
       <c r="C153" s="16"/>
       <c r="D153" s="16"/>
       <c r="E153" s="30" t="inlineStr">
         <is>
-          <t>100% del gasto actual · dato del cuestionario</t>
+          <t>65 años · dato del cuestionario</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="B154" s="16" t="inlineStr">
         <is>
-          <t>Edad de inicio de la pensión</t>
+          <t>Modalidad del ROP</t>
         </is>
       </c>
       <c r="C154" s="16"/>
       <c r="D154" s="16"/>
       <c r="E154" s="30" t="inlineStr">
         <is>
-          <t>65 años · dato del cuestionario</t>
+          <t>Retiro programado · dato del cuestionario</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="B155" s="16" t="inlineStr">
         <is>
-          <t>Modalidad del ROP</t>
+          <t>Año de retiro de la pensión voluntaria</t>
         </is>
       </c>
       <c r="C155" s="16"/>
       <c r="D155" s="16"/>
       <c r="E155" s="30" t="inlineStr">
-        <is>
-          <t>Retiro programado · dato del cuestionario</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="B156" s="16" t="inlineStr">
-        <is>
-          <t>Año de retiro de la pensión voluntaria</t>
-        </is>
-      </c>
-      <c r="C156" s="16"/>
-      <c r="D156" s="16"/>
-      <c r="E156" s="30" t="inlineStr">
         <is>
           <t>2031 · dato del cuestionario</t>
         </is>
@@ -4746,8 +4732,8 @@
     <mergeCell ref="B81:E81"/>
     <mergeCell ref="B100:E100"/>
     <mergeCell ref="B105:E105"/>
-    <mergeCell ref="B126:E126"/>
-    <mergeCell ref="B138:E138"/>
+    <mergeCell ref="B125:E125"/>
+    <mergeCell ref="B137:E137"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -6315,7 +6301,7 @@
         <v>3000</v>
       </c>
       <c r="U29" s="22">
-        <f>IF(D29&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B29)*'Gastos'!$G$22:$G$26)*12)</f>
+        <f>IF(D29&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B29)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B29)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B29)*'Gastos'!$K$51:$K$53)</f>
         <v>20400</v>
       </c>
       <c r="V29" s="23">
@@ -6469,7 +6455,7 @@
         <v>3117</v>
       </c>
       <c r="U30" s="22">
-        <f>IF(D30&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B30)*'Gastos'!$G$22:$G$26)*12)</f>
+        <f>IF(D30&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B30)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B30)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B30)*'Gastos'!$K$51:$K$53)</f>
         <v>20400</v>
       </c>
       <c r="V30" s="23">
@@ -6623,7 +6609,7 @@
         <v>3239</v>
       </c>
       <c r="U31" s="22">
-        <f>IF(D31&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B31)*'Gastos'!$G$22:$G$26)*12)</f>
+        <f>IF(D31&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B31)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B31)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B31)*'Gastos'!$K$51:$K$53)</f>
         <v>18600</v>
       </c>
       <c r="V31" s="23">
@@ -6777,7 +6763,7 @@
         <v>3365</v>
       </c>
       <c r="U32" s="22">
-        <f>IF(D32&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B32)*'Gastos'!$G$22:$G$26)*12)</f>
+        <f>IF(D32&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B32)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B32)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B32)*'Gastos'!$K$51:$K$53)</f>
         <v>18600</v>
       </c>
       <c r="V32" s="23">
@@ -6931,7 +6917,7 @@
         <v>3496</v>
       </c>
       <c r="U33" s="22">
-        <f>IF(D33&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B33)*'Gastos'!$G$22:$G$26)*12)</f>
+        <f>IF(D33&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B33)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B33)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B33)*'Gastos'!$K$51:$K$53)</f>
         <v>14400</v>
       </c>
       <c r="V33" s="23">
@@ -7085,7 +7071,7 @@
         <v>3632</v>
       </c>
       <c r="U34" s="22">
-        <f>IF(D34&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B34)*'Gastos'!$G$22:$G$26)*12)</f>
+        <f>IF(D34&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B34)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B34)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B34)*'Gastos'!$K$51:$K$53)</f>
         <v>14400</v>
       </c>
       <c r="V34" s="23">
@@ -7239,7 +7225,7 @@
         <v>3774</v>
       </c>
       <c r="U35" s="22">
-        <f>IF(D35&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B35)*'Gastos'!$G$22:$G$26)*12)</f>
+        <f>IF(D35&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B35)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B35)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B35)*'Gastos'!$K$51:$K$53)</f>
         <v>14400</v>
       </c>
       <c r="V35" s="23">
@@ -7393,7 +7379,7 @@
         <v>3921</v>
       </c>
       <c r="U36" s="22">
-        <f>IF(D36&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B36)*'Gastos'!$G$22:$G$26)*12)</f>
+        <f>IF(D36&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B36)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B36)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B36)*'Gastos'!$K$51:$K$53)</f>
         <v>14400</v>
       </c>
       <c r="V36" s="23">
@@ -7547,7 +7533,7 @@
         <v>4074</v>
       </c>
       <c r="U37" s="22">
-        <f>IF(D37&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B37)*'Gastos'!$G$22:$G$26)*12)</f>
+        <f>IF(D37&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B37)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B37)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B37)*'Gastos'!$K$51:$K$53)</f>
         <v>14400</v>
       </c>
       <c r="V37" s="23">
@@ -7701,7 +7687,7 @@
         <v>4233</v>
       </c>
       <c r="U38" s="22">
-        <f>IF(D38&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B38)*'Gastos'!$G$22:$G$26)*12)</f>
+        <f>IF(D38&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B38)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B38)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B38)*'Gastos'!$K$51:$K$53)</f>
         <v>14400</v>
       </c>
       <c r="V38" s="23">
@@ -7855,7 +7841,7 @@
         <v>4398</v>
       </c>
       <c r="U39" s="22">
-        <f>IF(D39&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B39)*'Gastos'!$G$22:$G$26)*12)</f>
+        <f>IF(D39&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B39)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B39)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B39)*'Gastos'!$K$51:$K$53)</f>
         <v>14400</v>
       </c>
       <c r="V39" s="23">
@@ -8009,7 +7995,7 @@
         <v>4570</v>
       </c>
       <c r="U40" s="22">
-        <f>IF(D40&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B40)*'Gastos'!$G$22:$G$26)*12)</f>
+        <f>IF(D40&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B40)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B40)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B40)*'Gastos'!$K$51:$K$53)</f>
         <v>14400</v>
       </c>
       <c r="V40" s="23">
@@ -8163,7 +8149,7 @@
         <v>4748</v>
       </c>
       <c r="U41" s="22">
-        <f>IF(D41&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B41)*'Gastos'!$G$22:$G$26)*12)</f>
+        <f>IF(D41&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B41)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B41)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B41)*'Gastos'!$K$51:$K$53)</f>
         <v>14400</v>
       </c>
       <c r="V41" s="23">
@@ -8317,7 +8303,7 @@
         <v>4933</v>
       </c>
       <c r="U42" s="22">
-        <f>IF(D42&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B42)*'Gastos'!$G$22:$G$26)*12)</f>
+        <f>IF(D42&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B42)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B42)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B42)*'Gastos'!$K$51:$K$53)</f>
         <v>14400</v>
       </c>
       <c r="V42" s="23">
@@ -8471,7 +8457,7 @@
         <v>5126</v>
       </c>
       <c r="U43" s="22">
-        <f>IF(D43&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B43)*'Gastos'!$G$22:$G$26)*12)</f>
+        <f>IF(D43&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B43)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B43)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B43)*'Gastos'!$K$51:$K$53)</f>
         <v>14400</v>
       </c>
       <c r="V43" s="23">
@@ -8625,7 +8611,7 @@
         <v>5325</v>
       </c>
       <c r="U44" s="22">
-        <f>IF(D44&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B44)*'Gastos'!$G$22:$G$26)*12)</f>
+        <f>IF(D44&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B44)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B44)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B44)*'Gastos'!$K$51:$K$53)</f>
         <v>0</v>
       </c>
       <c r="V44" s="23">
@@ -8779,7 +8765,7 @@
         <v>5533</v>
       </c>
       <c r="U45" s="22">
-        <f>IF(D45&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B45)*'Gastos'!$G$22:$G$26)*12)</f>
+        <f>IF(D45&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B45)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B45)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B45)*'Gastos'!$K$51:$K$53)</f>
         <v>0</v>
       </c>
       <c r="V45" s="23">
@@ -8933,7 +8919,7 @@
         <v>5749</v>
       </c>
       <c r="U46" s="22">
-        <f>IF(D46&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B46)*'Gastos'!$G$22:$G$26)*12)</f>
+        <f>IF(D46&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B46)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B46)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B46)*'Gastos'!$K$51:$K$53)</f>
         <v>0</v>
       </c>
       <c r="V46" s="23">
@@ -9087,7 +9073,7 @@
         <v>5973</v>
       </c>
       <c r="U47" s="22">
-        <f>IF(D47&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B47)*'Gastos'!$G$22:$G$26)*12)</f>
+        <f>IF(D47&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B47)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B47)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B47)*'Gastos'!$K$51:$K$53)</f>
         <v>0</v>
       </c>
       <c r="V47" s="23">
@@ -9241,7 +9227,7 @@
         <v>6206</v>
       </c>
       <c r="U48" s="22">
-        <f>IF(D48&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B48)*'Gastos'!$G$22:$G$26)*12)</f>
+        <f>IF(D48&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B48)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B48)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B48)*'Gastos'!$K$51:$K$53)</f>
         <v>0</v>
       </c>
       <c r="V48" s="23">
@@ -9395,7 +9381,7 @@
         <v>6448</v>
       </c>
       <c r="U49" s="22">
-        <f>IF(D49&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B49)*'Gastos'!$G$22:$G$26)*12)</f>
+        <f>IF(D49&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B49)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B49)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B49)*'Gastos'!$K$51:$K$53)</f>
         <v>0</v>
       </c>
       <c r="V49" s="23">
@@ -9549,7 +9535,7 @@
         <v>6700</v>
       </c>
       <c r="U50" s="22">
-        <f>IF(D50&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B50)*'Gastos'!$G$22:$G$26)*12)</f>
+        <f>IF(D50&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B50)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B50)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B50)*'Gastos'!$K$51:$K$53)</f>
         <v>0</v>
       </c>
       <c r="V50" s="23">
@@ -9703,7 +9689,7 @@
         <v>6961</v>
       </c>
       <c r="U51" s="22">
-        <f>IF(D51&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B51)*'Gastos'!$G$22:$G$26)*12)</f>
+        <f>IF(D51&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B51)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B51)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B51)*'Gastos'!$K$51:$K$53)</f>
         <v>0</v>
       </c>
       <c r="V51" s="23">
@@ -9857,7 +9843,7 @@
         <v>7232</v>
       </c>
       <c r="U52" s="22">
-        <f>IF(D52&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B52)*'Gastos'!$G$22:$G$26)*12)</f>
+        <f>IF(D52&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B52)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B52)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B52)*'Gastos'!$K$51:$K$53)</f>
         <v>0</v>
       </c>
       <c r="V52" s="23">
@@ -10011,7 +9997,7 @@
         <v>7514</v>
       </c>
       <c r="U53" s="22">
-        <f>IF(D53&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B53)*'Gastos'!$G$22:$G$26)*12)</f>
+        <f>IF(D53&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B53)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B53)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B53)*'Gastos'!$K$51:$K$53)</f>
         <v>0</v>
       </c>
       <c r="V53" s="23">
@@ -10165,7 +10151,7 @@
         <v>7807</v>
       </c>
       <c r="U54" s="22">
-        <f>IF(D54&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B54)*'Gastos'!$G$22:$G$26)*12)</f>
+        <f>IF(D54&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B54)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B54)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B54)*'Gastos'!$K$51:$K$53)</f>
         <v>0</v>
       </c>
       <c r="V54" s="23">
@@ -10319,7 +10305,7 @@
         <v>8112</v>
       </c>
       <c r="U55" s="22">
-        <f>IF(D55&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B55)*'Gastos'!$G$22:$G$26)*12)</f>
+        <f>IF(D55&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B55)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B55)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B55)*'Gastos'!$K$51:$K$53)</f>
         <v>0</v>
       </c>
       <c r="V55" s="23">
@@ -10473,7 +10459,7 @@
         <v>8428</v>
       </c>
       <c r="U56" s="22">
-        <f>IF(D56&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B56)*'Gastos'!$G$22:$G$26)*12)</f>
+        <f>IF(D56&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B56)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B56)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B56)*'Gastos'!$K$51:$K$53)</f>
         <v>0</v>
       </c>
       <c r="V56" s="23">
@@ -10627,7 +10613,7 @@
         <v>8757</v>
       </c>
       <c r="U57" s="22">
-        <f>IF(D57&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B57)*'Gastos'!$G$22:$G$26)*12)</f>
+        <f>IF(D57&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B57)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B57)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B57)*'Gastos'!$K$51:$K$53)</f>
         <v>0</v>
       </c>
       <c r="V57" s="23">
@@ -10781,7 +10767,7 @@
         <v>9099</v>
       </c>
       <c r="U58" s="22">
-        <f>IF(D58&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B58)*'Gastos'!$G$22:$G$26)*12)</f>
+        <f>IF(D58&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B58)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B58)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B58)*'Gastos'!$K$51:$K$53)</f>
         <v>0</v>
       </c>
       <c r="V58" s="23">
@@ -10935,7 +10921,7 @@
         <v>9453</v>
       </c>
       <c r="U59" s="22">
-        <f>IF(D59&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B59)*'Gastos'!$G$22:$G$26)*12)</f>
+        <f>IF(D59&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B59)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B59)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B59)*'Gastos'!$K$51:$K$53)</f>
         <v>0</v>
       </c>
       <c r="V59" s="23">
@@ -11089,7 +11075,7 @@
         <v>9822</v>
       </c>
       <c r="U60" s="22">
-        <f>IF(D60&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B60)*'Gastos'!$G$22:$G$26)*12)</f>
+        <f>IF(D60&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B60)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B60)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B60)*'Gastos'!$K$51:$K$53)</f>
         <v>0</v>
       </c>
       <c r="V60" s="23">
@@ -11243,7 +11229,7 @@
         <v>10205</v>
       </c>
       <c r="U61" s="22">
-        <f>IF(D61&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B61)*'Gastos'!$G$22:$G$26)*12)</f>
+        <f>IF(D61&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B61)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B61)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B61)*'Gastos'!$K$51:$K$53)</f>
         <v>0</v>
       </c>
       <c r="V61" s="23">
@@ -11397,7 +11383,7 @@
         <v>10603</v>
       </c>
       <c r="U62" s="22">
-        <f>IF(D62&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B62)*'Gastos'!$G$22:$G$26)*12)</f>
+        <f>IF(D62&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B62)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B62)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B62)*'Gastos'!$K$51:$K$53)</f>
         <v>0</v>
       </c>
       <c r="V62" s="23">
@@ -11551,7 +11537,7 @@
         <v>11017</v>
       </c>
       <c r="U63" s="22">
-        <f>IF(D63&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B63)*'Gastos'!$G$22:$G$26)*12)</f>
+        <f>IF(D63&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B63)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B63)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B63)*'Gastos'!$K$51:$K$53)</f>
         <v>0</v>
       </c>
       <c r="V63" s="23">
@@ -11705,7 +11691,7 @@
         <v>11446</v>
       </c>
       <c r="U64" s="22">
-        <f>IF(D64&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B64)*'Gastos'!$G$22:$G$26)*12)</f>
+        <f>IF(D64&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B64)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B64)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B64)*'Gastos'!$K$51:$K$53)</f>
         <v>0</v>
       </c>
       <c r="V64" s="23">
@@ -11859,7 +11845,7 @@
         <v>11893</v>
       </c>
       <c r="U65" s="22">
-        <f>IF(D65&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B65)*'Gastos'!$G$22:$G$26)*12)</f>
+        <f>IF(D65&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B65)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B65)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B65)*'Gastos'!$K$51:$K$53)</f>
         <v>0</v>
       </c>
       <c r="V65" s="23">
@@ -12013,7 +11999,7 @@
         <v>12357</v>
       </c>
       <c r="U66" s="22">
-        <f>IF(D66&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B66)*'Gastos'!$G$22:$G$26)*12)</f>
+        <f>IF(D66&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B66)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B66)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B66)*'Gastos'!$K$51:$K$53)</f>
         <v>0</v>
       </c>
       <c r="V66" s="23">
@@ -12167,7 +12153,7 @@
         <v>12838</v>
       </c>
       <c r="U67" s="22">
-        <f>IF(D67&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B67)*'Gastos'!$G$22:$G$26)*12)</f>
+        <f>IF(D67&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B67)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B67)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B67)*'Gastos'!$K$51:$K$53)</f>
         <v>0</v>
       </c>
       <c r="V67" s="23">
@@ -12321,7 +12307,7 @@
         <v>13339</v>
       </c>
       <c r="U68" s="22">
-        <f>IF(D68&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B68)*'Gastos'!$G$22:$G$26)*12)</f>
+        <f>IF(D68&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B68)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B68)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B68)*'Gastos'!$K$51:$K$53)</f>
         <v>0</v>
       </c>
       <c r="V68" s="23">
@@ -12475,7 +12461,7 @@
         <v>13859</v>
       </c>
       <c r="U69" s="22">
-        <f>IF(D69&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B69)*'Gastos'!$G$22:$G$26)*12)</f>
+        <f>IF(D69&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B69)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B69)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B69)*'Gastos'!$K$51:$K$53)</f>
         <v>0</v>
       </c>
       <c r="V69" s="23">
@@ -12629,7 +12615,7 @@
         <v>14400</v>
       </c>
       <c r="U70" s="22">
-        <f>IF(D70&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B70)*'Gastos'!$G$22:$G$26)*12)</f>
+        <f>IF(D70&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B70)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B70)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B70)*'Gastos'!$K$51:$K$53)</f>
         <v>0</v>
       </c>
       <c r="V70" s="23">
@@ -12783,7 +12769,7 @@
         <v>14961</v>
       </c>
       <c r="U71" s="22">
-        <f>IF(D71&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B71)*'Gastos'!$G$22:$G$26)*12)</f>
+        <f>IF(D71&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B71)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B71)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B71)*'Gastos'!$K$51:$K$53)</f>
         <v>0</v>
       </c>
       <c r="V71" s="23">
@@ -12937,7 +12923,7 @@
         <v>15545</v>
       </c>
       <c r="U72" s="22">
-        <f>IF(D72&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B72)*'Gastos'!$G$22:$G$26)*12)</f>
+        <f>IF(D72&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B72)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B72)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B72)*'Gastos'!$K$51:$K$53)</f>
         <v>0</v>
       </c>
       <c r="V72" s="23">
@@ -13091,7 +13077,7 @@
         <v>16151</v>
       </c>
       <c r="U73" s="22">
-        <f>IF(D73&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B73)*'Gastos'!$G$22:$G$26)*12)</f>
+        <f>IF(D73&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B73)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B73)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B73)*'Gastos'!$K$51:$K$53)</f>
         <v>0</v>
       </c>
       <c r="V73" s="23">
@@ -13245,7 +13231,7 @@
         <v>16781</v>
       </c>
       <c r="U74" s="22">
-        <f>IF(D74&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B74)*'Gastos'!$G$22:$G$26)*12)</f>
+        <f>IF(D74&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B74)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B74)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B74)*'Gastos'!$K$51:$K$53)</f>
         <v>0</v>
       </c>
       <c r="V74" s="23">
@@ -13399,7 +13385,7 @@
         <v>17436</v>
       </c>
       <c r="U75" s="22">
-        <f>IF(D75&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B75)*'Gastos'!$G$22:$G$26)*12)</f>
+        <f>IF(D75&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B75)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B75)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B75)*'Gastos'!$K$51:$K$53)</f>
         <v>0</v>
       </c>
       <c r="V75" s="23">
@@ -13553,7 +13539,7 @@
         <v>18116</v>
       </c>
       <c r="U76" s="22">
-        <f>IF(D76&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B76)*'Gastos'!$G$22:$G$26)*12)</f>
+        <f>IF(D76&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B76)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B76)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B76)*'Gastos'!$K$51:$K$53)</f>
         <v>0</v>
       </c>
       <c r="V76" s="23">
@@ -13707,7 +13693,7 @@
         <v>18822</v>
       </c>
       <c r="U77" s="22">
-        <f>IF(D77&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B77)*'Gastos'!$G$22:$G$26)*12)</f>
+        <f>IF(D77&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B77)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B77)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B77)*'Gastos'!$K$51:$K$53)</f>
         <v>0</v>
       </c>
       <c r="V77" s="23">
@@ -13861,7 +13847,7 @@
         <v>19556</v>
       </c>
       <c r="U78" s="22">
-        <f>IF(D78&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B78)*'Gastos'!$G$22:$G$26)*12)</f>
+        <f>IF(D78&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B78)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B78)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B78)*'Gastos'!$K$51:$K$53)</f>
         <v>0</v>
       </c>
       <c r="V78" s="23">
@@ -22242,7 +22228,7 @@
     <row r="47" ht="30" customHeight="1">
       <c r="B47" s="29" t="inlineStr">
         <is>
-          <t>Las metas financiadas con crédito no salen del portafolio y no entran a la proyección.</t>
+          <t>Las metas financiadas con crédito no salen del portafolio: entra a la proyección la cuota anual del crédito (sección siguiente).</t>
         </is>
       </c>
       <c r="C47" s="29"/>
@@ -22259,7 +22245,7 @@
     <row r="49" ht="22" customHeight="1">
       <c r="B49" s="13" t="inlineStr">
         <is>
-          <t>En la proyección · US$ nominales, todo el horizonte</t>
+          <t>Metas financiadas con crédito · cuota anual, desde el año de la meta</t>
         </is>
       </c>
       <c r="C49" s="13"/>
@@ -22273,53 +22259,232 @@
       <c r="K49" s="13"/>
       <c r="L49" s="13"/>
     </row>
-    <row r="50">
-      <c r="B50" s="16" t="inlineStr">
+    <row r="50" ht="32" customHeight="1">
+      <c r="B50" s="21" t="inlineStr">
+        <is>
+          <t>N.º</t>
+        </is>
+      </c>
+      <c r="C50" s="21" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="D50" s="21" t="inlineStr">
+        <is>
+          <t>Monto declarado</t>
+        </is>
+      </c>
+      <c r="E50" s="21" t="inlineStr">
+        <is>
+          <t>Moneda</t>
+        </is>
+      </c>
+      <c r="F50" s="21" t="inlineStr">
+        <is>
+          <t>Tipo de cambio aplicado</t>
+        </is>
+      </c>
+      <c r="G50" s="21" t="inlineStr">
+        <is>
+          <t>Monto en US$</t>
+        </is>
+      </c>
+      <c r="H50" s="21" t="inlineStr">
+        <is>
+          <t>Año de la meta</t>
+        </is>
+      </c>
+      <c r="I50" s="21" t="inlineStr">
+        <is>
+          <t>Plazo (años)</t>
+        </is>
+      </c>
+      <c r="J50" s="21" t="inlineStr">
+        <is>
+          <t>Tasa anual</t>
+        </is>
+      </c>
+      <c r="K50" s="21" t="inlineStr">
+        <is>
+          <t>Cuota anual (US$)</t>
+        </is>
+      </c>
+      <c r="L50" s="21"/>
+    </row>
+    <row r="51">
+      <c r="B51" s="25">
+        <v>1</v>
+      </c>
+      <c r="C51" s="20"/>
+      <c r="D51" s="17"/>
+      <c r="E51" s="33"/>
+      <c r="F51" s="35">
+        <f>IF(E51="CRC",'Proyección'!$F$7,1)</f>
+        <v>1</v>
+      </c>
+      <c r="G51" s="22">
+        <f>D51/F51</f>
+        <v>0</v>
+      </c>
+      <c r="H51" s="34"/>
+      <c r="I51" s="34"/>
+      <c r="J51" s="18"/>
+      <c r="K51" s="22">
+        <f>IF(OR(G51=0,N(I51)=0),0,PMT(N(J51),I51,-G51*(1+IF(E51="CRC",N('Proyección'!$F$8),'Proyección'!$F$9))^(H51-'Proyección'!$B$29)))</f>
+        <v>0</v>
+      </c>
+      <c r="L51" s="16"/>
+    </row>
+    <row r="52">
+      <c r="B52" s="25">
+        <v>2</v>
+      </c>
+      <c r="C52" s="20"/>
+      <c r="D52" s="17"/>
+      <c r="E52" s="33"/>
+      <c r="F52" s="35">
+        <f>IF(E52="CRC",'Proyección'!$F$7,1)</f>
+        <v>1</v>
+      </c>
+      <c r="G52" s="22">
+        <f>D52/F52</f>
+        <v>0</v>
+      </c>
+      <c r="H52" s="34"/>
+      <c r="I52" s="34"/>
+      <c r="J52" s="18"/>
+      <c r="K52" s="22">
+        <f>IF(OR(G52=0,N(I52)=0),0,PMT(N(J52),I52,-G52*(1+IF(E52="CRC",N('Proyección'!$F$8),'Proyección'!$F$9))^(H52-'Proyección'!$B$29)))</f>
+        <v>0</v>
+      </c>
+      <c r="L52" s="16"/>
+    </row>
+    <row r="53">
+      <c r="B53" s="25">
+        <v>3</v>
+      </c>
+      <c r="C53" s="20"/>
+      <c r="D53" s="17"/>
+      <c r="E53" s="33"/>
+      <c r="F53" s="35">
+        <f>IF(E53="CRC",'Proyección'!$F$7,1)</f>
+        <v>1</v>
+      </c>
+      <c r="G53" s="22">
+        <f>D53/F53</f>
+        <v>0</v>
+      </c>
+      <c r="H53" s="34"/>
+      <c r="I53" s="34"/>
+      <c r="J53" s="18"/>
+      <c r="K53" s="22">
+        <f>IF(OR(G53=0,N(I53)=0),0,PMT(N(J53),I53,-G53*(1+IF(E53="CRC",N('Proyección'!$F$8),'Proyección'!$F$9))^(H53-'Proyección'!$B$29)))</f>
+        <v>0</v>
+      </c>
+      <c r="L53" s="16"/>
+    </row>
+    <row r="54">
+      <c r="B54" s="23" t="inlineStr">
+        <is>
+          <t>Total de cuotas anuales de crédito (US$)</t>
+        </is>
+      </c>
+      <c r="C54" s="23"/>
+      <c r="D54" s="23"/>
+      <c r="E54" s="23"/>
+      <c r="F54" s="23"/>
+      <c r="G54" s="23"/>
+      <c r="H54" s="23"/>
+      <c r="I54" s="23"/>
+      <c r="J54" s="23"/>
+      <c r="K54" s="23">
+        <f>SUM(K51:K53)</f>
+        <v>0</v>
+      </c>
+      <c r="L54" s="23"/>
+    </row>
+    <row r="55" ht="30" customHeight="1">
+      <c r="B55" s="29" t="inlineStr">
+        <is>
+          <t>La cuota se paga cada año desde el año de la meta y durante el plazo del crédito, y se suma a las cuotas de hipoteca y deudas de la hoja Proyección. La tasa y el plazo son insumos: al cambiarlos, la proyección se recalcula.</t>
+        </is>
+      </c>
+      <c r="C55" s="29"/>
+      <c r="D55" s="29"/>
+      <c r="E55" s="29"/>
+      <c r="F55" s="29"/>
+      <c r="G55" s="29"/>
+      <c r="H55" s="29"/>
+      <c r="I55" s="29"/>
+      <c r="J55" s="29"/>
+      <c r="K55" s="29"/>
+      <c r="L55" s="29"/>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="B57" s="13" t="inlineStr">
+        <is>
+          <t>En la proyección · US$ nominales, todo el horizonte</t>
+        </is>
+      </c>
+      <c r="C57" s="13"/>
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
+      <c r="K57" s="13"/>
+      <c r="L57" s="13"/>
+    </row>
+    <row r="58">
+      <c r="B58" s="16" t="inlineStr">
         <is>
           <t>Gastos ordinarios</t>
         </is>
       </c>
-      <c r="C50" s="16"/>
-      <c r="D50" s="16"/>
-      <c r="E50" s="16"/>
-      <c r="F50" s="16"/>
-      <c r="G50" s="22">
+      <c r="C58" s="16"/>
+      <c r="D58" s="16"/>
+      <c r="E58" s="16"/>
+      <c r="F58" s="16"/>
+      <c r="G58" s="22">
         <f>-'Proyección'!$AJ$9</f>
         <v>10525660</v>
       </c>
     </row>
-    <row r="51">
-      <c r="B51" s="16" t="inlineStr">
+    <row r="59">
+      <c r="B59" s="16" t="inlineStr">
         <is>
           <t>Gastos extraordinarios</t>
         </is>
       </c>
-      <c r="C51" s="16"/>
-      <c r="D51" s="16"/>
-      <c r="E51" s="16"/>
-      <c r="F51" s="16"/>
-      <c r="G51" s="22">
+      <c r="C59" s="16"/>
+      <c r="D59" s="16"/>
+      <c r="E59" s="16"/>
+      <c r="F59" s="16"/>
+      <c r="G59" s="22">
         <f>-'Proyección'!$AJ$10</f>
         <v>971365</v>
       </c>
     </row>
-    <row r="52">
-      <c r="B52" s="23" t="inlineStr">
+    <row r="60">
+      <c r="B60" s="23" t="inlineStr">
         <is>
           <t>Total de gastos</t>
         </is>
       </c>
-      <c r="C52" s="23"/>
-      <c r="D52" s="23"/>
-      <c r="E52" s="23"/>
-      <c r="F52" s="23"/>
-      <c r="G52" s="23">
+      <c r="C60" s="23"/>
+      <c r="D60" s="23"/>
+      <c r="E60" s="23"/>
+      <c r="F60" s="23"/>
+      <c r="G60" s="23">
         <f>-'Proyección'!$AJ$9-'Proyección'!$AJ$10</f>
         <v>11497025</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="22">
     <mergeCell ref="B2:L2"/>
     <mergeCell ref="B4:L4"/>
     <mergeCell ref="B9:F9"/>
@@ -22336,9 +22501,12 @@
     <mergeCell ref="B46:F46"/>
     <mergeCell ref="B47:L47"/>
     <mergeCell ref="B49:L49"/>
-    <mergeCell ref="B50:F50"/>
-    <mergeCell ref="B51:F51"/>
-    <mergeCell ref="B52:F52"/>
+    <mergeCell ref="B54:J54"/>
+    <mergeCell ref="B55:L55"/>
+    <mergeCell ref="B57:L57"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B59:F59"/>
+    <mergeCell ref="B60:F60"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -22633,7 +22801,7 @@
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>Empresa</t>
+          <t>Empresa: EMPRESA</t>
         </is>
       </c>
       <c r="D16" s="17">

--- a/Ejemplo - proyeccion por flujo de caja.xlsx
+++ b/Ejemplo - proyeccion por flujo de caja.xlsx
@@ -4211,16 +4211,14 @@
     <row r="115">
       <c r="B115" s="16" t="inlineStr">
         <is>
-          <t>Empresa 1: EMPRESA (valor estimado, 100%)</t>
-        </is>
-      </c>
-      <c r="C115" s="22">
-        <v>900000</v>
-      </c>
+          <t>Empresa propia</t>
+        </is>
+      </c>
+      <c r="C115" s="16"/>
       <c r="D115" s="16"/>
       <c r="E115" s="30" t="inlineStr">
         <is>
-          <t>USD · participación 100% · estima traspasarla en 10 años</t>
+          <t>Estima traspasarla en 10 años · participación 100%</t>
         </is>
       </c>
     </row>
@@ -4257,39 +4255,39 @@
     <row r="118">
       <c r="B118" s="16" t="inlineStr">
         <is>
-          <t>Deuda 1: Préstamo personal</t>
+          <t>Valor estimado de la empresa</t>
         </is>
       </c>
       <c r="C118" s="22">
-        <v>5400000</v>
+        <v>900000</v>
       </c>
       <c r="D118" s="16"/>
       <c r="E118" s="30" t="inlineStr">
         <is>
-          <t>CRC · cuota 157 500 CRC al mes · tasa 11% · hasta 2029</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="B119" s="16" t="inlineStr">
         <is>
-          <t>Deuda 2: Tarjeta de crédito</t>
+          <t>Deuda 1: Préstamo personal</t>
         </is>
       </c>
       <c r="C119" s="22">
-        <v>3000</v>
+        <v>5400000</v>
       </c>
       <c r="D119" s="16"/>
       <c r="E119" s="30" t="inlineStr">
         <is>
-          <t>USD · cuota 150 USD al mes · tasa 32% · hasta 2027</t>
+          <t>CRC · cuota 157 500 CRC al mes · tasa 11% · hasta 2029</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="B120" s="16" t="inlineStr">
         <is>
-          <t>Donaciones al año (valor de hoy)</t>
+          <t>Deuda 2: Tarjeta de crédito</t>
         </is>
       </c>
       <c r="C120" s="22">
@@ -4298,86 +4296,90 @@
       <c r="D120" s="16"/>
       <c r="E120" s="30" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>USD · cuota 150 USD al mes · tasa 32% · hasta 2027</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="B121" s="16" t="inlineStr">
         <is>
-          <t>Gasto extraordinario 1: Seguro y marchamo de vehículos</t>
+          <t>Donaciones al año (valor de hoy)</t>
         </is>
       </c>
       <c r="C121" s="22">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="D121" s="16"/>
       <c r="E121" s="30" t="inlineStr">
         <is>
-          <t>USD de hoy · cada año desde 2027</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="B122" s="16" t="inlineStr">
         <is>
-          <t>Gasto extraordinario 2: Remodelación de la casa</t>
+          <t>Gasto extraordinario 1: Seguro y marchamo de vehículos</t>
         </is>
       </c>
       <c r="C122" s="22">
-        <v>15750000</v>
+        <v>6000</v>
       </c>
       <c r="D122" s="16"/>
       <c r="E122" s="30" t="inlineStr">
         <is>
-          <t>CRC de hoy · en 2030</t>
+          <t>USD de hoy · cada año desde 2027</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="B123" s="16" t="inlineStr">
         <is>
-          <t>Seguros vigentes</t>
-        </is>
-      </c>
-      <c r="C123" s="16"/>
+          <t>Gasto extraordinario 2: Remodelación de la casa</t>
+        </is>
+      </c>
+      <c r="C123" s="22">
+        <v>15750000</v>
+      </c>
       <c r="D123" s="16"/>
       <c r="E123" s="30" t="inlineStr">
         <is>
+          <t>CRC de hoy · en 2030</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" s="16" t="inlineStr">
+        <is>
+          <t>Seguros vigentes</t>
+        </is>
+      </c>
+      <c r="C124" s="16"/>
+      <c r="D124" s="16"/>
+      <c r="E124" s="30" t="inlineStr">
+        <is>
           <t>Ninguno</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="22" customHeight="1">
-      <c r="B125" s="13" t="inlineStr">
+    <row r="126" ht="22" customHeight="1">
+      <c r="B126" s="13" t="inlineStr">
         <is>
           <t>Patrimonio total (US$, sin la vivienda principal)</t>
         </is>
       </c>
-      <c r="C125" s="13"/>
-      <c r="D125" s="13"/>
-      <c r="E125" s="13"/>
-    </row>
-    <row r="126">
-      <c r="B126" s="16" t="inlineStr">
-        <is>
-          <t>Inversiones líquidas (este portafolio)</t>
-        </is>
-      </c>
-      <c r="C126" s="22">
-        <v>250000</v>
-      </c>
-      <c r="D126" s="16"/>
-      <c r="E126" s="16"/>
+      <c r="C126" s="13"/>
+      <c r="D126" s="13"/>
+      <c r="E126" s="13"/>
     </row>
     <row r="127">
       <c r="B127" s="16" t="inlineStr">
         <is>
-          <t>Fondos de pensión (ROP, FCL y voluntaria)</t>
+          <t>Inversiones líquidas (este portafolio)</t>
         </is>
       </c>
       <c r="C127" s="22">
-        <v>80000</v>
+        <v>250000</v>
       </c>
       <c r="D127" s="16"/>
       <c r="E127" s="16"/>
@@ -4385,11 +4387,11 @@
     <row r="128">
       <c r="B128" s="16" t="inlineStr">
         <is>
-          <t>Inversiones inmobiliarias</t>
+          <t>Fondos de pensión (ROP, FCL y voluntaria)</t>
         </is>
       </c>
       <c r="C128" s="22">
-        <v>180000</v>
+        <v>80000</v>
       </c>
       <c r="D128" s="16"/>
       <c r="E128" s="16"/>
@@ -4397,11 +4399,11 @@
     <row r="129">
       <c r="B129" s="16" t="inlineStr">
         <is>
-          <t>Empresas (según su participación)</t>
+          <t>Inversiones inmobiliarias</t>
         </is>
       </c>
       <c r="C129" s="22">
-        <v>900000</v>
+        <v>180000</v>
       </c>
       <c r="D129" s="16"/>
       <c r="E129" s="16"/>
@@ -4409,11 +4411,11 @@
     <row r="130">
       <c r="B130" s="16" t="inlineStr">
         <is>
-          <t>Capital privado</t>
+          <t>Empresa (según su participación)</t>
         </is>
       </c>
       <c r="C130" s="22">
-        <v>120000</v>
+        <v>900000</v>
       </c>
       <c r="D130" s="16"/>
       <c r="E130" s="16"/>
@@ -4421,11 +4423,11 @@
     <row r="131">
       <c r="B131" s="16" t="inlineStr">
         <is>
-          <t>Total de activos</t>
+          <t>Capital privado</t>
         </is>
       </c>
       <c r="C131" s="22">
-        <v>1530000</v>
+        <v>120000</v>
       </c>
       <c r="D131" s="16"/>
       <c r="E131" s="16"/>
@@ -4433,11 +4435,11 @@
     <row r="132">
       <c r="B132" s="16" t="inlineStr">
         <is>
-          <t>Deudas</t>
+          <t>Total de activos</t>
         </is>
       </c>
       <c r="C132" s="22">
-        <v>-135000</v>
+        <v>1530000</v>
       </c>
       <c r="D132" s="16"/>
       <c r="E132" s="16"/>
@@ -4445,11 +4447,11 @@
     <row r="133">
       <c r="B133" s="16" t="inlineStr">
         <is>
-          <t>Patrimonio neto</t>
+          <t>Deudas</t>
         </is>
       </c>
       <c r="C133" s="22">
-        <v>1395000</v>
+        <v>-135000</v>
       </c>
       <c r="D133" s="16"/>
       <c r="E133" s="16"/>
@@ -4457,61 +4459,61 @@
     <row r="134">
       <c r="B134" s="16" t="inlineStr">
         <is>
-          <t>Peso del portafolio declarado por el cliente</t>
-        </is>
-      </c>
-      <c r="C134" s="16"/>
+          <t>Patrimonio neto</t>
+        </is>
+      </c>
+      <c r="C134" s="22">
+        <v>1395000</v>
+      </c>
       <c r="D134" s="16"/>
-      <c r="E134" s="30" t="inlineStr">
-        <is>
-          <t>40% del patrimonio total</t>
-        </is>
-      </c>
+      <c r="E134" s="16"/>
     </row>
     <row r="135">
       <c r="B135" s="16" t="inlineStr">
         <is>
-          <t>Peso del portafolio calculado (control)</t>
+          <t>Peso del portafolio declarado por el cliente</t>
         </is>
       </c>
       <c r="C135" s="16"/>
       <c r="D135" s="16"/>
       <c r="E135" s="30" t="inlineStr">
         <is>
+          <t>40% del patrimonio total</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" s="16" t="inlineStr">
+        <is>
+          <t>Peso del portafolio calculado (control)</t>
+        </is>
+      </c>
+      <c r="C136" s="16"/>
+      <c r="D136" s="16"/>
+      <c r="E136" s="30" t="inlineStr">
+        <is>
           <t>16% de los activos declarados · no interviene en la proyección</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="22" customHeight="1">
-      <c r="B137" s="13" t="inlineStr">
+    <row r="138" ht="22" customHeight="1">
+      <c r="B138" s="13" t="inlineStr">
         <is>
           <t>Supuestos aplicados</t>
         </is>
       </c>
-      <c r="C137" s="13"/>
-      <c r="D137" s="13"/>
-      <c r="E137" s="13"/>
-    </row>
-    <row r="138">
-      <c r="B138" s="16" t="inlineStr">
-        <is>
-          <t>Tipo de cambio ₡/US$</t>
-        </is>
-      </c>
-      <c r="C138" s="22">
-        <v>450</v>
-      </c>
-      <c r="D138" s="16"/>
-      <c r="E138" s="16"/>
+      <c r="C138" s="13"/>
+      <c r="D138" s="13"/>
+      <c r="E138" s="13"/>
     </row>
     <row r="139">
       <c r="B139" s="16" t="inlineStr">
         <is>
-          <t>Inflación local (Costa Rica)</t>
-        </is>
-      </c>
-      <c r="C139" s="24">
-        <v>0.039</v>
+          <t>Tipo de cambio ₡/US$</t>
+        </is>
+      </c>
+      <c r="C139" s="22">
+        <v>450</v>
       </c>
       <c r="D139" s="16"/>
       <c r="E139" s="16"/>
@@ -4519,7 +4521,7 @@
     <row r="140">
       <c r="B140" s="16" t="inlineStr">
         <is>
-          <t>Inflación internacional (EE. UU.)</t>
+          <t>Inflación local (Costa Rica)</t>
         </is>
       </c>
       <c r="C140" s="24">
@@ -4531,11 +4533,11 @@
     <row r="141">
       <c r="B141" s="16" t="inlineStr">
         <is>
-          <t>Inflación de la pensión del IVM</t>
+          <t>Inflación internacional (EE. UU.)</t>
         </is>
       </c>
       <c r="C141" s="24">
-        <v>0.01</v>
+        <v>0.039</v>
       </c>
       <c r="D141" s="16"/>
       <c r="E141" s="16"/>
@@ -4543,11 +4545,11 @@
     <row r="142">
       <c r="B142" s="16" t="inlineStr">
         <is>
-          <t>Inflación del ROP</t>
+          <t>Inflación de la pensión del IVM</t>
         </is>
       </c>
       <c r="C142" s="24">
-        <v>0.039</v>
+        <v>0.01</v>
       </c>
       <c r="D142" s="16"/>
       <c r="E142" s="16"/>
@@ -4555,7 +4557,7 @@
     <row r="143">
       <c r="B143" s="16" t="inlineStr">
         <is>
-          <t>Inflación de la pensión voluntaria</t>
+          <t>Inflación del ROP</t>
         </is>
       </c>
       <c r="C143" s="24">
@@ -4567,11 +4569,11 @@
     <row r="144">
       <c r="B144" s="16" t="inlineStr">
         <is>
-          <t>Año de inicio</t>
-        </is>
-      </c>
-      <c r="C144" s="32">
-        <v>2026</v>
+          <t>Inflación de la pensión voluntaria</t>
+        </is>
+      </c>
+      <c r="C144" s="24">
+        <v>0.039</v>
       </c>
       <c r="D144" s="16"/>
       <c r="E144" s="16"/>
@@ -4579,11 +4581,11 @@
     <row r="145">
       <c r="B145" s="16" t="inlineStr">
         <is>
-          <t>Edad final de la proyección</t>
+          <t>Año de inicio</t>
         </is>
       </c>
       <c r="C145" s="32">
-        <v>95</v>
+        <v>2026</v>
       </c>
       <c r="D145" s="16"/>
       <c r="E145" s="16"/>
@@ -4591,11 +4593,11 @@
     <row r="146">
       <c r="B146" s="16" t="inlineStr">
         <is>
-          <t>Rendimiento de los fondos de pensión</t>
-        </is>
-      </c>
-      <c r="C146" s="24">
-        <v>0.06</v>
+          <t>Edad final de la proyección</t>
+        </is>
+      </c>
+      <c r="C146" s="32">
+        <v>95</v>
       </c>
       <c r="D146" s="16"/>
       <c r="E146" s="16"/>
@@ -4603,11 +4605,11 @@
     <row r="147">
       <c r="B147" s="16" t="inlineStr">
         <is>
-          <t>Aporte al ROP (% del salario, estimado)</t>
+          <t>Rendimiento de los fondos de pensión</t>
         </is>
       </c>
       <c r="C147" s="24">
-        <v>0.0425</v>
+        <v>0.06</v>
       </c>
       <c r="D147" s="16"/>
       <c r="E147" s="16"/>
@@ -4615,11 +4617,11 @@
     <row r="148">
       <c r="B148" s="16" t="inlineStr">
         <is>
-          <t>Aporte al FCL (% del salario, estimado)</t>
+          <t>Aporte al ROP (% del salario, estimado)</t>
         </is>
       </c>
       <c r="C148" s="24">
-        <v>0.015</v>
+        <v>0.0425</v>
       </c>
       <c r="D148" s="16"/>
       <c r="E148" s="16"/>
@@ -4627,94 +4629,106 @@
     <row r="149">
       <c r="B149" s="16" t="inlineStr">
         <is>
-          <t>Expectativa de vida (renta temporal)</t>
-        </is>
-      </c>
-      <c r="C149" s="16"/>
+          <t>Aporte al FCL (% del salario, estimado)</t>
+        </is>
+      </c>
+      <c r="C149" s="24">
+        <v>0.015</v>
+      </c>
       <c r="D149" s="16"/>
-      <c r="E149" s="30" t="inlineStr">
-        <is>
-          <t>N/A · su ROP no es renta temporal</t>
-        </is>
-      </c>
+      <c r="E149" s="16"/>
     </row>
     <row r="150">
       <c r="B150" s="16" t="inlineStr">
         <is>
-          <t>Edad final del retiro programado</t>
-        </is>
-      </c>
-      <c r="C150" s="32">
-        <v>100</v>
-      </c>
+          <t>Expectativa de vida (renta temporal)</t>
+        </is>
+      </c>
+      <c r="C150" s="16"/>
       <c r="D150" s="16"/>
-      <c r="E150" s="16"/>
+      <c r="E150" s="30" t="inlineStr">
+        <is>
+          <t>N/A · su ROP no es renta temporal</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="B151" s="16" t="inlineStr">
         <is>
-          <t>Edad de independencia financiera</t>
-        </is>
-      </c>
-      <c r="C151" s="16"/>
+          <t>Edad final del retiro programado</t>
+        </is>
+      </c>
+      <c r="C151" s="32">
+        <v>100</v>
+      </c>
       <c r="D151" s="16"/>
-      <c r="E151" s="30" t="inlineStr">
-        <is>
-          <t>60 años · dato del cuestionario</t>
-        </is>
-      </c>
+      <c r="E151" s="16"/>
     </row>
     <row r="152">
       <c r="B152" s="16" t="inlineStr">
         <is>
-          <t>Gasto en el retiro</t>
+          <t>Edad de independencia financiera</t>
         </is>
       </c>
       <c r="C152" s="16"/>
       <c r="D152" s="16"/>
       <c r="E152" s="30" t="inlineStr">
         <is>
-          <t>100% del gasto actual · dato del cuestionario</t>
+          <t>60 años · dato del cuestionario</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="B153" s="16" t="inlineStr">
         <is>
-          <t>Edad de inicio de la pensión</t>
+          <t>Gasto en el retiro</t>
         </is>
       </c>
       <c r="C153" s="16"/>
       <c r="D153" s="16"/>
       <c r="E153" s="30" t="inlineStr">
         <is>
-          <t>65 años · dato del cuestionario</t>
+          <t>100% del gasto actual · dato del cuestionario</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="B154" s="16" t="inlineStr">
         <is>
-          <t>Modalidad del ROP</t>
+          <t>Edad de inicio de la pensión</t>
         </is>
       </c>
       <c r="C154" s="16"/>
       <c r="D154" s="16"/>
       <c r="E154" s="30" t="inlineStr">
         <is>
-          <t>Retiro programado · dato del cuestionario</t>
+          <t>65 años · dato del cuestionario</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="B155" s="16" t="inlineStr">
         <is>
-          <t>Año de retiro de la pensión voluntaria</t>
+          <t>Modalidad del ROP</t>
         </is>
       </c>
       <c r="C155" s="16"/>
       <c r="D155" s="16"/>
       <c r="E155" s="30" t="inlineStr">
+        <is>
+          <t>Retiro programado · dato del cuestionario</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="B156" s="16" t="inlineStr">
+        <is>
+          <t>Año de retiro de la pensión voluntaria</t>
+        </is>
+      </c>
+      <c r="C156" s="16"/>
+      <c r="D156" s="16"/>
+      <c r="E156" s="30" t="inlineStr">
         <is>
           <t>2031 · dato del cuestionario</t>
         </is>
@@ -4732,8 +4746,8 @@
     <mergeCell ref="B81:E81"/>
     <mergeCell ref="B100:E100"/>
     <mergeCell ref="B105:E105"/>
-    <mergeCell ref="B125:E125"/>
-    <mergeCell ref="B137:E137"/>
+    <mergeCell ref="B126:E126"/>
+    <mergeCell ref="B138:E138"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -6301,7 +6315,7 @@
         <v>3000</v>
       </c>
       <c r="U29" s="22">
-        <f>IF(D29&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B29)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B29)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B29)*'Gastos'!$K$51:$K$53)</f>
+        <f>IF(D29&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B29)*'Gastos'!$G$22:$G$26)*12)</f>
         <v>20400</v>
       </c>
       <c r="V29" s="23">
@@ -6455,7 +6469,7 @@
         <v>3117</v>
       </c>
       <c r="U30" s="22">
-        <f>IF(D30&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B30)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B30)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B30)*'Gastos'!$K$51:$K$53)</f>
+        <f>IF(D30&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B30)*'Gastos'!$G$22:$G$26)*12)</f>
         <v>20400</v>
       </c>
       <c r="V30" s="23">
@@ -6609,7 +6623,7 @@
         <v>3239</v>
       </c>
       <c r="U31" s="22">
-        <f>IF(D31&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B31)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B31)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B31)*'Gastos'!$K$51:$K$53)</f>
+        <f>IF(D31&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B31)*'Gastos'!$G$22:$G$26)*12)</f>
         <v>18600</v>
       </c>
       <c r="V31" s="23">
@@ -6763,7 +6777,7 @@
         <v>3365</v>
       </c>
       <c r="U32" s="22">
-        <f>IF(D32&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B32)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B32)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B32)*'Gastos'!$K$51:$K$53)</f>
+        <f>IF(D32&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B32)*'Gastos'!$G$22:$G$26)*12)</f>
         <v>18600</v>
       </c>
       <c r="V32" s="23">
@@ -6917,7 +6931,7 @@
         <v>3496</v>
       </c>
       <c r="U33" s="22">
-        <f>IF(D33&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B33)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B33)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B33)*'Gastos'!$K$51:$K$53)</f>
+        <f>IF(D33&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B33)*'Gastos'!$G$22:$G$26)*12)</f>
         <v>14400</v>
       </c>
       <c r="V33" s="23">
@@ -7071,7 +7085,7 @@
         <v>3632</v>
       </c>
       <c r="U34" s="22">
-        <f>IF(D34&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B34)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B34)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B34)*'Gastos'!$K$51:$K$53)</f>
+        <f>IF(D34&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B34)*'Gastos'!$G$22:$G$26)*12)</f>
         <v>14400</v>
       </c>
       <c r="V34" s="23">
@@ -7225,7 +7239,7 @@
         <v>3774</v>
       </c>
       <c r="U35" s="22">
-        <f>IF(D35&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B35)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B35)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B35)*'Gastos'!$K$51:$K$53)</f>
+        <f>IF(D35&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B35)*'Gastos'!$G$22:$G$26)*12)</f>
         <v>14400</v>
       </c>
       <c r="V35" s="23">
@@ -7379,7 +7393,7 @@
         <v>3921</v>
       </c>
       <c r="U36" s="22">
-        <f>IF(D36&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B36)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B36)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B36)*'Gastos'!$K$51:$K$53)</f>
+        <f>IF(D36&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B36)*'Gastos'!$G$22:$G$26)*12)</f>
         <v>14400</v>
       </c>
       <c r="V36" s="23">
@@ -7533,7 +7547,7 @@
         <v>4074</v>
       </c>
       <c r="U37" s="22">
-        <f>IF(D37&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B37)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B37)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B37)*'Gastos'!$K$51:$K$53)</f>
+        <f>IF(D37&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B37)*'Gastos'!$G$22:$G$26)*12)</f>
         <v>14400</v>
       </c>
       <c r="V37" s="23">
@@ -7687,7 +7701,7 @@
         <v>4233</v>
       </c>
       <c r="U38" s="22">
-        <f>IF(D38&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B38)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B38)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B38)*'Gastos'!$K$51:$K$53)</f>
+        <f>IF(D38&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B38)*'Gastos'!$G$22:$G$26)*12)</f>
         <v>14400</v>
       </c>
       <c r="V38" s="23">
@@ -7841,7 +7855,7 @@
         <v>4398</v>
       </c>
       <c r="U39" s="22">
-        <f>IF(D39&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B39)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B39)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B39)*'Gastos'!$K$51:$K$53)</f>
+        <f>IF(D39&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B39)*'Gastos'!$G$22:$G$26)*12)</f>
         <v>14400</v>
       </c>
       <c r="V39" s="23">
@@ -7995,7 +8009,7 @@
         <v>4570</v>
       </c>
       <c r="U40" s="22">
-        <f>IF(D40&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B40)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B40)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B40)*'Gastos'!$K$51:$K$53)</f>
+        <f>IF(D40&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B40)*'Gastos'!$G$22:$G$26)*12)</f>
         <v>14400</v>
       </c>
       <c r="V40" s="23">
@@ -8149,7 +8163,7 @@
         <v>4748</v>
       </c>
       <c r="U41" s="22">
-        <f>IF(D41&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B41)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B41)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B41)*'Gastos'!$K$51:$K$53)</f>
+        <f>IF(D41&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B41)*'Gastos'!$G$22:$G$26)*12)</f>
         <v>14400</v>
       </c>
       <c r="V41" s="23">
@@ -8303,7 +8317,7 @@
         <v>4933</v>
       </c>
       <c r="U42" s="22">
-        <f>IF(D42&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B42)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B42)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B42)*'Gastos'!$K$51:$K$53)</f>
+        <f>IF(D42&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B42)*'Gastos'!$G$22:$G$26)*12)</f>
         <v>14400</v>
       </c>
       <c r="V42" s="23">
@@ -8457,7 +8471,7 @@
         <v>5126</v>
       </c>
       <c r="U43" s="22">
-        <f>IF(D43&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B43)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B43)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B43)*'Gastos'!$K$51:$K$53)</f>
+        <f>IF(D43&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B43)*'Gastos'!$G$22:$G$26)*12)</f>
         <v>14400</v>
       </c>
       <c r="V43" s="23">
@@ -8611,7 +8625,7 @@
         <v>5325</v>
       </c>
       <c r="U44" s="22">
-        <f>IF(D44&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B44)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B44)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B44)*'Gastos'!$K$51:$K$53)</f>
+        <f>IF(D44&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B44)*'Gastos'!$G$22:$G$26)*12)</f>
         <v>0</v>
       </c>
       <c r="V44" s="23">
@@ -8765,7 +8779,7 @@
         <v>5533</v>
       </c>
       <c r="U45" s="22">
-        <f>IF(D45&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B45)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B45)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B45)*'Gastos'!$K$51:$K$53)</f>
+        <f>IF(D45&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B45)*'Gastos'!$G$22:$G$26)*12)</f>
         <v>0</v>
       </c>
       <c r="V45" s="23">
@@ -8919,7 +8933,7 @@
         <v>5749</v>
       </c>
       <c r="U46" s="22">
-        <f>IF(D46&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B46)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B46)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B46)*'Gastos'!$K$51:$K$53)</f>
+        <f>IF(D46&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B46)*'Gastos'!$G$22:$G$26)*12)</f>
         <v>0</v>
       </c>
       <c r="V46" s="23">
@@ -9073,7 +9087,7 @@
         <v>5973</v>
       </c>
       <c r="U47" s="22">
-        <f>IF(D47&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B47)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B47)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B47)*'Gastos'!$K$51:$K$53)</f>
+        <f>IF(D47&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B47)*'Gastos'!$G$22:$G$26)*12)</f>
         <v>0</v>
       </c>
       <c r="V47" s="23">
@@ -9227,7 +9241,7 @@
         <v>6206</v>
       </c>
       <c r="U48" s="22">
-        <f>IF(D48&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B48)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B48)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B48)*'Gastos'!$K$51:$K$53)</f>
+        <f>IF(D48&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B48)*'Gastos'!$G$22:$G$26)*12)</f>
         <v>0</v>
       </c>
       <c r="V48" s="23">
@@ -9381,7 +9395,7 @@
         <v>6448</v>
       </c>
       <c r="U49" s="22">
-        <f>IF(D49&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B49)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B49)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B49)*'Gastos'!$K$51:$K$53)</f>
+        <f>IF(D49&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B49)*'Gastos'!$G$22:$G$26)*12)</f>
         <v>0</v>
       </c>
       <c r="V49" s="23">
@@ -9535,7 +9549,7 @@
         <v>6700</v>
       </c>
       <c r="U50" s="22">
-        <f>IF(D50&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B50)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B50)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B50)*'Gastos'!$K$51:$K$53)</f>
+        <f>IF(D50&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B50)*'Gastos'!$G$22:$G$26)*12)</f>
         <v>0</v>
       </c>
       <c r="V50" s="23">
@@ -9689,7 +9703,7 @@
         <v>6961</v>
       </c>
       <c r="U51" s="22">
-        <f>IF(D51&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B51)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B51)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B51)*'Gastos'!$K$51:$K$53)</f>
+        <f>IF(D51&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B51)*'Gastos'!$G$22:$G$26)*12)</f>
         <v>0</v>
       </c>
       <c r="V51" s="23">
@@ -9843,7 +9857,7 @@
         <v>7232</v>
       </c>
       <c r="U52" s="22">
-        <f>IF(D52&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B52)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B52)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B52)*'Gastos'!$K$51:$K$53)</f>
+        <f>IF(D52&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B52)*'Gastos'!$G$22:$G$26)*12)</f>
         <v>0</v>
       </c>
       <c r="V52" s="23">
@@ -9997,7 +10011,7 @@
         <v>7514</v>
       </c>
       <c r="U53" s="22">
-        <f>IF(D53&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B53)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B53)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B53)*'Gastos'!$K$51:$K$53)</f>
+        <f>IF(D53&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B53)*'Gastos'!$G$22:$G$26)*12)</f>
         <v>0</v>
       </c>
       <c r="V53" s="23">
@@ -10151,7 +10165,7 @@
         <v>7807</v>
       </c>
       <c r="U54" s="22">
-        <f>IF(D54&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B54)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B54)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B54)*'Gastos'!$K$51:$K$53)</f>
+        <f>IF(D54&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B54)*'Gastos'!$G$22:$G$26)*12)</f>
         <v>0</v>
       </c>
       <c r="V54" s="23">
@@ -10305,7 +10319,7 @@
         <v>8112</v>
       </c>
       <c r="U55" s="22">
-        <f>IF(D55&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B55)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B55)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B55)*'Gastos'!$K$51:$K$53)</f>
+        <f>IF(D55&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B55)*'Gastos'!$G$22:$G$26)*12)</f>
         <v>0</v>
       </c>
       <c r="V55" s="23">
@@ -10459,7 +10473,7 @@
         <v>8428</v>
       </c>
       <c r="U56" s="22">
-        <f>IF(D56&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B56)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B56)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B56)*'Gastos'!$K$51:$K$53)</f>
+        <f>IF(D56&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B56)*'Gastos'!$G$22:$G$26)*12)</f>
         <v>0</v>
       </c>
       <c r="V56" s="23">
@@ -10613,7 +10627,7 @@
         <v>8757</v>
       </c>
       <c r="U57" s="22">
-        <f>IF(D57&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B57)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B57)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B57)*'Gastos'!$K$51:$K$53)</f>
+        <f>IF(D57&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B57)*'Gastos'!$G$22:$G$26)*12)</f>
         <v>0</v>
       </c>
       <c r="V57" s="23">
@@ -10767,7 +10781,7 @@
         <v>9099</v>
       </c>
       <c r="U58" s="22">
-        <f>IF(D58&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B58)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B58)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B58)*'Gastos'!$K$51:$K$53)</f>
+        <f>IF(D58&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B58)*'Gastos'!$G$22:$G$26)*12)</f>
         <v>0</v>
       </c>
       <c r="V58" s="23">
@@ -10921,7 +10935,7 @@
         <v>9453</v>
       </c>
       <c r="U59" s="22">
-        <f>IF(D59&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B59)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B59)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B59)*'Gastos'!$K$51:$K$53)</f>
+        <f>IF(D59&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B59)*'Gastos'!$G$22:$G$26)*12)</f>
         <v>0</v>
       </c>
       <c r="V59" s="23">
@@ -11075,7 +11089,7 @@
         <v>9822</v>
       </c>
       <c r="U60" s="22">
-        <f>IF(D60&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B60)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B60)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B60)*'Gastos'!$K$51:$K$53)</f>
+        <f>IF(D60&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B60)*'Gastos'!$G$22:$G$26)*12)</f>
         <v>0</v>
       </c>
       <c r="V60" s="23">
@@ -11229,7 +11243,7 @@
         <v>10205</v>
       </c>
       <c r="U61" s="22">
-        <f>IF(D61&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B61)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B61)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B61)*'Gastos'!$K$51:$K$53)</f>
+        <f>IF(D61&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B61)*'Gastos'!$G$22:$G$26)*12)</f>
         <v>0</v>
       </c>
       <c r="V61" s="23">
@@ -11383,7 +11397,7 @@
         <v>10603</v>
       </c>
       <c r="U62" s="22">
-        <f>IF(D62&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B62)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B62)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B62)*'Gastos'!$K$51:$K$53)</f>
+        <f>IF(D62&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B62)*'Gastos'!$G$22:$G$26)*12)</f>
         <v>0</v>
       </c>
       <c r="V62" s="23">
@@ -11537,7 +11551,7 @@
         <v>11017</v>
       </c>
       <c r="U63" s="22">
-        <f>IF(D63&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B63)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B63)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B63)*'Gastos'!$K$51:$K$53)</f>
+        <f>IF(D63&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B63)*'Gastos'!$G$22:$G$26)*12)</f>
         <v>0</v>
       </c>
       <c r="V63" s="23">
@@ -11691,7 +11705,7 @@
         <v>11446</v>
       </c>
       <c r="U64" s="22">
-        <f>IF(D64&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B64)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B64)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B64)*'Gastos'!$K$51:$K$53)</f>
+        <f>IF(D64&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B64)*'Gastos'!$G$22:$G$26)*12)</f>
         <v>0</v>
       </c>
       <c r="V64" s="23">
@@ -11845,7 +11859,7 @@
         <v>11893</v>
       </c>
       <c r="U65" s="22">
-        <f>IF(D65&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B65)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B65)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B65)*'Gastos'!$K$51:$K$53)</f>
+        <f>IF(D65&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B65)*'Gastos'!$G$22:$G$26)*12)</f>
         <v>0</v>
       </c>
       <c r="V65" s="23">
@@ -11999,7 +12013,7 @@
         <v>12357</v>
       </c>
       <c r="U66" s="22">
-        <f>IF(D66&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B66)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B66)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B66)*'Gastos'!$K$51:$K$53)</f>
+        <f>IF(D66&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B66)*'Gastos'!$G$22:$G$26)*12)</f>
         <v>0</v>
       </c>
       <c r="V66" s="23">
@@ -12153,7 +12167,7 @@
         <v>12838</v>
       </c>
       <c r="U67" s="22">
-        <f>IF(D67&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B67)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B67)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B67)*'Gastos'!$K$51:$K$53)</f>
+        <f>IF(D67&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B67)*'Gastos'!$G$22:$G$26)*12)</f>
         <v>0</v>
       </c>
       <c r="V67" s="23">
@@ -12307,7 +12321,7 @@
         <v>13339</v>
       </c>
       <c r="U68" s="22">
-        <f>IF(D68&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B68)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B68)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B68)*'Gastos'!$K$51:$K$53)</f>
+        <f>IF(D68&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B68)*'Gastos'!$G$22:$G$26)*12)</f>
         <v>0</v>
       </c>
       <c r="V68" s="23">
@@ -12461,7 +12475,7 @@
         <v>13859</v>
       </c>
       <c r="U69" s="22">
-        <f>IF(D69&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B69)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B69)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B69)*'Gastos'!$K$51:$K$53)</f>
+        <f>IF(D69&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B69)*'Gastos'!$G$22:$G$26)*12)</f>
         <v>0</v>
       </c>
       <c r="V69" s="23">
@@ -12615,7 +12629,7 @@
         <v>14400</v>
       </c>
       <c r="U70" s="22">
-        <f>IF(D70&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B70)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B70)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B70)*'Gastos'!$K$51:$K$53)</f>
+        <f>IF(D70&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B70)*'Gastos'!$G$22:$G$26)*12)</f>
         <v>0</v>
       </c>
       <c r="V70" s="23">
@@ -12769,7 +12783,7 @@
         <v>14961</v>
       </c>
       <c r="U71" s="22">
-        <f>IF(D71&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B71)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B71)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B71)*'Gastos'!$K$51:$K$53)</f>
+        <f>IF(D71&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B71)*'Gastos'!$G$22:$G$26)*12)</f>
         <v>0</v>
       </c>
       <c r="V71" s="23">
@@ -12923,7 +12937,7 @@
         <v>15545</v>
       </c>
       <c r="U72" s="22">
-        <f>IF(D72&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B72)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B72)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B72)*'Gastos'!$K$51:$K$53)</f>
+        <f>IF(D72&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B72)*'Gastos'!$G$22:$G$26)*12)</f>
         <v>0</v>
       </c>
       <c r="V72" s="23">
@@ -13077,7 +13091,7 @@
         <v>16151</v>
       </c>
       <c r="U73" s="22">
-        <f>IF(D73&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B73)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B73)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B73)*'Gastos'!$K$51:$K$53)</f>
+        <f>IF(D73&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B73)*'Gastos'!$G$22:$G$26)*12)</f>
         <v>0</v>
       </c>
       <c r="V73" s="23">
@@ -13231,7 +13245,7 @@
         <v>16781</v>
       </c>
       <c r="U74" s="22">
-        <f>IF(D74&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B74)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B74)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B74)*'Gastos'!$K$51:$K$53)</f>
+        <f>IF(D74&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B74)*'Gastos'!$G$22:$G$26)*12)</f>
         <v>0</v>
       </c>
       <c r="V74" s="23">
@@ -13385,7 +13399,7 @@
         <v>17436</v>
       </c>
       <c r="U75" s="22">
-        <f>IF(D75&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B75)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B75)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B75)*'Gastos'!$K$51:$K$53)</f>
+        <f>IF(D75&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B75)*'Gastos'!$G$22:$G$26)*12)</f>
         <v>0</v>
       </c>
       <c r="V75" s="23">
@@ -13539,7 +13553,7 @@
         <v>18116</v>
       </c>
       <c r="U76" s="22">
-        <f>IF(D76&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B76)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B76)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B76)*'Gastos'!$K$51:$K$53)</f>
+        <f>IF(D76&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B76)*'Gastos'!$G$22:$G$26)*12)</f>
         <v>0</v>
       </c>
       <c r="V76" s="23">
@@ -13693,7 +13707,7 @@
         <v>18822</v>
       </c>
       <c r="U77" s="22">
-        <f>IF(D77&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B77)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B77)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B77)*'Gastos'!$K$51:$K$53)</f>
+        <f>IF(D77&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B77)*'Gastos'!$G$22:$G$26)*12)</f>
         <v>0</v>
       </c>
       <c r="V77" s="23">
@@ -13847,7 +13861,7 @@
         <v>19556</v>
       </c>
       <c r="U78" s="22">
-        <f>IF(D78&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B78)*'Gastos'!$G$22:$G$26)*12)+SUMPRODUCT(('Gastos'!$H$51:$H$53&lt;=B78)*('Gastos'!$H$51:$H$53+'Gastos'!$I$51:$I$53-1&gt;=B78)*'Gastos'!$K$51:$K$53)</f>
+        <f>IF(D78&lt;=$X$11,$W$11*12,0)+IF('Gastos'!$G$28="Sí",0,SUMPRODUCT(('Gastos'!$H$22:$H$26&gt;=B78)*'Gastos'!$G$22:$G$26)*12)</f>
         <v>0</v>
       </c>
       <c r="V78" s="23">
@@ -22228,7 +22242,7 @@
     <row r="47" ht="30" customHeight="1">
       <c r="B47" s="29" t="inlineStr">
         <is>
-          <t>Las metas financiadas con crédito no salen del portafolio: entra a la proyección la cuota anual del crédito (sección siguiente).</t>
+          <t>Las metas financiadas con crédito no salen del portafolio y no entran a la proyección.</t>
         </is>
       </c>
       <c r="C47" s="29"/>
@@ -22245,7 +22259,7 @@
     <row r="49" ht="22" customHeight="1">
       <c r="B49" s="13" t="inlineStr">
         <is>
-          <t>Metas financiadas con crédito · cuota anual, desde el año de la meta</t>
+          <t>En la proyección · US$ nominales, todo el horizonte</t>
         </is>
       </c>
       <c r="C49" s="13"/>
@@ -22259,232 +22273,53 @@
       <c r="K49" s="13"/>
       <c r="L49" s="13"/>
     </row>
-    <row r="50" ht="32" customHeight="1">
-      <c r="B50" s="21" t="inlineStr">
-        <is>
-          <t>N.º</t>
-        </is>
-      </c>
-      <c r="C50" s="21" t="inlineStr">
-        <is>
-          <t>Meta</t>
-        </is>
-      </c>
-      <c r="D50" s="21" t="inlineStr">
-        <is>
-          <t>Monto declarado</t>
-        </is>
-      </c>
-      <c r="E50" s="21" t="inlineStr">
-        <is>
-          <t>Moneda</t>
-        </is>
-      </c>
-      <c r="F50" s="21" t="inlineStr">
-        <is>
-          <t>Tipo de cambio aplicado</t>
-        </is>
-      </c>
-      <c r="G50" s="21" t="inlineStr">
-        <is>
-          <t>Monto en US$</t>
-        </is>
-      </c>
-      <c r="H50" s="21" t="inlineStr">
-        <is>
-          <t>Año de la meta</t>
-        </is>
-      </c>
-      <c r="I50" s="21" t="inlineStr">
-        <is>
-          <t>Plazo (años)</t>
-        </is>
-      </c>
-      <c r="J50" s="21" t="inlineStr">
-        <is>
-          <t>Tasa anual</t>
-        </is>
-      </c>
-      <c r="K50" s="21" t="inlineStr">
-        <is>
-          <t>Cuota anual (US$)</t>
-        </is>
-      </c>
-      <c r="L50" s="21"/>
-    </row>
-    <row r="51">
-      <c r="B51" s="25">
-        <v>1</v>
-      </c>
-      <c r="C51" s="20"/>
-      <c r="D51" s="17"/>
-      <c r="E51" s="33"/>
-      <c r="F51" s="35">
-        <f>IF(E51="CRC",'Proyección'!$F$7,1)</f>
-        <v>1</v>
-      </c>
-      <c r="G51" s="22">
-        <f>D51/F51</f>
-        <v>0</v>
-      </c>
-      <c r="H51" s="34"/>
-      <c r="I51" s="34"/>
-      <c r="J51" s="18"/>
-      <c r="K51" s="22">
-        <f>IF(OR(G51=0,N(I51)=0),0,PMT(N(J51),I51,-G51*(1+IF(E51="CRC",N('Proyección'!$F$8),'Proyección'!$F$9))^(H51-'Proyección'!$B$29)))</f>
-        <v>0</v>
-      </c>
-      <c r="L51" s="16"/>
-    </row>
-    <row r="52">
-      <c r="B52" s="25">
-        <v>2</v>
-      </c>
-      <c r="C52" s="20"/>
-      <c r="D52" s="17"/>
-      <c r="E52" s="33"/>
-      <c r="F52" s="35">
-        <f>IF(E52="CRC",'Proyección'!$F$7,1)</f>
-        <v>1</v>
-      </c>
-      <c r="G52" s="22">
-        <f>D52/F52</f>
-        <v>0</v>
-      </c>
-      <c r="H52" s="34"/>
-      <c r="I52" s="34"/>
-      <c r="J52" s="18"/>
-      <c r="K52" s="22">
-        <f>IF(OR(G52=0,N(I52)=0),0,PMT(N(J52),I52,-G52*(1+IF(E52="CRC",N('Proyección'!$F$8),'Proyección'!$F$9))^(H52-'Proyección'!$B$29)))</f>
-        <v>0</v>
-      </c>
-      <c r="L52" s="16"/>
-    </row>
-    <row r="53">
-      <c r="B53" s="25">
-        <v>3</v>
-      </c>
-      <c r="C53" s="20"/>
-      <c r="D53" s="17"/>
-      <c r="E53" s="33"/>
-      <c r="F53" s="35">
-        <f>IF(E53="CRC",'Proyección'!$F$7,1)</f>
-        <v>1</v>
-      </c>
-      <c r="G53" s="22">
-        <f>D53/F53</f>
-        <v>0</v>
-      </c>
-      <c r="H53" s="34"/>
-      <c r="I53" s="34"/>
-      <c r="J53" s="18"/>
-      <c r="K53" s="22">
-        <f>IF(OR(G53=0,N(I53)=0),0,PMT(N(J53),I53,-G53*(1+IF(E53="CRC",N('Proyección'!$F$8),'Proyección'!$F$9))^(H53-'Proyección'!$B$29)))</f>
-        <v>0</v>
-      </c>
-      <c r="L53" s="16"/>
-    </row>
-    <row r="54">
-      <c r="B54" s="23" t="inlineStr">
-        <is>
-          <t>Total de cuotas anuales de crédito (US$)</t>
-        </is>
-      </c>
-      <c r="C54" s="23"/>
-      <c r="D54" s="23"/>
-      <c r="E54" s="23"/>
-      <c r="F54" s="23"/>
-      <c r="G54" s="23"/>
-      <c r="H54" s="23"/>
-      <c r="I54" s="23"/>
-      <c r="J54" s="23"/>
-      <c r="K54" s="23">
-        <f>SUM(K51:K53)</f>
-        <v>0</v>
-      </c>
-      <c r="L54" s="23"/>
-    </row>
-    <row r="55" ht="30" customHeight="1">
-      <c r="B55" s="29" t="inlineStr">
-        <is>
-          <t>La cuota se paga cada año desde el año de la meta y durante el plazo del crédito, y se suma a las cuotas de hipoteca y deudas de la hoja Proyección. La tasa y el plazo son insumos: al cambiarlos, la proyección se recalcula.</t>
-        </is>
-      </c>
-      <c r="C55" s="29"/>
-      <c r="D55" s="29"/>
-      <c r="E55" s="29"/>
-      <c r="F55" s="29"/>
-      <c r="G55" s="29"/>
-      <c r="H55" s="29"/>
-      <c r="I55" s="29"/>
-      <c r="J55" s="29"/>
-      <c r="K55" s="29"/>
-      <c r="L55" s="29"/>
-    </row>
-    <row r="57" ht="22" customHeight="1">
-      <c r="B57" s="13" t="inlineStr">
-        <is>
-          <t>En la proyección · US$ nominales, todo el horizonte</t>
-        </is>
-      </c>
-      <c r="C57" s="13"/>
-      <c r="D57" s="13"/>
-      <c r="E57" s="13"/>
-      <c r="F57" s="13"/>
-      <c r="G57" s="13"/>
-      <c r="H57" s="13"/>
-      <c r="I57" s="13"/>
-      <c r="J57" s="13"/>
-      <c r="K57" s="13"/>
-      <c r="L57" s="13"/>
-    </row>
-    <row r="58">
-      <c r="B58" s="16" t="inlineStr">
+    <row r="50">
+      <c r="B50" s="16" t="inlineStr">
         <is>
           <t>Gastos ordinarios</t>
         </is>
       </c>
-      <c r="C58" s="16"/>
-      <c r="D58" s="16"/>
-      <c r="E58" s="16"/>
-      <c r="F58" s="16"/>
-      <c r="G58" s="22">
+      <c r="C50" s="16"/>
+      <c r="D50" s="16"/>
+      <c r="E50" s="16"/>
+      <c r="F50" s="16"/>
+      <c r="G50" s="22">
         <f>-'Proyección'!$AJ$9</f>
         <v>10525660</v>
       </c>
     </row>
-    <row r="59">
-      <c r="B59" s="16" t="inlineStr">
+    <row r="51">
+      <c r="B51" s="16" t="inlineStr">
         <is>
           <t>Gastos extraordinarios</t>
         </is>
       </c>
-      <c r="C59" s="16"/>
-      <c r="D59" s="16"/>
-      <c r="E59" s="16"/>
-      <c r="F59" s="16"/>
-      <c r="G59" s="22">
+      <c r="C51" s="16"/>
+      <c r="D51" s="16"/>
+      <c r="E51" s="16"/>
+      <c r="F51" s="16"/>
+      <c r="G51" s="22">
         <f>-'Proyección'!$AJ$10</f>
         <v>971365</v>
       </c>
     </row>
-    <row r="60">
-      <c r="B60" s="23" t="inlineStr">
+    <row r="52">
+      <c r="B52" s="23" t="inlineStr">
         <is>
           <t>Total de gastos</t>
         </is>
       </c>
-      <c r="C60" s="23"/>
-      <c r="D60" s="23"/>
-      <c r="E60" s="23"/>
-      <c r="F60" s="23"/>
-      <c r="G60" s="23">
+      <c r="C52" s="23"/>
+      <c r="D52" s="23"/>
+      <c r="E52" s="23"/>
+      <c r="F52" s="23"/>
+      <c r="G52" s="23">
         <f>-'Proyección'!$AJ$9-'Proyección'!$AJ$10</f>
         <v>11497025</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="19">
     <mergeCell ref="B2:L2"/>
     <mergeCell ref="B4:L4"/>
     <mergeCell ref="B9:F9"/>
@@ -22501,12 +22336,9 @@
     <mergeCell ref="B46:F46"/>
     <mergeCell ref="B47:L47"/>
     <mergeCell ref="B49:L49"/>
-    <mergeCell ref="B54:J54"/>
-    <mergeCell ref="B55:L55"/>
-    <mergeCell ref="B57:L57"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B59:F59"/>
-    <mergeCell ref="B60:F60"/>
+    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B51:F51"/>
+    <mergeCell ref="B52:F52"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -22801,7 +22633,7 @@
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>Empresa: EMPRESA</t>
+          <t>Empresa</t>
         </is>
       </c>
       <c r="D16" s="17">

--- a/Ejemplo - proyeccion por flujo de caja.xlsx
+++ b/Ejemplo - proyeccion por flujo de caja.xlsx
@@ -3168,7 +3168,7 @@
     <row r="57">
       <c r="B57" s="16" t="inlineStr">
         <is>
-          <t>Topes de la firma para el perfil</t>
+          <t>Topes del perfil moderado conservador (de la firma)</t>
         </is>
       </c>
       <c r="C57" s="16"/>

--- a/Ejemplo - proyeccion por flujo de caja.xlsx
+++ b/Ejemplo - proyeccion por flujo de caja.xlsx
@@ -2784,7 +2784,7 @@
     <row r="28" ht="22" customHeight="1">
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>Activos y pasivos (US$, sin la vivienda principal)</t>
+          <t>Activos y pasivos (US$)</t>
         </is>
       </c>
       <c r="C28" s="13"/>
@@ -2890,11 +2890,11 @@
     <row r="35">
       <c r="B35" s="16" t="inlineStr">
         <is>
-          <t>Activo: Capital privado (15%)</t>
+          <t>Activo: Capital privado (monto invertido)</t>
         </is>
       </c>
       <c r="C35" s="22">
-        <v>120000</v>
+        <v>800000</v>
       </c>
       <c r="D35" s="16"/>
       <c r="E35" s="30" t="inlineStr">
@@ -2910,7 +2910,7 @@
         </is>
       </c>
       <c r="C36" s="22">
-        <v>1530000</v>
+        <v>2210000</v>
       </c>
       <c r="D36" s="16"/>
       <c r="E36" s="16"/>
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="C41" s="22">
-        <v>1395000</v>
+        <v>2075000</v>
       </c>
       <c r="D41" s="16"/>
       <c r="E41" s="16"/>
@@ -3011,7 +3011,7 @@
       <c r="D43" s="16"/>
       <c r="E43" s="30" t="inlineStr">
         <is>
-          <t>16% de los activos declarados · no interviene en la proyección</t>
+          <t>11% de los activos declarados · no interviene en la proyección</t>
         </is>
       </c>
     </row>
@@ -3028,7 +3028,7 @@
     <row r="46">
       <c r="B46" s="16" t="inlineStr">
         <is>
-          <t>Rendimiento mínimo esperado</t>
+          <t>Rendimiento esperado</t>
         </is>
       </c>
       <c r="C46" s="24">
@@ -3234,7 +3234,7 @@
     <row r="63" ht="22" customHeight="1">
       <c r="B63" s="13" t="inlineStr">
         <is>
-          <t>Resultados de la proyección</t>
+          <t>Estrategia de flujo de caja por moneda</t>
         </is>
       </c>
       <c r="C63" s="13"/>
@@ -3244,717 +3244,737 @@
     <row r="64">
       <c r="B64" s="16" t="inlineStr">
         <is>
-          <t>Portafolio máximo proyectado</t>
-        </is>
-      </c>
-      <c r="C64" s="22">
-        <v>1111058</v>
+          <t>Rendimiento de la renta fija en colones (Costa Rica)</t>
+        </is>
+      </c>
+      <c r="C64" s="24">
+        <v>0.055999999999999994</v>
       </c>
       <c r="D64" s="16"/>
-      <c r="E64" s="16"/>
+      <c r="E64" s="30" t="inlineStr">
+        <is>
+          <t>Valores de la firma</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="B65" s="16" t="inlineStr">
         <is>
-          <t>Portafolio final nominal</t>
-        </is>
-      </c>
-      <c r="C65" s="22">
-        <v>0</v>
+          <t>Rendimiento de la renta fija en dólares</t>
+        </is>
+      </c>
+      <c r="C65" s="24">
+        <v>0.0546</v>
       </c>
       <c r="D65" s="16"/>
-      <c r="E65" s="16"/>
+      <c r="E65" s="30" t="inlineStr">
+        <is>
+          <t>Valores de la firma</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="B66" s="16" t="inlineStr">
         <is>
-          <t>Portafolio final en términos reales</t>
+          <t>Obligaciones netas en colones (US$ nominales, todo el horizonte)</t>
         </is>
       </c>
       <c r="C66" s="22">
-        <v>0</v>
+        <v>1802514</v>
       </c>
       <c r="D66" s="16"/>
-      <c r="E66" s="16"/>
+      <c r="E66" s="30" t="inlineStr">
+        <is>
+          <t>gastos − ingresos en colones, cada año que son positivos</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="B67" s="16" t="inlineStr">
         <is>
-          <t>Tasa de retiro inicial</t>
-        </is>
-      </c>
-      <c r="C67" s="24">
-        <v>0.028085118081586206</v>
+          <t>Obligaciones netas en dólares (US$ nominales, todo el horizonte)</t>
+        </is>
+      </c>
+      <c r="C67" s="22">
+        <v>4473591</v>
       </c>
       <c r="D67" s="16"/>
-      <c r="E67" s="16"/>
+      <c r="E67" s="30" t="inlineStr">
+        <is>
+          <t>gastos − ingresos en dólares, cada año que son positivos</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="B68" s="16" t="inlineStr">
         <is>
-          <t>Años de acumulación</t>
-        </is>
-      </c>
-      <c r="C68" s="32">
-        <v>14</v>
+          <t>Renta fija necesaria en colones (US$, valor presente)</t>
+        </is>
+      </c>
+      <c r="C68" s="22">
+        <v>282481</v>
       </c>
       <c r="D68" s="16"/>
-      <c r="E68" s="16"/>
+      <c r="E68" s="30" t="inlineStr">
+        <is>
+          <t>₡127 116 486 · Costa Rica · 113,0% del capital</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="B69" s="16" t="inlineStr">
         <is>
-          <t>Años de retiro</t>
-        </is>
-      </c>
-      <c r="C69" s="32">
-        <v>36</v>
+          <t>Renta fija necesaria en dólares (US$, valor presente)</t>
+        </is>
+      </c>
+      <c r="C69" s="22">
+        <v>1137057</v>
       </c>
       <c r="D69" s="16"/>
-      <c r="E69" s="16"/>
+      <c r="E69" s="30" t="inlineStr">
+        <is>
+          <t>454,8% del capital</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="B70" s="16" t="inlineStr">
         <is>
-          <t>Edad a la que se agota el portafolio</t>
-        </is>
-      </c>
-      <c r="C70" s="32">
-        <v>79</v>
+          <t>Renta fija necesaria total (US$)</t>
+        </is>
+      </c>
+      <c r="C70" s="22">
+        <v>1419538</v>
       </c>
       <c r="D70" s="16"/>
-      <c r="E70" s="16"/>
-    </row>
-    <row r="72" ht="22" customHeight="1">
-      <c r="B72" s="13" t="inlineStr">
-        <is>
-          <t>Caminos para alcanzar el objetivo</t>
-        </is>
-      </c>
-      <c r="C72" s="13"/>
-      <c r="D72" s="13"/>
-      <c r="E72" s="13"/>
-    </row>
-    <row r="73" ht="30" customHeight="1">
-      <c r="B73" s="21" t="inlineStr">
-        <is>
-          <t>Camino</t>
-        </is>
-      </c>
-      <c r="C73" s="21" t="inlineStr">
-        <is>
-          <t>Necesario</t>
-        </is>
-      </c>
-      <c r="D73" s="21"/>
-      <c r="E73" s="21" t="inlineStr">
-        <is>
-          <t>Hoy · lectura</t>
-        </is>
-      </c>
+      <c r="E70" s="30" t="inlineStr">
+        <is>
+          <t>567,8% del capital · supera el capital en US$1 169 538</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="16" t="inlineStr">
+        <is>
+          <t>Disponible para renta variable (US$)</t>
+        </is>
+      </c>
+      <c r="C71" s="22">
+        <v>0</v>
+      </c>
+      <c r="D71" s="16"/>
+      <c r="E71" s="30" t="inlineStr">
+        <is>
+          <t>0,0% del capital</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="16" t="inlineStr">
+        <is>
+          <t>Cartera sugerida: renta fija en colones (US$)</t>
+        </is>
+      </c>
+      <c r="C72" s="22">
+        <v>23631</v>
+      </c>
+      <c r="D72" s="16"/>
+      <c r="E72" s="30" t="inlineStr">
+        <is>
+          <t>la renta fija de la cartera, según las obligaciones de cada moneda</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="16" t="inlineStr">
+        <is>
+          <t>Cartera sugerida: renta fija en dólares (US$)</t>
+        </is>
+      </c>
+      <c r="C73" s="22">
+        <v>95119</v>
+      </c>
+      <c r="D73" s="16"/>
+      <c r="E73" s="16"/>
     </row>
     <row r="74">
       <c r="B74" s="16" t="inlineStr">
         <is>
-          <t>Mayor rendimiento del portafolio</t>
-        </is>
-      </c>
-      <c r="C74" s="22" t="inlineStr">
-        <is>
-          <t>7,9%</t>
-        </is>
-      </c>
+          <t>Lectura del flujo de caja</t>
+        </is>
+      </c>
+      <c r="C74" s="16"/>
       <c r="D74" s="16"/>
       <c r="E74" s="30" t="inlineStr">
         <is>
-          <t>Hoy 5,9% · Ninguna cartera modelo rinde lo necesario. (no basta por sí solo)</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="B75" s="16" t="inlineStr">
-        <is>
-          <t>Mayor capital inicial</t>
-        </is>
-      </c>
-      <c r="C75" s="22" t="inlineStr">
-        <is>
-          <t>$575 034</t>
-        </is>
-      </c>
-      <c r="D75" s="16"/>
-      <c r="E75" s="30" t="inlineStr">
-        <is>
-          <t>Hoy $250 000 · Aporte único hoy de $325 034.</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="B76" s="16" t="inlineStr">
-        <is>
-          <t>Aporte anual adicional al portafolio</t>
-        </is>
-      </c>
-      <c r="C76" s="22" t="inlineStr">
-        <is>
-          <t>$28 222 al año</t>
-        </is>
-      </c>
-      <c r="D76" s="16"/>
-      <c r="E76" s="30" t="inlineStr">
-        <is>
-          <t>Durante los 14 años de acumulación, en dólares de hoy (39% del ingreso anual).</t>
-        </is>
-      </c>
+          <t>Para cubrir sus obligaciones netas de todo el horizonte, el portafolio necesita $1,419,538 en renta fija: $282,481 en colones (Costa Rica, al 5,6%) y $1,137,057 en dólares (al 5,46%). Es más que el capital actual ($250,000): faltan $1,169,538, y no queda espacio para renta variable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="22" customHeight="1">
+      <c r="B76" s="13" t="inlineStr">
+        <is>
+          <t>Resultados de la proyección</t>
+        </is>
+      </c>
+      <c r="C76" s="13"/>
+      <c r="D76" s="13"/>
+      <c r="E76" s="13"/>
     </row>
     <row r="77">
       <c r="B77" s="16" t="inlineStr">
         <is>
-          <t>Menor gasto familiar</t>
-        </is>
-      </c>
-      <c r="C77" s="22" t="inlineStr">
-        <is>
-          <t>$4 643 al mes</t>
-        </is>
+          <t>Portafolio máximo proyectado</t>
+        </is>
+      </c>
+      <c r="C77" s="22">
+        <v>1111058</v>
       </c>
       <c r="D77" s="16"/>
-      <c r="E77" s="30" t="inlineStr">
-        <is>
-          <t>Hoy $5 500 al mes · Reducción de 16% en todos los años.</t>
-        </is>
-      </c>
+      <c r="E77" s="16"/>
     </row>
     <row r="78">
       <c r="B78" s="16" t="inlineStr">
         <is>
-          <t>Menores gastos extraordinarios</t>
-        </is>
-      </c>
-      <c r="C78" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Portafolio final nominal</t>
+        </is>
+      </c>
+      <c r="C78" s="22">
+        <v>0</v>
       </c>
       <c r="D78" s="16"/>
-      <c r="E78" s="30" t="inlineStr">
-        <is>
-          <t>Hoy $983 474 en total · Ni eliminándolos alcanza. (no basta por sí solo)</t>
-        </is>
-      </c>
+      <c r="E78" s="16"/>
     </row>
     <row r="79">
       <c r="B79" s="16" t="inlineStr">
         <is>
-          <t>Aporte mensual adicional a la pensión voluntaria</t>
-        </is>
-      </c>
-      <c r="C79" s="22" t="inlineStr">
-        <is>
-          <t>$2 172 al mes</t>
-        </is>
+          <t>Portafolio final en términos reales</t>
+        </is>
+      </c>
+      <c r="C79" s="22">
+        <v>0</v>
       </c>
       <c r="D79" s="16"/>
-      <c r="E79" s="30" t="inlineStr">
-        <is>
-          <t>Crece al 6,0% y se recibe al pensionarse, a los 65 años.</t>
-        </is>
-      </c>
+      <c r="E79" s="16"/>
     </row>
     <row r="80">
       <c r="B80" s="16" t="inlineStr">
         <is>
-          <t>Postergar la independencia financiera</t>
-        </is>
-      </c>
-      <c r="C80" s="22" t="inlineStr">
-        <is>
-          <t>66 años</t>
-        </is>
+          <t>Tasa de retiro inicial</t>
+        </is>
+      </c>
+      <c r="C80" s="24">
+        <v>0.028085118081586206</v>
       </c>
       <c r="D80" s="16"/>
-      <c r="E80" s="30" t="inlineStr">
-        <is>
-          <t>Hoy 60 años · 6 años más de ingreso por actividad y de aportes.</t>
-        </is>
-      </c>
+      <c r="E80" s="16"/>
     </row>
     <row r="81">
       <c r="B81" s="16" t="inlineStr">
         <is>
-          <t>Lectura</t>
-        </is>
-      </c>
-      <c r="C81" s="16"/>
+          <t>Años de acumulación</t>
+        </is>
+      </c>
+      <c r="C81" s="32">
+        <v>14</v>
+      </c>
       <c r="D81" s="16"/>
-      <c r="E81" s="30" t="inlineStr">
-        <is>
-          <t>Hay 5 caminos que alcanzan el objetivo cada uno por sí solo: mayor capital inicial, aporte anual adicional al portafolio, menor gasto familiar, aporte mensual adicional a la pensión voluntaria o postergar la independencia financiera. También pueden combinarse; combinados, cada uno exige un ajuste menor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="22" customHeight="1">
-      <c r="B83" s="13" t="inlineStr">
-        <is>
-          <t>Datos financieros declarados</t>
-        </is>
-      </c>
-      <c r="C83" s="13"/>
-      <c r="D83" s="13"/>
-      <c r="E83" s="13"/>
-    </row>
-    <row r="84">
-      <c r="B84" s="16" t="inlineStr">
-        <is>
-          <t>Ingreso total mensual</t>
-        </is>
-      </c>
-      <c r="C84" s="22">
-        <v>2700000</v>
-      </c>
-      <c r="D84" s="16"/>
-      <c r="E84" s="30" t="inlineStr">
-        <is>
-          <t>CRC</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="B85" s="16" t="inlineStr">
-        <is>
-          <t>Gasto familiar mensual</t>
-        </is>
-      </c>
-      <c r="C85" s="22">
-        <v>5500</v>
-      </c>
-      <c r="D85" s="16"/>
-      <c r="E85" s="30" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="B86" s="16" t="inlineStr">
-        <is>
-          <t>Capital inicial invertido</t>
-        </is>
-      </c>
-      <c r="C86" s="22">
-        <v>250000</v>
-      </c>
-      <c r="D86" s="16"/>
-      <c r="E86" s="30" t="inlineStr">
-        <is>
-          <t>USD</t>
+      <c r="E81" s="16"/>
+    </row>
+    <row r="82">
+      <c r="B82" s="16" t="inlineStr">
+        <is>
+          <t>Años de retiro</t>
+        </is>
+      </c>
+      <c r="C82" s="32">
+        <v>36</v>
+      </c>
+      <c r="D82" s="16"/>
+      <c r="E82" s="16"/>
+    </row>
+    <row r="83">
+      <c r="B83" s="16" t="inlineStr">
+        <is>
+          <t>Edad a la que se agota el portafolio</t>
+        </is>
+      </c>
+      <c r="C83" s="32">
+        <v>79</v>
+      </c>
+      <c r="D83" s="16"/>
+      <c r="E83" s="16"/>
+    </row>
+    <row r="85" ht="22" customHeight="1">
+      <c r="B85" s="13" t="inlineStr">
+        <is>
+          <t>Caminos para alcanzar el objetivo</t>
+        </is>
+      </c>
+      <c r="C85" s="13"/>
+      <c r="D85" s="13"/>
+      <c r="E85" s="13"/>
+    </row>
+    <row r="86" ht="30" customHeight="1">
+      <c r="B86" s="21" t="inlineStr">
+        <is>
+          <t>Camino</t>
+        </is>
+      </c>
+      <c r="C86" s="21" t="inlineStr">
+        <is>
+          <t>Necesario</t>
+        </is>
+      </c>
+      <c r="D86" s="21"/>
+      <c r="E86" s="21" t="inlineStr">
+        <is>
+          <t>Hoy · lectura</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="B87" s="16" t="inlineStr">
         <is>
-          <t>Gasto familiar por moneda</t>
-        </is>
-      </c>
-      <c r="C87" s="16"/>
+          <t>Mayor rendimiento del portafolio</t>
+        </is>
+      </c>
+      <c r="C87" s="22" t="inlineStr">
+        <is>
+          <t>7,9%</t>
+        </is>
+      </c>
       <c r="D87" s="16"/>
       <c r="E87" s="30" t="inlineStr">
         <is>
-          <t>30% en dólares · 70% en colones (cada parte con la inflación de su moneda)</t>
+          <t>Hoy 5,9% · Ninguna cartera modelo rinde lo necesario. (no basta por sí solo)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="B88" s="16" t="inlineStr">
         <is>
-          <t>Comentarios del cliente</t>
-        </is>
-      </c>
-      <c r="C88" s="16"/>
+          <t>Mayor capital inicial</t>
+        </is>
+      </c>
+      <c r="C88" s="22" t="inlineStr">
+        <is>
+          <t>$575 034</t>
+        </is>
+      </c>
       <c r="D88" s="16"/>
-      <c r="E88" s="16"/>
-    </row>
-    <row r="90" ht="22" customHeight="1">
-      <c r="B90" s="13" t="inlineStr">
-        <is>
-          <t>Retiro, pensión, fondos y flujos previstos</t>
-        </is>
-      </c>
-      <c r="C90" s="13"/>
-      <c r="D90" s="13"/>
-      <c r="E90" s="13"/>
+      <c r="E88" s="30" t="inlineStr">
+        <is>
+          <t>Hoy $250 000 · Aporte único hoy de $325 034.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" s="16" t="inlineStr">
+        <is>
+          <t>Aporte anual adicional al portafolio</t>
+        </is>
+      </c>
+      <c r="C89" s="22" t="inlineStr">
+        <is>
+          <t>$28 222 al año</t>
+        </is>
+      </c>
+      <c r="D89" s="16"/>
+      <c r="E89" s="30" t="inlineStr">
+        <is>
+          <t>Durante los 14 años de acumulación, en dólares de hoy (39% del ingreso anual).</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" s="16" t="inlineStr">
+        <is>
+          <t>Menor gasto familiar</t>
+        </is>
+      </c>
+      <c r="C90" s="22" t="inlineStr">
+        <is>
+          <t>$4 643 al mes</t>
+        </is>
+      </c>
+      <c r="D90" s="16"/>
+      <c r="E90" s="30" t="inlineStr">
+        <is>
+          <t>Hoy $5 500 al mes · Reducción de 16% en todos los años.</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="B91" s="16" t="inlineStr">
         <is>
-          <t>Gasto en el retiro (% del gasto actual)</t>
-        </is>
-      </c>
-      <c r="C91" s="24">
-        <v>1</v>
+          <t>Menores gastos extraordinarios</t>
+        </is>
+      </c>
+      <c r="C91" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="D91" s="16"/>
-      <c r="E91" s="16"/>
+      <c r="E91" s="30" t="inlineStr">
+        <is>
+          <t>Hoy $983 474 en total · Ni eliminándolos alcanza. (no basta por sí solo)</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="B92" s="16" t="inlineStr">
         <is>
-          <t>Régimen de pensión</t>
-        </is>
-      </c>
-      <c r="C92" s="16"/>
+          <t>Aporte mensual adicional a la pensión voluntaria</t>
+        </is>
+      </c>
+      <c r="C92" s="22" t="inlineStr">
+        <is>
+          <t>$2 172 al mes</t>
+        </is>
+      </c>
       <c r="D92" s="16"/>
       <c r="E92" s="30" t="inlineStr">
         <is>
-          <t>Magisterio Nacional</t>
+          <t>Crece al 6,0% y se recibe al pensionarse, a los 65 años.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="B93" s="16" t="inlineStr">
         <is>
-          <t>Pensión mensual estimada (valor de hoy)</t>
-        </is>
-      </c>
-      <c r="C93" s="22">
-        <v>800000</v>
+          <t>Postergar la independencia financiera</t>
+        </is>
+      </c>
+      <c r="C93" s="22" t="inlineStr">
+        <is>
+          <t>66 años</t>
+        </is>
       </c>
       <c r="D93" s="16"/>
       <c r="E93" s="30" t="inlineStr">
         <is>
-          <t>CRC</t>
+          <t>Hoy 60 años · 6 años más de ingreso por actividad y de aportes.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="B94" s="16" t="inlineStr">
         <is>
-          <t>Edad de inicio de la pensión</t>
-        </is>
-      </c>
-      <c r="C94" s="32">
-        <v>65</v>
-      </c>
+          <t>Lectura</t>
+        </is>
+      </c>
+      <c r="C94" s="16"/>
       <c r="D94" s="16"/>
-      <c r="E94" s="16"/>
+      <c r="E94" s="30" t="inlineStr">
+        <is>
+          <t>Hay 5 caminos que alcanzan el objetivo cada uno por sí solo: mayor capital inicial, aporte anual adicional al portafolio, menor gasto familiar, aporte mensual adicional a la pensión voluntaria o postergar la independencia financiera. También pueden combinarse; combinados, cada uno exige un ajuste menor.</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="B95" s="16" t="inlineStr">
         <is>
-          <t>Otros ingresos recurrentes mensuales (valor de hoy)</t>
-        </is>
-      </c>
-      <c r="C95" s="22">
-        <v>500000</v>
-      </c>
+          <t>Procedimiento · Regla general</t>
+        </is>
+      </c>
+      <c r="C95" s="16"/>
       <c r="D95" s="16"/>
       <c r="E95" s="30" t="inlineStr">
         <is>
-          <t>CRC · desde 2030 · durante toda la proyección</t>
+          <t>Cada valor necesario se obtiene cambiando una sola variable, con todo lo demás igual, y recalculando la proyección completa. Una búsqueda binaria (40 iteraciones) encuentra el valor en que el plan pasa de alcanzar a no alcanzar el objetivo. El objetivo es que no quede gasto sin cubrir en ningún año y que el saldo final del portafolio, en dólares de hoy, sea al menos la herencia.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="B96" s="16" t="inlineStr">
         <is>
-          <t>ROP: saldo actual</t>
-        </is>
-      </c>
-      <c r="C96" s="22">
-        <v>12000000</v>
-      </c>
+          <t>Procedimiento · Herencia</t>
+        </is>
+      </c>
+      <c r="C96" s="16"/>
       <c r="D96" s="16"/>
       <c r="E96" s="30" t="inlineStr">
         <is>
-          <t>CRC · pensión: retiro programado</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="B97" s="16" t="inlineStr">
-        <is>
-          <t>ROP: aporte mensual</t>
-        </is>
-      </c>
-      <c r="C97" s="16"/>
-      <c r="D97" s="16"/>
-      <c r="E97" s="30" t="inlineStr">
-        <is>
-          <t>No lo indicó: se estima con el salario</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="B98" s="16" t="inlineStr">
-        <is>
-          <t>FCL: saldo actual</t>
-        </is>
-      </c>
-      <c r="C98" s="22">
-        <v>12000000</v>
-      </c>
-      <c r="D98" s="16"/>
-      <c r="E98" s="30" t="inlineStr">
-        <is>
-          <t>CRC · traslado al momento del retiro</t>
-        </is>
-      </c>
+          <t>Está en términos reales (dólares de hoy). Saldo final nominal en 2075: $0. En dólares de hoy = saldo nominal ÷ (1 + inflación internacional)^años = $0 ÷ (1 + 3,9%)^49,25 = $0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="22" customHeight="1">
+      <c r="B98" s="13" t="inlineStr">
+        <is>
+          <t>Datos financieros declarados</t>
+        </is>
+      </c>
+      <c r="C98" s="13"/>
+      <c r="D98" s="13"/>
+      <c r="E98" s="13"/>
     </row>
     <row r="99">
       <c r="B99" s="16" t="inlineStr">
         <is>
-          <t>FCL: aporte mensual</t>
-        </is>
-      </c>
-      <c r="C99" s="16"/>
+          <t>Ingreso total mensual</t>
+        </is>
+      </c>
+      <c r="C99" s="22">
+        <v>2700000</v>
+      </c>
       <c r="D99" s="16"/>
       <c r="E99" s="30" t="inlineStr">
         <is>
-          <t>No lo indicó: se estima con el salario</t>
+          <t>CRC</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="B100" s="16" t="inlineStr">
         <is>
-          <t>Pensión voluntaria: saldo actual</t>
+          <t>Gasto familiar mensual</t>
         </is>
       </c>
       <c r="C100" s="22">
-        <v>12000000</v>
+        <v>5500</v>
       </c>
       <c r="D100" s="16"/>
       <c r="E100" s="30" t="inlineStr">
         <is>
-          <t>CRC · pensión mensual desde la edad de pensión</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="B101" s="16" t="inlineStr">
         <is>
-          <t>Pensión voluntaria: aporte mensual</t>
+          <t>Capital inicial invertido</t>
         </is>
       </c>
       <c r="C101" s="22">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="D101" s="16"/>
       <c r="E101" s="30" t="inlineStr">
         <is>
-          <t>CRC</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="B102" s="16" t="inlineStr">
         <is>
-          <t>Ingreso extraordinario 1: Bono por antigüedad (valor de hoy)</t>
-        </is>
-      </c>
-      <c r="C102" s="22">
-        <v>40000</v>
-      </c>
+          <t>Gasto familiar por moneda</t>
+        </is>
+      </c>
+      <c r="C102" s="16"/>
       <c r="D102" s="16"/>
       <c r="E102" s="30" t="inlineStr">
         <is>
-          <t>USD · año 2028</t>
+          <t>30% en dólares · 70% en colones (cada parte con la inflación de su moneda)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="B103" s="16" t="inlineStr">
         <is>
-          <t>Ingreso extraordinario 2: Herencia esperada (valor de hoy)</t>
-        </is>
-      </c>
-      <c r="C103" s="22">
-        <v>120000</v>
-      </c>
+          <t>Comentarios del cliente</t>
+        </is>
+      </c>
+      <c r="C103" s="16"/>
       <c r="D103" s="16"/>
-      <c r="E103" s="30" t="inlineStr">
-        <is>
-          <t>USD · año 2032</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="B104" s="16" t="inlineStr">
-        <is>
-          <t>Desinversión: Venta del inmueble 1</t>
-        </is>
-      </c>
-      <c r="C104" s="22">
-        <v>180000</v>
-      </c>
-      <c r="D104" s="16"/>
-      <c r="E104" s="30" t="inlineStr">
-        <is>
-          <t>USD · año 2031 · monto que entra al portafolio</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="B105" s="16" t="inlineStr">
-        <is>
-          <t>Desinversión: Venta de un lote</t>
-        </is>
-      </c>
-      <c r="C105" s="22">
-        <v>150000</v>
-      </c>
-      <c r="D105" s="16"/>
-      <c r="E105" s="30" t="inlineStr">
-        <is>
-          <t>USD · año 2033 · monto que entra al portafolio</t>
-        </is>
-      </c>
+      <c r="E103" s="16"/>
+    </row>
+    <row r="105" ht="22" customHeight="1">
+      <c r="B105" s="13" t="inlineStr">
+        <is>
+          <t>Retiro, pensión, fondos y flujos previstos</t>
+        </is>
+      </c>
+      <c r="C105" s="13"/>
+      <c r="D105" s="13"/>
+      <c r="E105" s="13"/>
     </row>
     <row r="106">
       <c r="B106" s="16" t="inlineStr">
         <is>
-          <t>Gasto de dependiente 1 (valor de hoy, por año)</t>
-        </is>
-      </c>
-      <c r="C106" s="22">
-        <v>12000</v>
+          <t>Gasto en el retiro (% del gasto actual)</t>
+        </is>
+      </c>
+      <c r="C106" s="24">
+        <v>1</v>
       </c>
       <c r="D106" s="16"/>
-      <c r="E106" s="30" t="inlineStr">
-        <is>
-          <t>USD · Cónyuge o pareja · salud · desde 2030 por 5 años</t>
-        </is>
-      </c>
+      <c r="E106" s="16"/>
     </row>
     <row r="107">
       <c r="B107" s="16" t="inlineStr">
         <is>
-          <t>Meta 1 (valor de hoy)</t>
-        </is>
-      </c>
-      <c r="C107" s="22">
-        <v>40000</v>
-      </c>
+          <t>Régimen de pensión</t>
+        </is>
+      </c>
+      <c r="C107" s="16"/>
       <c r="D107" s="16"/>
       <c r="E107" s="30" t="inlineStr">
         <is>
-          <t>USD · Vivienda o propiedad · año 2031 · deseable · salida del portafolio</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="22" customHeight="1">
-      <c r="B109" s="13" t="inlineStr">
-        <is>
-          <t>Perfil de permanencia y aportes</t>
-        </is>
-      </c>
-      <c r="C109" s="13"/>
-      <c r="D109" s="13"/>
-      <c r="E109" s="13"/>
+          <t>Magisterio Nacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" s="16" t="inlineStr">
+        <is>
+          <t>Pensión mensual estimada (valor de hoy)</t>
+        </is>
+      </c>
+      <c r="C108" s="22">
+        <v>800000</v>
+      </c>
+      <c r="D108" s="16"/>
+      <c r="E108" s="30" t="inlineStr">
+        <is>
+          <t>CRC</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" s="16" t="inlineStr">
+        <is>
+          <t>Edad de inicio de la pensión</t>
+        </is>
+      </c>
+      <c r="C109" s="32">
+        <v>65</v>
+      </c>
+      <c r="D109" s="16"/>
+      <c r="E109" s="16"/>
     </row>
     <row r="110">
       <c r="B110" s="16" t="inlineStr">
         <is>
-          <t>Retiro: Retiro del portafolio (2031, valor de hoy)</t>
+          <t>Otros ingresos recurrentes mensuales (valor de hoy)</t>
         </is>
       </c>
       <c r="C110" s="22">
-        <v>50000</v>
+        <v>500000</v>
       </c>
       <c r="D110" s="16"/>
       <c r="E110" s="30" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>CRC · desde 2030 · durante toda la proyección</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="B111" s="16" t="inlineStr">
         <is>
-          <t>Destino del patrimonio</t>
-        </is>
-      </c>
-      <c r="C111" s="16"/>
+          <t>ROP: saldo actual</t>
+        </is>
+      </c>
+      <c r="C111" s="22">
+        <v>12000000</v>
+      </c>
       <c r="D111" s="16"/>
       <c r="E111" s="30" t="inlineStr">
         <is>
-          <t>Utilizarlo durante su vida</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="22" customHeight="1">
-      <c r="B113" s="13" t="inlineStr">
-        <is>
-          <t>Hogar, patrimonio y protección</t>
-        </is>
-      </c>
-      <c r="C113" s="13"/>
-      <c r="D113" s="13"/>
-      <c r="E113" s="13"/>
+          <t>CRC · pensión: retiro programado</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" s="16" t="inlineStr">
+        <is>
+          <t>ROP: aporte mensual</t>
+        </is>
+      </c>
+      <c r="C112" s="16"/>
+      <c r="D112" s="16"/>
+      <c r="E112" s="30" t="inlineStr">
+        <is>
+          <t>No lo indicó: se estima con el salario</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" s="16" t="inlineStr">
+        <is>
+          <t>FCL: saldo actual</t>
+        </is>
+      </c>
+      <c r="C113" s="22">
+        <v>12000000</v>
+      </c>
+      <c r="D113" s="16"/>
+      <c r="E113" s="30" t="inlineStr">
+        <is>
+          <t>CRC · traslado al momento del retiro</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="B114" s="16" t="inlineStr">
         <is>
-          <t>Hijos</t>
+          <t>FCL: aporte mensual</t>
         </is>
       </c>
       <c r="C114" s="16"/>
       <c r="D114" s="16"/>
       <c r="E114" s="30" t="inlineStr">
         <is>
-          <t>No tiene</t>
+          <t>No lo indicó: se estima con el salario</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="B115" s="16" t="inlineStr">
         <is>
-          <t>Otros dependientes</t>
-        </is>
-      </c>
-      <c r="C115" s="32">
-        <v>1</v>
+          <t>Pensión voluntaria: saldo actual</t>
+        </is>
+      </c>
+      <c r="C115" s="22">
+        <v>12000000</v>
       </c>
       <c r="D115" s="16"/>
       <c r="E115" s="30" t="inlineStr">
         <is>
-          <t>otros 1</t>
+          <t>CRC · pensión mensual desde la edad de pensión</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="B116" s="16" t="inlineStr">
         <is>
-          <t>Fuentes del ingreso</t>
-        </is>
-      </c>
-      <c r="C116" s="16"/>
+          <t>Pensión voluntaria: aporte mensual</t>
+        </is>
+      </c>
+      <c r="C116" s="22">
+        <v>150000</v>
+      </c>
       <c r="D116" s="16"/>
       <c r="E116" s="30" t="inlineStr">
         <is>
-          <t>Salario · Empresa propia</t>
+          <t>CRC</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="B117" s="16" t="inlineStr">
         <is>
-          <t>Vivienda principal</t>
-        </is>
-      </c>
-      <c r="C117" s="16"/>
+          <t>Ingreso extraordinario 1: Bono por antigüedad (valor de hoy)</t>
+        </is>
+      </c>
+      <c r="C117" s="22">
+        <v>40000</v>
+      </c>
       <c r="D117" s="16"/>
       <c r="E117" s="30" t="inlineStr">
         <is>
-          <t>Propia, con hipoteca</t>
+          <t>USD · año 2028</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="B118" s="16" t="inlineStr">
         <is>
-          <t>Saldo de la hipoteca</t>
+          <t>Ingreso extraordinario 2: Herencia esperada (valor de hoy)</t>
         </is>
       </c>
       <c r="C118" s="22">
@@ -3963,236 +3983,222 @@
       <c r="D118" s="16"/>
       <c r="E118" s="30" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>USD · año 2032</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="B119" s="16" t="inlineStr">
         <is>
-          <t>Cuota mensual de la hipoteca</t>
+          <t>Desinversión: Venta del inmueble 1</t>
         </is>
       </c>
       <c r="C119" s="22">
-        <v>1200</v>
+        <v>180000</v>
       </c>
       <c r="D119" s="16"/>
       <c r="E119" s="30" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>USD · año 2031 · monto que entra al portafolio</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="B120" s="16" t="inlineStr">
         <is>
-          <t>Tasa de interés anual de la hipoteca</t>
-        </is>
-      </c>
-      <c r="C120" s="24">
-        <v>0.085</v>
+          <t>Desinversión: Venta de un lote</t>
+        </is>
+      </c>
+      <c r="C120" s="22">
+        <v>150000</v>
       </c>
       <c r="D120" s="16"/>
-      <c r="E120" s="16"/>
+      <c r="E120" s="30" t="inlineStr">
+        <is>
+          <t>USD · año 2033 · monto que entra al portafolio</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="B121" s="16" t="inlineStr">
         <is>
-          <t>Plazo restante de la hipoteca (años)</t>
-        </is>
-      </c>
-      <c r="C121" s="32">
-        <v>15</v>
+          <t>Gasto de dependiente 1 (valor de hoy, por año)</t>
+        </is>
+      </c>
+      <c r="C121" s="22">
+        <v>12000</v>
       </c>
       <c r="D121" s="16"/>
-      <c r="E121" s="16"/>
+      <c r="E121" s="30" t="inlineStr">
+        <is>
+          <t>USD · Cónyuge o pareja · salud · desde 2030 por 5 años</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="B122" s="16" t="inlineStr">
         <is>
-          <t>Apartamento en Santa Ana (valor)</t>
+          <t>Meta 1 (valor de hoy)</t>
         </is>
       </c>
       <c r="C122" s="22">
-        <v>180000</v>
+        <v>40000</v>
       </c>
       <c r="D122" s="16"/>
       <c r="E122" s="30" t="inlineStr">
         <is>
-          <t>USD · renta neta 1 100 USD · deuda 0 USD · estima venderlo en 2031 · invertiría todo aquí</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="B123" s="16" t="inlineStr">
-        <is>
-          <t>Empresa 1: EMPRESA (valor estimado, 100%)</t>
-        </is>
-      </c>
-      <c r="C123" s="22">
-        <v>900000</v>
-      </c>
-      <c r="D123" s="16"/>
-      <c r="E123" s="30" t="inlineStr">
-        <is>
-          <t>USD · participación 100% · estima traspasarla en 10 años</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="B124" s="16" t="inlineStr">
-        <is>
-          <t>Capital privado: valor estimado (100%)</t>
-        </is>
-      </c>
-      <c r="C124" s="22">
-        <v>800000</v>
-      </c>
-      <c r="D124" s="16"/>
-      <c r="E124" s="30" t="inlineStr">
-        <is>
-          <t>USD · participación 15%</t>
-        </is>
-      </c>
+          <t>USD · Vivienda o propiedad · año 2031 · deseable · salida del portafolio</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="22" customHeight="1">
+      <c r="B124" s="13" t="inlineStr">
+        <is>
+          <t>Perfil de permanencia y aportes</t>
+        </is>
+      </c>
+      <c r="C124" s="13"/>
+      <c r="D124" s="13"/>
+      <c r="E124" s="13"/>
     </row>
     <row r="125">
       <c r="B125" s="16" t="inlineStr">
         <is>
-          <t>Posee estructuras jurídicas</t>
-        </is>
-      </c>
-      <c r="C125" s="16"/>
+          <t>Retiro: Retiro del portafolio (2031, valor de hoy)</t>
+        </is>
+      </c>
+      <c r="C125" s="22">
+        <v>50000</v>
+      </c>
       <c r="D125" s="16"/>
       <c r="E125" s="30" t="inlineStr">
         <is>
-          <t>No indicó</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="B126" s="16" t="inlineStr">
         <is>
-          <t>Deuda 1: Préstamo personal</t>
-        </is>
-      </c>
-      <c r="C126" s="22">
-        <v>5400000</v>
-      </c>
+          <t>Destino del patrimonio</t>
+        </is>
+      </c>
+      <c r="C126" s="16"/>
       <c r="D126" s="16"/>
       <c r="E126" s="30" t="inlineStr">
         <is>
-          <t>CRC · cuota 157 500 CRC al mes · tasa 11% · hasta 2029</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="B127" s="16" t="inlineStr">
-        <is>
-          <t>Deuda 2: Tarjeta de crédito</t>
-        </is>
-      </c>
-      <c r="C127" s="22">
-        <v>3000</v>
-      </c>
-      <c r="D127" s="16"/>
-      <c r="E127" s="30" t="inlineStr">
-        <is>
-          <t>USD · cuota 150 USD al mes · tasa 32% · hasta 2027</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="B128" s="16" t="inlineStr">
-        <is>
-          <t>Donaciones al año (valor de hoy)</t>
-        </is>
-      </c>
-      <c r="C128" s="22">
-        <v>3000</v>
-      </c>
-      <c r="D128" s="16"/>
-      <c r="E128" s="30" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
+          <t>Utilizarlo durante su vida</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="22" customHeight="1">
+      <c r="B128" s="13" t="inlineStr">
+        <is>
+          <t>Hogar, patrimonio y protección</t>
+        </is>
+      </c>
+      <c r="C128" s="13"/>
+      <c r="D128" s="13"/>
+      <c r="E128" s="13"/>
     </row>
     <row r="129">
       <c r="B129" s="16" t="inlineStr">
         <is>
-          <t>Gasto extraordinario 1: Seguro y marchamo de vehículos</t>
-        </is>
-      </c>
-      <c r="C129" s="22">
-        <v>6000</v>
-      </c>
+          <t>Hijos</t>
+        </is>
+      </c>
+      <c r="C129" s="16"/>
       <c r="D129" s="16"/>
       <c r="E129" s="30" t="inlineStr">
         <is>
-          <t>USD de hoy · cada año desde 2027</t>
+          <t>No tiene</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="B130" s="16" t="inlineStr">
         <is>
-          <t>Gasto extraordinario 2: Remodelación de la casa</t>
-        </is>
-      </c>
-      <c r="C130" s="22">
-        <v>15750000</v>
+          <t>Otros dependientes</t>
+        </is>
+      </c>
+      <c r="C130" s="32">
+        <v>1</v>
       </c>
       <c r="D130" s="16"/>
       <c r="E130" s="30" t="inlineStr">
         <is>
-          <t>CRC de hoy · en 2030</t>
+          <t>otros 1</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="B131" s="16" t="inlineStr">
         <is>
-          <t>Seguros vigentes</t>
+          <t>Fuentes del ingreso</t>
         </is>
       </c>
       <c r="C131" s="16"/>
       <c r="D131" s="16"/>
       <c r="E131" s="30" t="inlineStr">
         <is>
-          <t>Ninguno</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="22" customHeight="1">
-      <c r="B133" s="13" t="inlineStr">
-        <is>
-          <t>Supuestos aplicados</t>
-        </is>
-      </c>
-      <c r="C133" s="13"/>
-      <c r="D133" s="13"/>
-      <c r="E133" s="13"/>
+          <t>Salario · Empresa propia</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" s="16" t="inlineStr">
+        <is>
+          <t>Vivienda principal</t>
+        </is>
+      </c>
+      <c r="C132" s="16"/>
+      <c r="D132" s="16"/>
+      <c r="E132" s="30" t="inlineStr">
+        <is>
+          <t>Propia, con hipoteca</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" s="16" t="inlineStr">
+        <is>
+          <t>Saldo de la hipoteca</t>
+        </is>
+      </c>
+      <c r="C133" s="22">
+        <v>120000</v>
+      </c>
+      <c r="D133" s="16"/>
+      <c r="E133" s="30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="B134" s="16" t="inlineStr">
         <is>
-          <t>Tipo de cambio ₡/US$</t>
+          <t>Cuota mensual de la hipoteca</t>
         </is>
       </c>
       <c r="C134" s="22">
-        <v>450</v>
+        <v>1200</v>
       </c>
       <c r="D134" s="16"/>
-      <c r="E134" s="16"/>
+      <c r="E134" s="30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="B135" s="16" t="inlineStr">
         <is>
-          <t>Inflación local (Costa Rica)</t>
+          <t>Tasa de interés anual de la hipoteca</t>
         </is>
       </c>
       <c r="C135" s="24">
-        <v>0.039</v>
+        <v>0.085</v>
       </c>
       <c r="D135" s="16"/>
       <c r="E135" s="16"/>
@@ -4200,11 +4206,11 @@
     <row r="136">
       <c r="B136" s="16" t="inlineStr">
         <is>
-          <t>Inflación internacional (EE. UU.)</t>
-        </is>
-      </c>
-      <c r="C136" s="24">
-        <v>0.039</v>
+          <t>Plazo restante de la hipoteca (años)</t>
+        </is>
+      </c>
+      <c r="C136" s="32">
+        <v>15</v>
       </c>
       <c r="D136" s="16"/>
       <c r="E136" s="16"/>
@@ -4212,209 +4218,436 @@
     <row r="137">
       <c r="B137" s="16" t="inlineStr">
         <is>
-          <t>Inflación de la pensión del IVM</t>
-        </is>
-      </c>
-      <c r="C137" s="24">
-        <v>0.01</v>
+          <t>Apartamento en Santa Ana (valor)</t>
+        </is>
+      </c>
+      <c r="C137" s="22">
+        <v>180000</v>
       </c>
       <c r="D137" s="16"/>
-      <c r="E137" s="16"/>
+      <c r="E137" s="30" t="inlineStr">
+        <is>
+          <t>USD · renta neta 1 100 USD · deuda 0 USD · estima venderlo en 2031 · invertiría todo aquí</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="B138" s="16" t="inlineStr">
         <is>
-          <t>Inflación del ROP</t>
-        </is>
-      </c>
-      <c r="C138" s="24">
-        <v>0.039</v>
+          <t>Empresa 1: EMPRESA (valor estimado, 100%)</t>
+        </is>
+      </c>
+      <c r="C138" s="22">
+        <v>900000</v>
       </c>
       <c r="D138" s="16"/>
-      <c r="E138" s="16"/>
+      <c r="E138" s="30" t="inlineStr">
+        <is>
+          <t>USD · participación 100% · estima traspasarla en 10 años</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="B139" s="16" t="inlineStr">
         <is>
-          <t>Inflación de la pensión voluntaria</t>
-        </is>
-      </c>
-      <c r="C139" s="24">
-        <v>0.039</v>
+          <t>Capital privado: monto total invertido</t>
+        </is>
+      </c>
+      <c r="C139" s="22">
+        <v>800000</v>
       </c>
       <c r="D139" s="16"/>
-      <c r="E139" s="16"/>
+      <c r="E139" s="30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="B140" s="16" t="inlineStr">
         <is>
-          <t>Año de inicio</t>
-        </is>
-      </c>
-      <c r="C140" s="32">
-        <v>2026</v>
-      </c>
+          <t>Posee estructuras jurídicas</t>
+        </is>
+      </c>
+      <c r="C140" s="16"/>
       <c r="D140" s="16"/>
-      <c r="E140" s="16"/>
+      <c r="E140" s="30" t="inlineStr">
+        <is>
+          <t>No indicó</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="B141" s="16" t="inlineStr">
         <is>
-          <t>Edad final de la proyección</t>
-        </is>
-      </c>
-      <c r="C141" s="32">
-        <v>95</v>
+          <t>Deuda 1: Préstamo personal</t>
+        </is>
+      </c>
+      <c r="C141" s="22">
+        <v>5400000</v>
       </c>
       <c r="D141" s="16"/>
-      <c r="E141" s="16"/>
+      <c r="E141" s="30" t="inlineStr">
+        <is>
+          <t>CRC · cuota 157 500 CRC al mes · tasa 11% · hasta 2029</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="B142" s="16" t="inlineStr">
         <is>
-          <t>Rendimiento de los fondos de pensión</t>
-        </is>
-      </c>
-      <c r="C142" s="24">
-        <v>0.06</v>
+          <t>Deuda 2: Tarjeta de crédito</t>
+        </is>
+      </c>
+      <c r="C142" s="22">
+        <v>3000</v>
       </c>
       <c r="D142" s="16"/>
-      <c r="E142" s="16"/>
+      <c r="E142" s="30" t="inlineStr">
+        <is>
+          <t>USD · cuota 150 USD al mes · tasa 32% · hasta 2027</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="B143" s="16" t="inlineStr">
         <is>
-          <t>Aporte al ROP (% del salario, estimado)</t>
-        </is>
-      </c>
-      <c r="C143" s="24">
-        <v>0.0425</v>
+          <t>Donaciones al año (valor de hoy)</t>
+        </is>
+      </c>
+      <c r="C143" s="22">
+        <v>3000</v>
       </c>
       <c r="D143" s="16"/>
-      <c r="E143" s="16"/>
+      <c r="E143" s="30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="B144" s="16" t="inlineStr">
         <is>
-          <t>Aporte al FCL (% del salario, estimado)</t>
-        </is>
-      </c>
-      <c r="C144" s="24">
-        <v>0.015</v>
+          <t>Gasto extraordinario 1: Seguro y marchamo de vehículos</t>
+        </is>
+      </c>
+      <c r="C144" s="22">
+        <v>6000</v>
       </c>
       <c r="D144" s="16"/>
-      <c r="E144" s="16"/>
+      <c r="E144" s="30" t="inlineStr">
+        <is>
+          <t>USD de hoy · cada año desde 2027</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="B145" s="16" t="inlineStr">
         <is>
-          <t>Expectativa de vida (renta temporal)</t>
-        </is>
-      </c>
-      <c r="C145" s="16"/>
+          <t>Gasto extraordinario 2: Remodelación de la casa</t>
+        </is>
+      </c>
+      <c r="C145" s="22">
+        <v>15750000</v>
+      </c>
       <c r="D145" s="16"/>
       <c r="E145" s="30" t="inlineStr">
         <is>
-          <t>N/A · su ROP no es renta temporal</t>
+          <t>CRC de hoy · en 2030</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="B146" s="16" t="inlineStr">
         <is>
-          <t>Edad final del retiro programado</t>
-        </is>
-      </c>
-      <c r="C146" s="32">
-        <v>100</v>
-      </c>
+          <t>Seguros vigentes</t>
+        </is>
+      </c>
+      <c r="C146" s="16"/>
       <c r="D146" s="16"/>
-      <c r="E146" s="16"/>
-    </row>
-    <row r="147">
-      <c r="B147" s="16" t="inlineStr">
-        <is>
-          <t>Edad de independencia financiera</t>
-        </is>
-      </c>
-      <c r="C147" s="16"/>
-      <c r="D147" s="16"/>
-      <c r="E147" s="30" t="inlineStr">
-        <is>
-          <t>60 años · dato del cuestionario</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="B148" s="16" t="inlineStr">
-        <is>
-          <t>Gasto en el retiro</t>
-        </is>
-      </c>
-      <c r="C148" s="16"/>
-      <c r="D148" s="16"/>
-      <c r="E148" s="30" t="inlineStr">
-        <is>
-          <t>100% del gasto actual · dato del cuestionario</t>
-        </is>
-      </c>
+      <c r="E146" s="30" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="22" customHeight="1">
+      <c r="B148" s="13" t="inlineStr">
+        <is>
+          <t>Supuestos aplicados</t>
+        </is>
+      </c>
+      <c r="C148" s="13"/>
+      <c r="D148" s="13"/>
+      <c r="E148" s="13"/>
     </row>
     <row r="149">
       <c r="B149" s="16" t="inlineStr">
         <is>
-          <t>Edad de inicio de la pensión</t>
-        </is>
-      </c>
-      <c r="C149" s="16"/>
+          <t>Tipo de cambio ₡/US$</t>
+        </is>
+      </c>
+      <c r="C149" s="22">
+        <v>450</v>
+      </c>
       <c r="D149" s="16"/>
-      <c r="E149" s="30" t="inlineStr">
-        <is>
-          <t>65 años · dato del cuestionario</t>
-        </is>
-      </c>
+      <c r="E149" s="16"/>
     </row>
     <row r="150">
       <c r="B150" s="16" t="inlineStr">
         <is>
-          <t>Modalidad del ROP</t>
-        </is>
-      </c>
-      <c r="C150" s="16"/>
+          <t>Inflación local (Costa Rica)</t>
+        </is>
+      </c>
+      <c r="C150" s="24">
+        <v>0.039</v>
+      </c>
       <c r="D150" s="16"/>
-      <c r="E150" s="30" t="inlineStr">
-        <is>
-          <t>Retiro programado · dato del cuestionario</t>
-        </is>
-      </c>
+      <c r="E150" s="16"/>
     </row>
     <row r="151">
       <c r="B151" s="16" t="inlineStr">
         <is>
+          <t>Inflación internacional (EE. UU.)</t>
+        </is>
+      </c>
+      <c r="C151" s="24">
+        <v>0.039</v>
+      </c>
+      <c r="D151" s="16"/>
+      <c r="E151" s="16"/>
+    </row>
+    <row r="152">
+      <c r="B152" s="16" t="inlineStr">
+        <is>
+          <t>Inflación de la pensión del IVM</t>
+        </is>
+      </c>
+      <c r="C152" s="24">
+        <v>0.01</v>
+      </c>
+      <c r="D152" s="16"/>
+      <c r="E152" s="16"/>
+    </row>
+    <row r="153">
+      <c r="B153" s="16" t="inlineStr">
+        <is>
+          <t>Inflación del ROP</t>
+        </is>
+      </c>
+      <c r="C153" s="24">
+        <v>0.039</v>
+      </c>
+      <c r="D153" s="16"/>
+      <c r="E153" s="16"/>
+    </row>
+    <row r="154">
+      <c r="B154" s="16" t="inlineStr">
+        <is>
+          <t>Inflación de la pensión voluntaria</t>
+        </is>
+      </c>
+      <c r="C154" s="24">
+        <v>0.039</v>
+      </c>
+      <c r="D154" s="16"/>
+      <c r="E154" s="16"/>
+    </row>
+    <row r="155">
+      <c r="B155" s="16" t="inlineStr">
+        <is>
+          <t>Año de inicio</t>
+        </is>
+      </c>
+      <c r="C155" s="32">
+        <v>2026</v>
+      </c>
+      <c r="D155" s="16"/>
+      <c r="E155" s="16"/>
+    </row>
+    <row r="156">
+      <c r="B156" s="16" t="inlineStr">
+        <is>
+          <t>Edad final de la proyección</t>
+        </is>
+      </c>
+      <c r="C156" s="32">
+        <v>95</v>
+      </c>
+      <c r="D156" s="16"/>
+      <c r="E156" s="16"/>
+    </row>
+    <row r="157">
+      <c r="B157" s="16" t="inlineStr">
+        <is>
+          <t>Rendimiento de los fondos de pensión</t>
+        </is>
+      </c>
+      <c r="C157" s="24">
+        <v>0.06</v>
+      </c>
+      <c r="D157" s="16"/>
+      <c r="E157" s="16"/>
+    </row>
+    <row r="158">
+      <c r="B158" s="16" t="inlineStr">
+        <is>
+          <t>Aporte al ROP (% del salario, estimado)</t>
+        </is>
+      </c>
+      <c r="C158" s="24">
+        <v>0.0425</v>
+      </c>
+      <c r="D158" s="16"/>
+      <c r="E158" s="16"/>
+    </row>
+    <row r="159">
+      <c r="B159" s="16" t="inlineStr">
+        <is>
+          <t>Aporte al FCL (% del salario, estimado)</t>
+        </is>
+      </c>
+      <c r="C159" s="24">
+        <v>0.015</v>
+      </c>
+      <c r="D159" s="16"/>
+      <c r="E159" s="16"/>
+    </row>
+    <row r="160">
+      <c r="B160" s="16" t="inlineStr">
+        <is>
+          <t>Expectativa de vida (renta temporal)</t>
+        </is>
+      </c>
+      <c r="C160" s="16"/>
+      <c r="D160" s="16"/>
+      <c r="E160" s="30" t="inlineStr">
+        <is>
+          <t>N/A · su ROP no es renta temporal</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="B161" s="16" t="inlineStr">
+        <is>
+          <t>Edad final del retiro programado</t>
+        </is>
+      </c>
+      <c r="C161" s="32">
+        <v>100</v>
+      </c>
+      <c r="D161" s="16"/>
+      <c r="E161" s="16"/>
+    </row>
+    <row r="162">
+      <c r="B162" s="16" t="inlineStr">
+        <is>
+          <t>Renta fija en colones</t>
+        </is>
+      </c>
+      <c r="C162" s="22">
+        <v>5.6</v>
+      </c>
+      <c r="D162" s="16"/>
+      <c r="E162" s="16"/>
+    </row>
+    <row r="163">
+      <c r="B163" s="16" t="inlineStr">
+        <is>
+          <t>Renta fija en dólares</t>
+        </is>
+      </c>
+      <c r="C163" s="22">
+        <v>5.46</v>
+      </c>
+      <c r="D163" s="16"/>
+      <c r="E163" s="16"/>
+    </row>
+    <row r="164">
+      <c r="B164" s="16" t="inlineStr">
+        <is>
+          <t>Edad de independencia financiera</t>
+        </is>
+      </c>
+      <c r="C164" s="16"/>
+      <c r="D164" s="16"/>
+      <c r="E164" s="30" t="inlineStr">
+        <is>
+          <t>60 años · dato del cuestionario</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="B165" s="16" t="inlineStr">
+        <is>
+          <t>Gasto en el retiro</t>
+        </is>
+      </c>
+      <c r="C165" s="16"/>
+      <c r="D165" s="16"/>
+      <c r="E165" s="30" t="inlineStr">
+        <is>
+          <t>100% del gasto actual · dato del cuestionario</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="B166" s="16" t="inlineStr">
+        <is>
+          <t>Edad de inicio de la pensión</t>
+        </is>
+      </c>
+      <c r="C166" s="16"/>
+      <c r="D166" s="16"/>
+      <c r="E166" s="30" t="inlineStr">
+        <is>
+          <t>65 años · dato del cuestionario</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="B167" s="16" t="inlineStr">
+        <is>
+          <t>Modalidad del ROP</t>
+        </is>
+      </c>
+      <c r="C167" s="16"/>
+      <c r="D167" s="16"/>
+      <c r="E167" s="30" t="inlineStr">
+        <is>
+          <t>Retiro programado · dato del cuestionario</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="B168" s="16" t="inlineStr">
+        <is>
           <t>Año de retiro de la pensión voluntaria</t>
         </is>
       </c>
-      <c r="C151" s="16"/>
-      <c r="D151" s="16"/>
-      <c r="E151" s="30" t="inlineStr">
+      <c r="C168" s="16"/>
+      <c r="D168" s="16"/>
+      <c r="E168" s="30" t="inlineStr">
         <is>
           <t>2031 · dato del cuestionario</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="13">
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B22:E22"/>
     <mergeCell ref="B28:E28"/>
     <mergeCell ref="B45:E45"/>
     <mergeCell ref="B52:E52"/>
     <mergeCell ref="B63:E63"/>
-    <mergeCell ref="B72:E72"/>
-    <mergeCell ref="B83:E83"/>
-    <mergeCell ref="B90:E90"/>
-    <mergeCell ref="B109:E109"/>
-    <mergeCell ref="B113:E113"/>
-    <mergeCell ref="B133:E133"/>
+    <mergeCell ref="B76:E76"/>
+    <mergeCell ref="B85:E85"/>
+    <mergeCell ref="B98:E98"/>
+    <mergeCell ref="B105:E105"/>
+    <mergeCell ref="B124:E124"/>
+    <mergeCell ref="B128:E128"/>
+    <mergeCell ref="B148:E148"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -22413,7 +22646,7 @@
       </c>
       <c r="C17" s="20" t="inlineStr">
         <is>
-          <t>Capital privado</t>
+          <t>Capital privado (monto invertido)</t>
         </is>
       </c>
       <c r="D17" s="17">
@@ -22432,12 +22665,10 @@
         <f>D17/F17</f>
         <v>800000</v>
       </c>
-      <c r="H17" s="18">
-        <v>0.15</v>
-      </c>
+      <c r="H17" s="18"/>
       <c r="I17" s="22">
         <f>G17*IF(H17="",1,H17)</f>
-        <v>120000</v>
+        <v>800000</v>
       </c>
       <c r="J17" s="26"/>
     </row>
@@ -22629,7 +22860,7 @@
       <c r="H24" s="23"/>
       <c r="I24" s="23">
         <f>SUM(I15:I23)</f>
-        <v>1280000.01</v>
+        <v>1960000.01</v>
       </c>
       <c r="J24" s="23"/>
     </row>

--- a/Ejemplo - proyeccion por flujo de caja.xlsx
+++ b/Ejemplo - proyeccion por flujo de caja.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="560">
   <si>
     <t xml:space="preserve">Chotocruz &amp; Co. · Ficha de cliente</t>
   </si>
@@ -312,7 +312,7 @@
     <t xml:space="preserve">Ninguna combinación de carteras modelo alcanza el equilibrio; se muestra la de mayor rendimiento.</t>
   </si>
   <si>
-    <t xml:space="preserve">Renta fija en Costa Rica y en EE. UU.</t>
+    <t xml:space="preserve">Porcentaje del portafolio en colones para cubrir gastos</t>
   </si>
   <si>
     <t xml:space="preserve">Gasto anual en colones (US$, valor de hoy)</t>
@@ -393,6 +393,72 @@
     <t xml:space="preserve">Edad a la que se agota el portafolio</t>
   </si>
   <si>
+    <t xml:space="preserve">¿Alcanza el plan?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Respuesta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No alcanza: el portafolio se agota a los 79 años y deja sin cubrir $689 048 de gasto, en dólares de hoy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los rendimientos pagan el faltante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En 50 años, los gastos superan a los ingresos en $5 149 758; los rendimientos del portafolio suman $1 310 831, menos que ese faltante.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Margen de rendimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El plan necesita 7,9% anual y la cartera sugerida rinde 5,9%: faltan 2,1 puntos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saldo del portafolio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se agota a los 79 años.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conclusiones para la toma de decisiones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dependencia del portafolio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90,0% del gasto · En 2027, sus ingresos propios pagan 90,0% de sus gastos; el portafolio debe aportar $9 802 ($817 al mes).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tasa de retiro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,8% · Retira 2,8% del portafolio al año, dentro de la referencia del 4% que se considera sostenible a largo plazo (Bengen, 1994).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rendimiento real</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,0% · La cartera rinde 5,9% y la inflación en dólares es 3,9%: el portafolio crece 2,0% al año en poder de compra. Los gastos en colones crecen con la inflación local (3,9%).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liquidez de cinco años</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$59 759 · En los próximos cinco años el portafolio debe entregar $59 759. La renta fija y el efectivo de la cartera ($162 500) lo cubren 2,7 veces: no habría que vender renta variable en una caída.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exposición al colón</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46,9% del gasto · Sus ingresos en colones cubren sus gastos en colones: el tipo de cambio no presiona el plan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patrimonio y liquidez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11,3% líquido · El portafolio es 11,3% de sus activos ($2 210 000); el resto, $1 960 000, es poco líquido (inmuebles, empresas, capital privado) y no paga gastos sin venderse. Pasivos: $135 000.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Caminos para alcanzar el objetivo</t>
   </si>
   <si>
@@ -471,16 +537,16 @@
     <t xml:space="preserve">Hay 5 caminos que alcanzan el objetivo cada uno por sí solo: mayor capital inicial, aporte anual adicional al portafolio, menor gasto familiar, aporte mensual adicional a la pensión voluntaria o postergar la independencia financiera. También pueden combinarse; combinados, cada uno exige un ajuste menor.</t>
   </si>
   <si>
-    <t xml:space="preserve">Procedimiento · Regla general</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cada valor necesario se obtiene cambiando una sola variable, con todo lo demás igual, y recalculando la proyección completa. Una búsqueda binaria (40 iteraciones) encuentra el valor en que el plan pasa de alcanzar a no alcanzar el objetivo. El objetivo es que no quede gasto sin cubrir en ningún año y que el saldo final del portafolio, en dólares de hoy, sea al menos la herencia.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Procedimiento · Herencia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Está en términos reales (dólares de hoy). Saldo final nominal en 2075: $0. En dólares de hoy = saldo nominal ÷ (1 + inflación internacional)^años = $0 ÷ (1 + 3,9%)^49,25 = $0.</t>
+    <t xml:space="preserve">Metodología de cálculo · Método</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se mueve una sola variable, con todo lo demás igual, hasta el punto en que el plan deja de alcanzar el objetivo: ningún año con gasto sin cubrir y saldo final real igual o mayor que la herencia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metodología de cálculo · Herencia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saldo final real = saldo nominal 2075 ÷ (1 + inflación)^años = $0 ÷ (1 + 3,9%)^49,25 = $0.</t>
   </si>
   <si>
     <t xml:space="preserve">Datos financieros declarados</t>
@@ -600,7 +666,7 @@
     <t xml:space="preserve">USD · Vivienda o propiedad · año 2031 · deseable · salida del portafolio</t>
   </si>
   <si>
-    <t xml:space="preserve">Perfil de permanencia y aportes</t>
+    <t xml:space="preserve">Retiros, aportes y herencia declarados</t>
   </si>
   <si>
     <t xml:space="preserve">Retiro: Retiro del portafolio (2031, valor de hoy)</t>
@@ -952,9 +1018,6 @@
   </si>
   <si>
     <t xml:space="preserve">Retiros adicionales del portafolio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Alcanza el plan?</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo del ROP al final (fuera del portafolio)</t>
@@ -3956,11 +4019,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="45662244"/>
-        <c:axId val="8956827"/>
+        <c:axId val="72667620"/>
+        <c:axId val="81828653"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="45662244"/>
+        <c:axId val="72667620"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="0.2"/>
@@ -4028,13 +4091,13 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="8956827"/>
+        <c:crossAx val="81828653"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="0.05"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="8956827"/>
+        <c:axId val="81828653"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -4111,7 +4174,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="45662244"/>
+        <c:crossAx val="72667620"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -5061,11 +5124,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="25907548"/>
-        <c:axId val="72167890"/>
+        <c:axId val="84236114"/>
+        <c:axId val="71457598"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="25907548"/>
+        <c:axId val="84236114"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="10"/>
@@ -5143,13 +5206,13 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="72167890"/>
+        <c:crossAx val="71457598"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="5"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="72167890"/>
+        <c:axId val="71457598"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="10"/>
@@ -5227,7 +5290,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="25907548"/>
+        <c:crossAx val="84236114"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="5"/>
@@ -6052,11 +6115,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="7250583"/>
-        <c:axId val="53740838"/>
+        <c:axId val="43701061"/>
+        <c:axId val="21361559"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="7250583"/>
+        <c:axId val="43701061"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6122,7 +6185,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="53740838"/>
+        <c:crossAx val="21361559"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6130,7 +6193,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="53740838"/>
+        <c:axId val="21361559"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6206,7 +6269,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="7250583"/>
+        <c:crossAx val="43701061"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6598,7 +6661,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:E166"/>
+  <dimension ref="B1:E180"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -7396,417 +7459,386 @@
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
     </row>
-    <row r="85" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B85" s="2" t="s">
+    <row r="85" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B85" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="C85" s="2" t="s">
+      <c r="C85" s="4"/>
+      <c r="D85" s="4"/>
+      <c r="E85" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="D85" s="2"/>
-      <c r="E85" s="2" t="s">
+    </row>
+    <row r="86" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B86" s="4" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B86" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="C86" s="8" t="s">
-        <v>126</v>
-      </c>
+      <c r="C86" s="4"/>
       <c r="D86" s="4"/>
       <c r="E86" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B87" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="C87" s="8" t="s">
-        <v>129</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="C87" s="4"/>
       <c r="D87" s="4"/>
       <c r="E87" s="5" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B88" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="C88" s="8" t="s">
-        <v>132</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="C88" s="4"/>
       <c r="D88" s="4"/>
       <c r="E88" s="5" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B89" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="C89" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="D89" s="4"/>
-      <c r="E89" s="5" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B90" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="C90" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D90" s="4"/>
-      <c r="E90" s="5" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="90" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B90" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C90" s="3"/>
+      <c r="D90" s="3"/>
+      <c r="E90" s="3"/>
+    </row>
+    <row r="91" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B91" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="C91" s="8" t="s">
-        <v>140</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="C91" s="4"/>
       <c r="D91" s="4"/>
       <c r="E91" s="5" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B92" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="C92" s="8" t="s">
-        <v>143</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="C92" s="4"/>
       <c r="D92" s="4"/>
       <c r="E92" s="5" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B93" s="4" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="C93" s="4"/>
       <c r="D93" s="4"/>
       <c r="E93" s="5" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B94" s="4" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="C94" s="4"/>
       <c r="D94" s="4"/>
       <c r="E94" s="5" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B95" s="4" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C95" s="4"/>
       <c r="D95" s="4"/>
       <c r="E95" s="5" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="97" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B97" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="C97" s="3"/>
-      <c r="D97" s="3"/>
-      <c r="E97" s="3"/>
-    </row>
-    <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B98" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C98" s="8" t="n">
-        <v>2700000</v>
-      </c>
-      <c r="D98" s="4"/>
-      <c r="E98" s="5" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B99" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="C99" s="8" t="n">
-        <v>5500</v>
-      </c>
-      <c r="D99" s="4"/>
-      <c r="E99" s="5" t="s">
-        <v>155</v>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B96" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C96" s="4"/>
+      <c r="D96" s="4"/>
+      <c r="E96" s="5" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="98" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B98" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C98" s="3"/>
+      <c r="D98" s="3"/>
+      <c r="E98" s="3"/>
+    </row>
+    <row r="99" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B99" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D99" s="2"/>
+      <c r="E99" s="2" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B100" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="C100" s="8" t="n">
-        <v>250000</v>
+        <v>147</v>
+      </c>
+      <c r="C100" s="8" t="s">
+        <v>148</v>
       </c>
       <c r="D100" s="4"/>
       <c r="E100" s="5" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B101" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="C101" s="4"/>
+        <v>150</v>
+      </c>
+      <c r="C101" s="8" t="s">
+        <v>151</v>
+      </c>
       <c r="D101" s="4"/>
       <c r="E101" s="5" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B102" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C102" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="D102" s="4"/>
+      <c r="E102" s="5" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B103" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="C103" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="D103" s="4"/>
+      <c r="E103" s="5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B104" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="C102" s="4"/>
-      <c r="D102" s="4"/>
-      <c r="E102" s="4"/>
-    </row>
-    <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="104" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B104" s="3" t="s">
+      <c r="C104" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D104" s="4"/>
+      <c r="E104" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="C104" s="3"/>
-      <c r="D104" s="3"/>
-      <c r="E104" s="3"/>
     </row>
     <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B105" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="C105" s="9" t="n">
-        <v>1</v>
+      <c r="C105" s="8" t="s">
+        <v>162</v>
       </c>
       <c r="D105" s="4"/>
-      <c r="E105" s="4"/>
+      <c r="E105" s="5" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B106" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="C106" s="4"/>
+        <v>164</v>
+      </c>
+      <c r="C106" s="8" t="s">
+        <v>165</v>
+      </c>
       <c r="D106" s="4"/>
       <c r="E106" s="5" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="107" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B107" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="C107" s="8" t="n">
-        <v>800000</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="C107" s="4"/>
       <c r="D107" s="4"/>
       <c r="E107" s="5" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B108" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="C108" s="6" t="n">
-        <v>65</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="C108" s="4"/>
       <c r="D108" s="4"/>
-      <c r="E108" s="4"/>
-    </row>
-    <row r="109" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E108" s="5" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B109" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="C109" s="8" t="n">
-        <v>500000</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="C109" s="4"/>
       <c r="D109" s="4"/>
       <c r="E109" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="110" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B110" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="C110" s="8" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="D110" s="4"/>
-      <c r="E110" s="5" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="111" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B111" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="C111" s="4"/>
-      <c r="D111" s="4"/>
-      <c r="E111" s="5" t="s">
-        <v>171</v>
-      </c>
+        <v>172</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="111" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B111" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C111" s="3"/>
+      <c r="D111" s="3"/>
+      <c r="E111" s="3"/>
     </row>
     <row r="112" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B112" s="4" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C112" s="8" t="n">
-        <v>12000000</v>
+        <v>2700000</v>
       </c>
       <c r="D112" s="4"/>
       <c r="E112" s="5" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B113" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="C113" s="4"/>
+        <v>176</v>
+      </c>
+      <c r="C113" s="8" t="n">
+        <v>5500</v>
+      </c>
       <c r="D113" s="4"/>
       <c r="E113" s="5" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B114" s="4" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C114" s="8" t="n">
-        <v>12000000</v>
+        <v>250000</v>
       </c>
       <c r="D114" s="4"/>
       <c r="E114" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B115" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="C115" s="8" t="n">
-        <v>150000</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="C115" s="4"/>
       <c r="D115" s="4"/>
       <c r="E115" s="5" t="s">
-        <v>153</v>
+        <v>180</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B116" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="C116" s="8" t="n">
-        <v>40000</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="C116" s="4"/>
       <c r="D116" s="4"/>
-      <c r="E116" s="5" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="117" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B117" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="C117" s="8" t="n">
-        <v>120000</v>
-      </c>
-      <c r="D117" s="4"/>
-      <c r="E117" s="5" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="118" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B118" s="4" t="s">
+      <c r="E116" s="4"/>
+    </row>
+    <row r="117" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="118" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B118" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C118" s="8" t="n">
-        <v>180000</v>
-      </c>
-      <c r="D118" s="4"/>
-      <c r="E118" s="5" t="s">
-        <v>183</v>
-      </c>
+      <c r="C118" s="3"/>
+      <c r="D118" s="3"/>
+      <c r="E118" s="3"/>
     </row>
     <row r="119" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B119" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="C119" s="8" t="n">
-        <v>150000</v>
+        <v>183</v>
+      </c>
+      <c r="C119" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="D119" s="4"/>
-      <c r="E119" s="5" t="s">
-        <v>185</v>
-      </c>
+      <c r="E119" s="4"/>
     </row>
     <row r="120" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B120" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="C120" s="8" t="n">
-        <v>12000</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="C120" s="4"/>
       <c r="D120" s="4"/>
       <c r="E120" s="5" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B121" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C121" s="8" t="n">
-        <v>40000</v>
+        <v>800000</v>
       </c>
       <c r="D121" s="4"/>
       <c r="E121" s="5" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B122" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="C122" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="D122" s="4"/>
+      <c r="E122" s="4"/>
+    </row>
+    <row r="123" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B123" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="C123" s="8" t="n">
+        <v>500000</v>
+      </c>
+      <c r="D123" s="4"/>
+      <c r="E123" s="5" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="122" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="123" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B123" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="C123" s="3"/>
-      <c r="D123" s="3"/>
-      <c r="E123" s="3"/>
     </row>
     <row r="124" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B124" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C124" s="8" t="n">
-        <v>50000</v>
+        <v>12000000</v>
       </c>
       <c r="D124" s="4"/>
       <c r="E124" s="5" t="s">
-        <v>155</v>
+        <v>191</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7819,189 +7851,180 @@
         <v>193</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="127" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B127" s="3" t="s">
+    <row r="126" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B126" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="C127" s="3"/>
-      <c r="D127" s="3"/>
-      <c r="E127" s="3"/>
+      <c r="C126" s="8" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="D126" s="4"/>
+      <c r="E126" s="5" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B127" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C127" s="4"/>
+      <c r="D127" s="4"/>
+      <c r="E127" s="5" t="s">
+        <v>193</v>
+      </c>
     </row>
     <row r="128" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B128" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="C128" s="4"/>
+        <v>197</v>
+      </c>
+      <c r="C128" s="8" t="n">
+        <v>12000000</v>
+      </c>
       <c r="D128" s="4"/>
       <c r="E128" s="5" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B129" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="C129" s="6" t="n">
-        <v>1</v>
+        <v>199</v>
+      </c>
+      <c r="C129" s="8" t="n">
+        <v>150000</v>
       </c>
       <c r="D129" s="4"/>
       <c r="E129" s="5" t="s">
-        <v>198</v>
+        <v>175</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B130" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="C130" s="4"/>
+        <v>200</v>
+      </c>
+      <c r="C130" s="8" t="n">
+        <v>40000</v>
+      </c>
       <c r="D130" s="4"/>
       <c r="E130" s="5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B131" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="C131" s="4"/>
+        <v>202</v>
+      </c>
+      <c r="C131" s="8" t="n">
+        <v>120000</v>
+      </c>
       <c r="D131" s="4"/>
       <c r="E131" s="5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B132" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C132" s="8" t="n">
-        <v>120000</v>
+        <v>180000</v>
       </c>
       <c r="D132" s="4"/>
       <c r="E132" s="5" t="s">
-        <v>155</v>
+        <v>205</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B133" s="4" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C133" s="8" t="n">
-        <v>1200</v>
+        <v>150000</v>
       </c>
       <c r="D133" s="4"/>
       <c r="E133" s="5" t="s">
-        <v>155</v>
+        <v>207</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B134" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="C134" s="9" t="n">
-        <v>0.085</v>
+        <v>208</v>
+      </c>
+      <c r="C134" s="8" t="n">
+        <v>12000</v>
       </c>
       <c r="D134" s="4"/>
-      <c r="E134" s="4"/>
+      <c r="E134" s="5" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="135" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B135" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="C135" s="6" t="n">
-        <v>15</v>
+        <v>210</v>
+      </c>
+      <c r="C135" s="8" t="n">
+        <v>40000</v>
       </c>
       <c r="D135" s="4"/>
-      <c r="E135" s="4"/>
-    </row>
-    <row r="136" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B136" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="C136" s="8" t="n">
-        <v>180000</v>
-      </c>
-      <c r="D136" s="4"/>
-      <c r="E136" s="5" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="137" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B137" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="C137" s="8" t="n">
-        <v>900000</v>
-      </c>
-      <c r="D137" s="4"/>
-      <c r="E137" s="5" t="s">
-        <v>210</v>
-      </c>
+      <c r="E135" s="5" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="137" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B137" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C137" s="3"/>
+      <c r="D137" s="3"/>
+      <c r="E137" s="3"/>
     </row>
     <row r="138" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B138" s="4" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C138" s="8" t="n">
-        <v>800000</v>
+        <v>50000</v>
       </c>
       <c r="D138" s="4"/>
       <c r="E138" s="5" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B139" s="4" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C139" s="4"/>
       <c r="D139" s="4"/>
       <c r="E139" s="5" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="140" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B140" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="C140" s="8" t="n">
-        <v>5400000</v>
-      </c>
-      <c r="D140" s="4"/>
-      <c r="E140" s="5" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="141" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B141" s="4" t="s">
+    <row r="140" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="141" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B141" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="C141" s="8" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D141" s="4"/>
-      <c r="E141" s="5" t="s">
-        <v>217</v>
-      </c>
+      <c r="C141" s="3"/>
+      <c r="D141" s="3"/>
+      <c r="E141" s="3"/>
     </row>
     <row r="142" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B142" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="C142" s="8" t="n">
-        <v>3000</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="C142" s="4"/>
       <c r="D142" s="4"/>
       <c r="E142" s="5" t="s">
-        <v>155</v>
+        <v>218</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B143" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="C143" s="8" t="n">
-        <v>6000</v>
+      <c r="C143" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="D143" s="4"/>
       <c r="E143" s="5" t="s">
@@ -8012,9 +8035,7 @@
       <c r="B144" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="C144" s="8" t="n">
-        <v>15750000</v>
-      </c>
+      <c r="C144" s="4"/>
       <c r="D144" s="4"/>
       <c r="E144" s="5" t="s">
         <v>222</v>
@@ -8030,207 +8051,367 @@
         <v>224</v>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="147" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B147" s="3" t="s">
+    <row r="146" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B146" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="C147" s="3"/>
-      <c r="D147" s="3"/>
-      <c r="E147" s="3"/>
+      <c r="C146" s="8" t="n">
+        <v>120000</v>
+      </c>
+      <c r="D146" s="4"/>
+      <c r="E146" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B147" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="C147" s="8" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D147" s="4"/>
+      <c r="E147" s="5" t="s">
+        <v>177</v>
+      </c>
     </row>
     <row r="148" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B148" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="C148" s="8" t="n">
-        <v>450</v>
+        <v>227</v>
+      </c>
+      <c r="C148" s="9" t="n">
+        <v>0.085</v>
       </c>
       <c r="D148" s="4"/>
       <c r="E148" s="4"/>
     </row>
     <row r="149" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B149" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="C149" s="9" t="n">
-        <v>0.039</v>
+        <v>228</v>
+      </c>
+      <c r="C149" s="6" t="n">
+        <v>15</v>
       </c>
       <c r="D149" s="4"/>
       <c r="E149" s="4"/>
     </row>
-    <row r="150" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B150" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="C150" s="9" t="n">
-        <v>0.039</v>
+        <v>229</v>
+      </c>
+      <c r="C150" s="8" t="n">
+        <v>180000</v>
       </c>
       <c r="D150" s="4"/>
-      <c r="E150" s="4"/>
+      <c r="E150" s="5" t="s">
+        <v>230</v>
+      </c>
     </row>
     <row r="151" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B151" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="C151" s="9" t="n">
-        <v>0.01</v>
+        <v>231</v>
+      </c>
+      <c r="C151" s="8" t="n">
+        <v>900000</v>
       </c>
       <c r="D151" s="4"/>
-      <c r="E151" s="4"/>
+      <c r="E151" s="5" t="s">
+        <v>232</v>
+      </c>
     </row>
     <row r="152" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B152" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="C152" s="9" t="n">
-        <v>0.039</v>
+        <v>233</v>
+      </c>
+      <c r="C152" s="8" t="n">
+        <v>800000</v>
       </c>
       <c r="D152" s="4"/>
-      <c r="E152" s="4"/>
+      <c r="E152" s="5" t="s">
+        <v>177</v>
+      </c>
     </row>
     <row r="153" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B153" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="C153" s="9" t="n">
-        <v>0.039</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="C153" s="4"/>
       <c r="D153" s="4"/>
-      <c r="E153" s="4"/>
+      <c r="E153" s="5" t="s">
+        <v>235</v>
+      </c>
     </row>
     <row r="154" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B154" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="C154" s="6" t="n">
-        <v>2026</v>
+        <v>236</v>
+      </c>
+      <c r="C154" s="8" t="n">
+        <v>5400000</v>
       </c>
       <c r="D154" s="4"/>
-      <c r="E154" s="4"/>
+      <c r="E154" s="5" t="s">
+        <v>237</v>
+      </c>
     </row>
     <row r="155" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B155" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="C155" s="6" t="n">
-        <v>95</v>
+        <v>238</v>
+      </c>
+      <c r="C155" s="8" t="n">
+        <v>3000</v>
       </c>
       <c r="D155" s="4"/>
-      <c r="E155" s="4"/>
+      <c r="E155" s="5" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="156" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B156" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="C156" s="9" t="n">
-        <v>0.06</v>
+        <v>240</v>
+      </c>
+      <c r="C156" s="8" t="n">
+        <v>3000</v>
       </c>
       <c r="D156" s="4"/>
-      <c r="E156" s="4"/>
+      <c r="E156" s="5" t="s">
+        <v>177</v>
+      </c>
     </row>
     <row r="157" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B157" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="C157" s="9" t="n">
-        <v>0.0425</v>
+        <v>241</v>
+      </c>
+      <c r="C157" s="8" t="n">
+        <v>6000</v>
       </c>
       <c r="D157" s="4"/>
-      <c r="E157" s="4"/>
+      <c r="E157" s="5" t="s">
+        <v>242</v>
+      </c>
     </row>
     <row r="158" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B158" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="C158" s="9" t="n">
-        <v>0.015</v>
+        <v>243</v>
+      </c>
+      <c r="C158" s="8" t="n">
+        <v>15750000</v>
       </c>
       <c r="D158" s="4"/>
-      <c r="E158" s="4"/>
+      <c r="E158" s="5" t="s">
+        <v>244</v>
+      </c>
     </row>
     <row r="159" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B159" s="4" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="C159" s="4"/>
       <c r="D159" s="4"/>
       <c r="E159" s="5" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="160" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B160" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="C160" s="6" t="n">
-        <v>100</v>
-      </c>
-      <c r="D160" s="4"/>
-      <c r="E160" s="4"/>
-    </row>
-    <row r="161" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B161" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="C161" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="D161" s="4"/>
-      <c r="E161" s="4"/>
+        <v>246</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="161" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B161" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C161" s="3"/>
+      <c r="D161" s="3"/>
+      <c r="E161" s="3"/>
     </row>
     <row r="162" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B162" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C162" s="4"/>
+        <v>248</v>
+      </c>
+      <c r="C162" s="8" t="n">
+        <v>450</v>
+      </c>
       <c r="D162" s="4"/>
-      <c r="E162" s="5" t="s">
-        <v>240</v>
-      </c>
+      <c r="E162" s="4"/>
     </row>
     <row r="163" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B163" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="C163" s="4"/>
+        <v>249</v>
+      </c>
+      <c r="C163" s="9" t="n">
+        <v>0.039</v>
+      </c>
       <c r="D163" s="4"/>
-      <c r="E163" s="5" t="s">
-        <v>242</v>
-      </c>
+      <c r="E163" s="4"/>
     </row>
     <row r="164" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B164" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="C164" s="4"/>
+        <v>250</v>
+      </c>
+      <c r="C164" s="9" t="n">
+        <v>0.039</v>
+      </c>
       <c r="D164" s="4"/>
-      <c r="E164" s="5" t="s">
-        <v>243</v>
-      </c>
+      <c r="E164" s="4"/>
     </row>
     <row r="165" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B165" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="C165" s="4"/>
+        <v>251</v>
+      </c>
+      <c r="C165" s="9" t="n">
+        <v>0.01</v>
+      </c>
       <c r="D165" s="4"/>
-      <c r="E165" s="5" t="s">
-        <v>245</v>
-      </c>
+      <c r="E165" s="4"/>
     </row>
     <row r="166" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B166" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="C166" s="4"/>
+        <v>252</v>
+      </c>
+      <c r="C166" s="9" t="n">
+        <v>0.039</v>
+      </c>
       <c r="D166" s="4"/>
-      <c r="E166" s="5" t="s">
-        <v>247</v>
+      <c r="E166" s="4"/>
+    </row>
+    <row r="167" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B167" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="C167" s="9" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="D167" s="4"/>
+      <c r="E167" s="4"/>
+    </row>
+    <row r="168" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B168" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="C168" s="6" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D168" s="4"/>
+      <c r="E168" s="4"/>
+    </row>
+    <row r="169" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B169" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="C169" s="6" t="n">
+        <v>95</v>
+      </c>
+      <c r="D169" s="4"/>
+      <c r="E169" s="4"/>
+    </row>
+    <row r="170" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B170" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="C170" s="9" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="D170" s="4"/>
+      <c r="E170" s="4"/>
+    </row>
+    <row r="171" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B171" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="C171" s="9" t="n">
+        <v>0.0425</v>
+      </c>
+      <c r="D171" s="4"/>
+      <c r="E171" s="4"/>
+    </row>
+    <row r="172" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B172" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="C172" s="9" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D172" s="4"/>
+      <c r="E172" s="4"/>
+    </row>
+    <row r="173" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B173" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="C173" s="4"/>
+      <c r="D173" s="4"/>
+      <c r="E173" s="5" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="174" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B174" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="C174" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="D174" s="4"/>
+      <c r="E174" s="4"/>
+    </row>
+    <row r="175" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B175" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C175" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D175" s="4"/>
+      <c r="E175" s="4"/>
+    </row>
+    <row r="176" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B176" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C176" s="4"/>
+      <c r="D176" s="4"/>
+      <c r="E176" s="5" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="177" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B177" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="C177" s="4"/>
+      <c r="D177" s="4"/>
+      <c r="E177" s="5" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="178" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B178" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="C178" s="4"/>
+      <c r="D178" s="4"/>
+      <c r="E178" s="5" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="179" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B179" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="C179" s="4"/>
+      <c r="D179" s="4"/>
+      <c r="E179" s="5" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="180" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B180" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="C180" s="4"/>
+      <c r="D180" s="4"/>
+      <c r="E180" s="5" t="s">
+        <v>269</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="15">
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B22:E22"/>
     <mergeCell ref="B28:E28"/>
@@ -8239,11 +8420,13 @@
     <mergeCell ref="B63:E63"/>
     <mergeCell ref="B75:E75"/>
     <mergeCell ref="B84:E84"/>
-    <mergeCell ref="B97:E97"/>
-    <mergeCell ref="B104:E104"/>
-    <mergeCell ref="B123:E123"/>
-    <mergeCell ref="B127:E127"/>
-    <mergeCell ref="B147:E147"/>
+    <mergeCell ref="B90:E90"/>
+    <mergeCell ref="B98:E98"/>
+    <mergeCell ref="B111:E111"/>
+    <mergeCell ref="B118:E118"/>
+    <mergeCell ref="B137:E137"/>
+    <mergeCell ref="B141:E141"/>
+    <mergeCell ref="B161:E161"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -8279,18 +8462,18 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>248</v>
+        <v>270</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="10" t="s">
-        <v>249</v>
+        <v>271</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="3" t="s">
-        <v>250</v>
+        <v>272</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -8298,7 +8481,7 @@
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
       <c r="I4" s="3" t="s">
-        <v>251</v>
+        <v>273</v>
       </c>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
@@ -8308,7 +8491,7 @@
       <c r="O4" s="3"/>
       <c r="P4" s="3"/>
       <c r="R4" s="3" t="s">
-        <v>252</v>
+        <v>274</v>
       </c>
       <c r="S4" s="3"/>
       <c r="T4" s="3"/>
@@ -8317,7 +8500,7 @@
       <c r="W4" s="3"/>
       <c r="X4" s="3"/>
       <c r="Z4" s="3" t="s">
-        <v>253</v>
+        <v>275</v>
       </c>
       <c r="AA4" s="3"/>
       <c r="AB4" s="3"/>
@@ -8325,7 +8508,7 @@
       <c r="AD4" s="3"/>
       <c r="AE4" s="3"/>
       <c r="AG4" s="3" t="s">
-        <v>254</v>
+        <v>276</v>
       </c>
       <c r="AH4" s="3"/>
       <c r="AI4" s="3"/>
@@ -8338,51 +8521,51 @@
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F5" s="2" t="s">
-        <v>255</v>
+        <v>277</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>256</v>
+        <v>278</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>257</v>
+        <v>279</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>258</v>
+        <v>280</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>259</v>
+        <v>281</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>260</v>
+        <v>282</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>261</v>
+        <v>283</v>
       </c>
       <c r="U5" s="2" t="s">
-        <v>257</v>
+        <v>279</v>
       </c>
       <c r="V5" s="2" t="s">
-        <v>258</v>
+        <v>280</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>259</v>
+        <v>281</v>
       </c>
       <c r="X5" s="2" t="s">
-        <v>261</v>
+        <v>283</v>
       </c>
       <c r="AC5" s="2" t="s">
-        <v>257</v>
+        <v>279</v>
       </c>
       <c r="AD5" s="2" t="s">
-        <v>258</v>
+        <v>280</v>
       </c>
       <c r="AE5" s="2" t="s">
-        <v>259</v>
+        <v>281</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="11" t="s">
-        <v>262</v>
+        <v>284</v>
       </c>
       <c r="C6" s="11"/>
       <c r="D6" s="11"/>
@@ -8390,7 +8573,7 @@
       <c r="F6" s="11"/>
       <c r="G6" s="11"/>
       <c r="I6" s="11" t="s">
-        <v>263</v>
+        <v>285</v>
       </c>
       <c r="J6" s="11"/>
       <c r="K6" s="11"/>
@@ -8400,7 +8583,7 @@
       <c r="O6" s="11"/>
       <c r="P6" s="11"/>
       <c r="R6" s="11" t="s">
-        <v>264</v>
+        <v>286</v>
       </c>
       <c r="S6" s="11"/>
       <c r="T6" s="11"/>
@@ -8409,7 +8592,7 @@
       <c r="W6" s="11"/>
       <c r="X6" s="11"/>
       <c r="Z6" s="11" t="s">
-        <v>265</v>
+        <v>287</v>
       </c>
       <c r="AA6" s="11"/>
       <c r="AB6" s="11"/>
@@ -8417,13 +8600,13 @@
       <c r="AD6" s="11"/>
       <c r="AE6" s="11"/>
       <c r="AG6" s="11" t="s">
-        <v>266</v>
+        <v>288</v>
       </c>
       <c r="AH6" s="11"/>
       <c r="AI6" s="11"/>
       <c r="AJ6" s="11"/>
       <c r="AL6" s="11" t="s">
-        <v>267</v>
+        <v>289</v>
       </c>
       <c r="AM6" s="11"/>
       <c r="AN6" s="11"/>
@@ -8431,7 +8614,7 @@
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="4" t="s">
-        <v>226</v>
+        <v>248</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
@@ -8440,10 +8623,10 @@
         <v>450</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>268</v>
+        <v>290</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>269</v>
+        <v>291</v>
       </c>
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
@@ -8468,7 +8651,7 @@
         <v>14</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="S7" s="4"/>
       <c r="T7" s="4"/>
@@ -8486,7 +8669,7 @@
       </c>
       <c r="X7" s="4"/>
       <c r="Z7" s="4" t="s">
-        <v>270</v>
+        <v>292</v>
       </c>
       <c r="AA7" s="4"/>
       <c r="AB7" s="4"/>
@@ -8503,7 +8686,7 @@
         <v>250000</v>
       </c>
       <c r="AG7" s="4" t="s">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="AH7" s="4"/>
       <c r="AI7" s="4"/>
@@ -8512,7 +8695,7 @@
         <v>5643124.40977774</v>
       </c>
       <c r="AL7" s="4" t="s">
-        <v>272</v>
+        <v>294</v>
       </c>
       <c r="AM7" s="4"/>
       <c r="AN7" s="4"/>
@@ -8523,7 +8706,7 @@
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="4" t="s">
-        <v>227</v>
+        <v>249</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
@@ -8532,10 +8715,10 @@
         <v>0.039</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>268</v>
+        <v>290</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>273</v>
+        <v>295</v>
       </c>
       <c r="J8" s="4"/>
       <c r="K8" s="4"/>
@@ -8560,7 +8743,7 @@
         <v>0</v>
       </c>
       <c r="R8" s="4" t="s">
-        <v>274</v>
+        <v>296</v>
       </c>
       <c r="S8" s="4"/>
       <c r="T8" s="4"/>
@@ -8572,7 +8755,7 @@
       </c>
       <c r="X8" s="4"/>
       <c r="Z8" s="4" t="s">
-        <v>275</v>
+        <v>297</v>
       </c>
       <c r="AA8" s="4"/>
       <c r="AB8" s="4"/>
@@ -8583,7 +8766,7 @@
         <v>0.0585725</v>
       </c>
       <c r="AG8" s="4" t="s">
-        <v>276</v>
+        <v>298</v>
       </c>
       <c r="AH8" s="4"/>
       <c r="AI8" s="4"/>
@@ -8592,7 +8775,7 @@
         <v>283622.368463526</v>
       </c>
       <c r="AL8" s="4" t="s">
-        <v>277</v>
+        <v>299</v>
       </c>
       <c r="AM8" s="4"/>
       <c r="AN8" s="4"/>
@@ -8603,7 +8786,7 @@
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="4" t="s">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
@@ -8612,10 +8795,10 @@
         <v>0.039</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>268</v>
+        <v>290</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>278</v>
+        <v>300</v>
       </c>
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
@@ -8640,7 +8823,7 @@
         <v>50</v>
       </c>
       <c r="R9" s="4" t="s">
-        <v>279</v>
+        <v>301</v>
       </c>
       <c r="S9" s="4"/>
       <c r="T9" s="4"/>
@@ -8652,7 +8835,7 @@
       </c>
       <c r="X9" s="4"/>
       <c r="Z9" s="11" t="s">
-        <v>280</v>
+        <v>302</v>
       </c>
       <c r="AA9" s="11"/>
       <c r="AB9" s="11"/>
@@ -8660,7 +8843,7 @@
       <c r="AD9" s="11"/>
       <c r="AE9" s="11"/>
       <c r="AG9" s="4" t="s">
-        <v>281</v>
+        <v>303</v>
       </c>
       <c r="AH9" s="4"/>
       <c r="AI9" s="4"/>
@@ -8669,7 +8852,7 @@
         <v>-10458609.9323128</v>
       </c>
       <c r="AL9" s="4" t="s">
-        <v>282</v>
+        <v>304</v>
       </c>
       <c r="AM9" s="4"/>
       <c r="AN9" s="4"/>
@@ -8680,7 +8863,7 @@
     </row>
     <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="4" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -8689,10 +8872,10 @@
         <v>0.01</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>268</v>
+        <v>290</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>283</v>
+        <v>305</v>
       </c>
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
@@ -8714,7 +8897,7 @@
       </c>
       <c r="P10" s="4"/>
       <c r="R10" s="4" t="s">
-        <v>284</v>
+        <v>306</v>
       </c>
       <c r="S10" s="4"/>
       <c r="T10" s="4"/>
@@ -8732,7 +8915,7 @@
       </c>
       <c r="X10" s="4"/>
       <c r="Z10" s="4" t="s">
-        <v>285</v>
+        <v>307</v>
       </c>
       <c r="AA10" s="4"/>
       <c r="AB10" s="4"/>
@@ -8743,7 +8926,7 @@
         <v>180000</v>
       </c>
       <c r="AG10" s="4" t="s">
-        <v>286</v>
+        <v>308</v>
       </c>
       <c r="AH10" s="4"/>
       <c r="AI10" s="4"/>
@@ -8752,7 +8935,7 @@
         <v>-1031906.10610854</v>
       </c>
       <c r="AL10" s="4" t="s">
-        <v>287</v>
+        <v>309</v>
       </c>
       <c r="AM10" s="4"/>
       <c r="AN10" s="4"/>
@@ -8763,7 +8946,7 @@
     </row>
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="4" t="s">
-        <v>288</v>
+        <v>310</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
@@ -8772,10 +8955,10 @@
         <v>0.039</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>268</v>
+        <v>290</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>289</v>
+        <v>311</v>
       </c>
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
@@ -8788,7 +8971,7 @@
       <c r="O11" s="4"/>
       <c r="P11" s="4"/>
       <c r="R11" s="4" t="s">
-        <v>204</v>
+        <v>226</v>
       </c>
       <c r="S11" s="4"/>
       <c r="T11" s="4"/>
@@ -8809,7 +8992,7 @@
         <v>15</v>
       </c>
       <c r="Z11" s="4" t="s">
-        <v>290</v>
+        <v>312</v>
       </c>
       <c r="AA11" s="4"/>
       <c r="AB11" s="4"/>
@@ -8820,7 +9003,7 @@
         <v>0</v>
       </c>
       <c r="AG11" s="15" t="s">
-        <v>291</v>
+        <v>313</v>
       </c>
       <c r="AH11" s="15"/>
       <c r="AI11" s="15"/>
@@ -8829,7 +9012,7 @@
         <v>-5563769.26018004</v>
       </c>
       <c r="AL11" s="4" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="AM11" s="4"/>
       <c r="AN11" s="4"/>
@@ -8840,7 +9023,7 @@
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="4" t="s">
-        <v>231</v>
+        <v>253</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
@@ -8849,22 +9032,22 @@
         <v>0.039</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>268</v>
+        <v>290</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>293</v>
+        <v>315</v>
       </c>
       <c r="J12" s="4"/>
       <c r="K12" s="4"/>
       <c r="L12" s="4" t="s">
-        <v>294</v>
+        <v>316</v>
       </c>
       <c r="M12" s="4"/>
       <c r="N12" s="4"/>
       <c r="O12" s="4"/>
       <c r="P12" s="4"/>
       <c r="R12" s="4" t="s">
-        <v>295</v>
+        <v>317</v>
       </c>
       <c r="S12" s="4"/>
       <c r="T12" s="4"/>
@@ -8876,7 +9059,7 @@
       </c>
       <c r="X12" s="4"/>
       <c r="Z12" s="4" t="s">
-        <v>296</v>
+        <v>318</v>
       </c>
       <c r="AA12" s="4"/>
       <c r="AB12" s="4"/>
@@ -8887,13 +9070,13 @@
         <v>150000</v>
       </c>
       <c r="AG12" s="11" t="s">
-        <v>297</v>
+        <v>319</v>
       </c>
       <c r="AH12" s="11"/>
       <c r="AI12" s="11"/>
       <c r="AJ12" s="11"/>
       <c r="AL12" s="15" t="s">
-        <v>298</v>
+        <v>320</v>
       </c>
       <c r="AM12" s="15"/>
       <c r="AN12" s="15"/>
@@ -8904,7 +9087,7 @@
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="4" t="s">
-        <v>299</v>
+        <v>321</v>
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
@@ -8916,19 +9099,19 @@
         <v>39</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>300</v>
+        <v>322</v>
       </c>
       <c r="J13" s="4"/>
       <c r="K13" s="4"/>
       <c r="L13" s="4" t="s">
-        <v>294</v>
+        <v>316</v>
       </c>
       <c r="M13" s="4"/>
       <c r="N13" s="4"/>
       <c r="O13" s="4"/>
       <c r="P13" s="4"/>
       <c r="R13" s="11" t="s">
-        <v>301</v>
+        <v>323</v>
       </c>
       <c r="S13" s="11"/>
       <c r="T13" s="11"/>
@@ -8937,7 +9120,7 @@
       <c r="W13" s="11"/>
       <c r="X13" s="11"/>
       <c r="AG13" s="4" t="s">
-        <v>302</v>
+        <v>324</v>
       </c>
       <c r="AH13" s="4"/>
       <c r="AI13" s="4"/>
@@ -8945,7 +9128,7 @@
         <v>0</v>
       </c>
       <c r="AL13" s="15" t="s">
-        <v>303</v>
+        <v>325</v>
       </c>
       <c r="AM13" s="15"/>
       <c r="AN13" s="15"/>
@@ -8956,7 +9139,7 @@
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="4" t="s">
-        <v>234</v>
+        <v>256</v>
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
@@ -8965,10 +9148,10 @@
         <v>0.06</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>268</v>
+        <v>290</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>304</v>
+        <v>326</v>
       </c>
       <c r="J14" s="11"/>
       <c r="K14" s="11"/>
@@ -8978,7 +9161,7 @@
       <c r="O14" s="11"/>
       <c r="P14" s="11"/>
       <c r="R14" s="4" t="s">
-        <v>286</v>
+        <v>308</v>
       </c>
       <c r="S14" s="4"/>
       <c r="T14" s="4"/>
@@ -8999,7 +9182,7 @@
         <v>79</v>
       </c>
       <c r="AL14" s="4" t="s">
-        <v>305</v>
+        <v>327</v>
       </c>
       <c r="AM14" s="4"/>
       <c r="AN14" s="4"/>
@@ -9010,7 +9193,7 @@
     </row>
     <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="4" t="s">
-        <v>306</v>
+        <v>328</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
@@ -9019,10 +9202,10 @@
         <v>0.0425</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>268</v>
+        <v>290</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>276</v>
+        <v>298</v>
       </c>
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
@@ -9035,7 +9218,7 @@
       <c r="O15" s="4"/>
       <c r="P15" s="4"/>
       <c r="R15" s="4" t="s">
-        <v>307</v>
+        <v>329</v>
       </c>
       <c r="S15" s="4"/>
       <c r="T15" s="4"/>
@@ -9047,7 +9230,7 @@
       </c>
       <c r="X15" s="4"/>
       <c r="AG15" s="15" t="s">
-        <v>308</v>
+        <v>121</v>
       </c>
       <c r="AH15" s="15"/>
       <c r="AI15" s="15"/>
@@ -9056,7 +9239,7 @@
         <v>No alcanza</v>
       </c>
       <c r="AL15" s="4" t="s">
-        <v>309</v>
+        <v>330</v>
       </c>
       <c r="AM15" s="4"/>
       <c r="AN15" s="4"/>
@@ -9067,7 +9250,7 @@
     </row>
     <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="4" t="s">
-        <v>310</v>
+        <v>331</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
@@ -9076,22 +9259,22 @@
         <v>0.015</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>268</v>
+        <v>290</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>311</v>
+        <v>332</v>
       </c>
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>
       <c r="L16" s="4" t="s">
-        <v>294</v>
+        <v>316</v>
       </c>
       <c r="M16" s="4"/>
       <c r="N16" s="4"/>
       <c r="O16" s="4"/>
       <c r="P16" s="4"/>
       <c r="R16" s="4" t="s">
-        <v>312</v>
+        <v>333</v>
       </c>
       <c r="S16" s="4"/>
       <c r="T16" s="4"/>
@@ -9105,7 +9288,7 @@
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="11" t="s">
-        <v>313</v>
+        <v>334</v>
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
@@ -9115,7 +9298,7 @@
     </row>
     <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="4" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
@@ -9124,12 +9307,12 @@
         <v>1</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="4" t="s">
-        <v>315</v>
+        <v>336</v>
       </c>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
@@ -9138,12 +9321,12 @@
         <v>14</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="4" t="s">
-        <v>165</v>
+        <v>187</v>
       </c>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
@@ -9152,12 +9335,12 @@
         <v>65</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="4" t="s">
-        <v>316</v>
+        <v>337</v>
       </c>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
@@ -9166,12 +9349,12 @@
         <v>5</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="4" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
@@ -9180,12 +9363,12 @@
         <v>0.3</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="4" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
@@ -9195,12 +9378,12 @@
         <v>0.7</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="4" t="s">
-        <v>320</v>
+        <v>341</v>
       </c>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
@@ -9209,14 +9392,14 @@
         <v>3</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>321</v>
+        <v>342</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="3" t="s">
-        <v>322</v>
+        <v>343</v>
       </c>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
@@ -9258,13 +9441,13 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="17" t="s">
-        <v>323</v>
+        <v>344</v>
       </c>
       <c r="C28" s="17"/>
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
       <c r="F28" s="17" t="s">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="G28" s="17"/>
       <c r="H28" s="17"/>
@@ -9274,42 +9457,42 @@
       <c r="L28" s="17"/>
       <c r="M28" s="17"/>
       <c r="N28" s="17" t="s">
-        <v>276</v>
+        <v>298</v>
       </c>
       <c r="O28" s="17"/>
       <c r="P28" s="17"/>
       <c r="Q28" s="17" t="s">
-        <v>324</v>
+        <v>345</v>
       </c>
       <c r="R28" s="17" t="s">
-        <v>281</v>
+        <v>303</v>
       </c>
       <c r="S28" s="17"/>
       <c r="T28" s="17"/>
       <c r="U28" s="17"/>
       <c r="V28" s="17"/>
       <c r="W28" s="17" t="s">
-        <v>286</v>
+        <v>308</v>
       </c>
       <c r="X28" s="17"/>
       <c r="Y28" s="17"/>
       <c r="Z28" s="17" t="s">
-        <v>325</v>
+        <v>346</v>
       </c>
       <c r="AA28" s="17" t="s">
-        <v>291</v>
+        <v>313</v>
       </c>
       <c r="AB28" s="17" t="s">
-        <v>326</v>
+        <v>347</v>
       </c>
       <c r="AC28" s="17"/>
       <c r="AD28" s="17"/>
       <c r="AE28" s="17"/>
       <c r="AF28" s="17" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="AG28" s="17" t="s">
-        <v>328</v>
+        <v>349</v>
       </c>
       <c r="AH28" s="17"/>
       <c r="AI28" s="17"/>
@@ -9320,118 +9503,118 @@
     </row>
     <row r="29" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="2" t="s">
-        <v>329</v>
+        <v>350</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>330</v>
+        <v>351</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>323</v>
+        <v>344</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>331</v>
+        <v>352</v>
       </c>
       <c r="F29" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="M29" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="N29" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="O29" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="G29" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="L29" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="M29" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="N29" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="O29" s="2" t="s">
-        <v>311</v>
-      </c>
       <c r="P29" s="2" t="s">
-        <v>338</v>
+        <v>359</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>339</v>
+        <v>360</v>
       </c>
       <c r="R29" s="2" t="s">
-        <v>340</v>
+        <v>361</v>
       </c>
       <c r="S29" s="2" t="s">
-        <v>341</v>
+        <v>362</v>
       </c>
       <c r="T29" s="2" t="s">
-        <v>342</v>
+        <v>363</v>
       </c>
       <c r="U29" s="2" t="s">
-        <v>343</v>
+        <v>364</v>
       </c>
       <c r="V29" s="2" t="s">
-        <v>344</v>
+        <v>365</v>
       </c>
       <c r="W29" s="2" t="s">
-        <v>286</v>
+        <v>308</v>
       </c>
       <c r="X29" s="2" t="s">
-        <v>345</v>
+        <v>366</v>
       </c>
       <c r="Y29" s="2" t="s">
-        <v>346</v>
+        <v>367</v>
       </c>
       <c r="Z29" s="2" t="s">
-        <v>347</v>
+        <v>368</v>
       </c>
       <c r="AA29" s="2" t="s">
-        <v>277</v>
+        <v>299</v>
       </c>
       <c r="AB29" s="2" t="s">
-        <v>285</v>
+        <v>307</v>
       </c>
       <c r="AC29" s="2" t="s">
-        <v>290</v>
+        <v>312</v>
       </c>
       <c r="AD29" s="2" t="s">
-        <v>296</v>
+        <v>318</v>
       </c>
       <c r="AE29" s="2" t="s">
-        <v>348</v>
+        <v>369</v>
       </c>
       <c r="AF29" s="2" t="s">
-        <v>282</v>
+        <v>304</v>
       </c>
       <c r="AG29" s="2" t="s">
-        <v>349</v>
+        <v>370</v>
       </c>
       <c r="AH29" s="2" t="s">
-        <v>350</v>
+        <v>371</v>
       </c>
       <c r="AI29" s="2" t="s">
-        <v>291</v>
+        <v>313</v>
       </c>
       <c r="AJ29" s="2" t="s">
         <v>115</v>
       </c>
       <c r="AK29" s="2" t="s">
-        <v>351</v>
+        <v>372</v>
       </c>
       <c r="AL29" s="2" t="s">
-        <v>352</v>
+        <v>373</v>
       </c>
       <c r="AM29" s="2" t="s">
-        <v>353</v>
+        <v>374</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17134,7 +17317,7 @@
     <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="81" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B81" s="18" t="s">
-        <v>354</v>
+        <v>375</v>
       </c>
       <c r="C81" s="18"/>
       <c r="D81" s="18"/>
@@ -17271,12 +17454,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>355</v>
+        <v>376</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="18" t="s">
-        <v>356</v>
+        <v>377</v>
       </c>
       <c r="C2" s="18"/>
       <c r="D2" s="18"/>
@@ -17290,7 +17473,7 @@
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="3" t="s">
-        <v>357</v>
+        <v>378</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -17303,28 +17486,28 @@
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="2" t="s">
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>258</v>
+        <v>280</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>360</v>
+        <v>381</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>361</v>
+        <v>382</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>260</v>
+        <v>282</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>261</v>
+        <v>283</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>92</v>
@@ -17335,13 +17518,13 @@
         <v>1</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>269</v>
+        <v>291</v>
       </c>
       <c r="D6" s="19" t="n">
         <v>2700000</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="F6" s="21" t="n">
         <f aca="false">IF(E6="CRC",Proyección!$F$7,1)</f>
@@ -17358,7 +17541,7 @@
         <v>14</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>362</v>
+        <v>383</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17366,13 +17549,13 @@
         <v>2</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>273</v>
+        <v>295</v>
       </c>
       <c r="D7" s="19" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="F7" s="21" t="n">
         <f aca="false">IF(E7="CRC",Proyección!$F$7,1)</f>
@@ -17389,7 +17572,7 @@
         <v>0</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>363</v>
+        <v>384</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17397,13 +17580,13 @@
         <v>3</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>278</v>
+        <v>300</v>
       </c>
       <c r="D8" s="19" t="n">
         <v>500000</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="F8" s="21" t="n">
         <f aca="false">IF(E8="CRC",Proyección!$F$7,1)</f>
@@ -17423,7 +17606,7 @@
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="15" t="s">
-        <v>364</v>
+        <v>385</v>
       </c>
       <c r="C9" s="15"/>
       <c r="D9" s="15"/>
@@ -17439,7 +17622,7 @@
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="18" t="s">
-        <v>365</v>
+        <v>386</v>
       </c>
       <c r="C10" s="18"/>
       <c r="D10" s="18"/>
@@ -17453,7 +17636,7 @@
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="3" t="s">
-        <v>366</v>
+        <v>387</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
@@ -17466,25 +17649,25 @@
     </row>
     <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="2" t="s">
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>367</v>
+        <v>388</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>368</v>
+        <v>389</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>258</v>
+        <v>280</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>360</v>
+        <v>381</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>361</v>
+        <v>382</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>369</v>
+        <v>390</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2" t="s">
@@ -17496,13 +17679,13 @@
         <v>1</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>370</v>
+        <v>391</v>
       </c>
       <c r="D14" s="19" t="n">
         <v>1100</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="F14" s="21" t="n">
         <f aca="false">IF(E14="CRC",Proyección!$F$7,1)</f>
@@ -17517,7 +17700,7 @@
       </c>
       <c r="I14" s="4"/>
       <c r="J14" s="4" t="s">
-        <v>371</v>
+        <v>392</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17579,7 +17762,7 @@
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="15" t="s">
-        <v>372</v>
+        <v>393</v>
       </c>
       <c r="C18" s="15"/>
       <c r="D18" s="15"/>
@@ -17596,7 +17779,7 @@
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="3" t="s">
-        <v>373</v>
+        <v>394</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
@@ -17609,25 +17792,25 @@
     </row>
     <row r="21" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="2" t="s">
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>258</v>
+        <v>280</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>360</v>
+        <v>381</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>361</v>
+        <v>382</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>329</v>
+        <v>350</v>
       </c>
       <c r="I21" s="2"/>
       <c r="J21" s="2" t="s">
@@ -17639,13 +17822,13 @@
         <v>1</v>
       </c>
       <c r="C22" s="23" t="s">
-        <v>374</v>
+        <v>395</v>
       </c>
       <c r="D22" s="19" t="n">
         <v>40000</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="F22" s="21" t="n">
         <f aca="false">IF(E22="CRC",Proyección!$F$7,1)</f>
@@ -17666,13 +17849,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>375</v>
+        <v>396</v>
       </c>
       <c r="D23" s="19" t="n">
         <v>120000</v>
       </c>
       <c r="E23" s="20" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="F23" s="21" t="n">
         <f aca="false">IF(E23="CRC",Proyección!$F$7,1)</f>
@@ -17747,7 +17930,7 @@
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="15" t="s">
-        <v>376</v>
+        <v>397</v>
       </c>
       <c r="C27" s="15"/>
       <c r="D27" s="15"/>
@@ -17763,7 +17946,7 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="18" t="s">
-        <v>377</v>
+        <v>398</v>
       </c>
       <c r="C28" s="18"/>
       <c r="D28" s="18"/>
@@ -17777,7 +17960,7 @@
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="3" t="s">
-        <v>378</v>
+        <v>399</v>
       </c>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
@@ -17790,7 +17973,7 @@
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="4" t="s">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
@@ -17803,7 +17986,7 @@
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="4" t="s">
-        <v>276</v>
+        <v>298</v>
       </c>
       <c r="C32" s="4"/>
       <c r="D32" s="4"/>
@@ -17816,7 +17999,7 @@
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="15" t="s">
-        <v>379</v>
+        <v>400</v>
       </c>
       <c r="C33" s="15"/>
       <c r="D33" s="15"/>
@@ -17876,12 +18059,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>380</v>
+        <v>401</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="18" t="s">
-        <v>381</v>
+        <v>402</v>
       </c>
       <c r="C2" s="18"/>
       <c r="D2" s="18"/>
@@ -17897,7 +18080,7 @@
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="3" t="s">
-        <v>382</v>
+        <v>403</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -17912,28 +18095,28 @@
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="2" t="s">
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>258</v>
+        <v>280</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>360</v>
+        <v>381</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>361</v>
+        <v>382</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>383</v>
+        <v>404</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>261</v>
+        <v>283</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>92</v>
@@ -17946,13 +18129,13 @@
         <v>1</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="D6" s="19" t="n">
         <v>5500</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="F6" s="21" t="n">
         <f aca="false">IF(E6="CRC",Proyección!$F$7,1)</f>
@@ -17963,11 +18146,11 @@
         <v>5500</v>
       </c>
       <c r="H6" s="13" t="s">
-        <v>384</v>
+        <v>405</v>
       </c>
       <c r="I6" s="4"/>
       <c r="J6" s="4" t="s">
-        <v>385</v>
+        <v>406</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -17977,13 +18160,13 @@
         <v>2</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>284</v>
+        <v>306</v>
       </c>
       <c r="D7" s="19" t="n">
         <v>3000</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="F7" s="21" t="n">
         <f aca="false">IF(E7="CRC",Proyección!$F$7,1)</f>
@@ -17994,7 +18177,7 @@
         <v>3000</v>
       </c>
       <c r="H7" s="13" t="s">
-        <v>386</v>
+        <v>407</v>
       </c>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
@@ -18006,13 +18189,13 @@
         <v>3</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>204</v>
+        <v>226</v>
       </c>
       <c r="D8" s="19" t="n">
         <v>1200</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="F8" s="21" t="n">
         <f aca="false">IF(E8="CRC",Proyección!$F$7,1)</f>
@@ -18023,20 +18206,20 @@
         <v>1200</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>384</v>
+        <v>405</v>
       </c>
       <c r="I8" s="22" t="n">
         <v>15</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>387</v>
+        <v>408</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="15" t="s">
-        <v>388</v>
+        <v>409</v>
       </c>
       <c r="C9" s="15"/>
       <c r="D9" s="15"/>
@@ -18054,7 +18237,7 @@
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="15" t="s">
-        <v>389</v>
+        <v>410</v>
       </c>
       <c r="C10" s="15"/>
       <c r="D10" s="15"/>
@@ -18073,7 +18256,7 @@
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="3" t="s">
-        <v>390</v>
+        <v>411</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
@@ -18088,28 +18271,28 @@
     </row>
     <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="2" t="s">
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>391</v>
+        <v>412</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>392</v>
+        <v>413</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>258</v>
+        <v>280</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>360</v>
+        <v>381</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>361</v>
+        <v>382</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>232</v>
+        <v>254</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>393</v>
+        <v>414</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>92</v>
@@ -18122,13 +18305,13 @@
         <v>1</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>394</v>
+        <v>415</v>
       </c>
       <c r="D14" s="19" t="n">
         <v>12000</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="F14" s="21" t="n">
         <f aca="false">IF(E14="CRC",Proyección!$F$7,1)</f>
@@ -18213,7 +18396,7 @@
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="15" t="s">
-        <v>395</v>
+        <v>416</v>
       </c>
       <c r="C18" s="15"/>
       <c r="D18" s="15"/>
@@ -18232,7 +18415,7 @@
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="3" t="s">
-        <v>396</v>
+        <v>417</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
@@ -18247,37 +18430,37 @@
     </row>
     <row r="21" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="2" t="s">
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>397</v>
+        <v>418</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>398</v>
+        <v>419</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>258</v>
+        <v>280</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>360</v>
+        <v>381</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>361</v>
+        <v>382</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>399</v>
+        <v>420</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>400</v>
+        <v>421</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>401</v>
+        <v>422</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>402</v>
+        <v>423</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>403</v>
+        <v>424</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18285,13 +18468,13 @@
         <v>1</v>
       </c>
       <c r="C22" s="23" t="s">
-        <v>404</v>
+        <v>425</v>
       </c>
       <c r="D22" s="19" t="n">
         <v>157500</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="F22" s="21" t="n">
         <f aca="false">IF(E22="CRC",Proyección!$F$7,1)</f>
@@ -18308,7 +18491,7 @@
         <v>5400000</v>
       </c>
       <c r="J22" s="20" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="K22" s="8" t="n">
         <f aca="false">IF(J22="CRC",I22/Proyección!$F$7,N(I22))</f>
@@ -18323,13 +18506,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>405</v>
+        <v>426</v>
       </c>
       <c r="D23" s="19" t="n">
         <v>150</v>
       </c>
       <c r="E23" s="20" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="F23" s="21" t="n">
         <f aca="false">IF(E23="CRC",Proyección!$F$7,1)</f>
@@ -18346,7 +18529,7 @@
         <v>3000</v>
       </c>
       <c r="J23" s="20" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="K23" s="8" t="n">
         <f aca="false">IF(J23="CRC",I23/Proyección!$F$7,N(I23))</f>
@@ -18430,7 +18613,7 @@
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="15" t="s">
-        <v>406</v>
+        <v>427</v>
       </c>
       <c r="C27" s="15"/>
       <c r="D27" s="15"/>
@@ -18451,14 +18634,14 @@
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="4" t="s">
-        <v>407</v>
+        <v>428</v>
       </c>
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
       <c r="G28" s="20" t="s">
-        <v>408</v>
+        <v>429</v>
       </c>
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
@@ -18468,7 +18651,7 @@
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="18" t="s">
-        <v>409</v>
+        <v>430</v>
       </c>
       <c r="C29" s="18"/>
       <c r="D29" s="18"/>
@@ -18484,7 +18667,7 @@
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="3" t="s">
-        <v>410</v>
+        <v>431</v>
       </c>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
@@ -18499,28 +18682,28 @@
     </row>
     <row r="32" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="2" t="s">
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>411</v>
+        <v>432</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>258</v>
+        <v>280</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>360</v>
+        <v>381</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>361</v>
+        <v>382</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>329</v>
+        <v>350</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>412</v>
+        <v>433</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>92</v>
@@ -18533,13 +18716,13 @@
         <v>1</v>
       </c>
       <c r="C33" s="23" t="s">
-        <v>413</v>
+        <v>434</v>
       </c>
       <c r="D33" s="19" t="n">
         <v>6000</v>
       </c>
       <c r="E33" s="20" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="F33" s="21" t="n">
         <f aca="false">IF(E33="CRC",Proyección!$F$7,1)</f>
@@ -18556,7 +18739,7 @@
         <v>2</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>414</v>
+        <v>435</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -18566,13 +18749,13 @@
         <v>2</v>
       </c>
       <c r="C34" s="23" t="s">
-        <v>415</v>
+        <v>436</v>
       </c>
       <c r="D34" s="19" t="n">
         <v>15750000</v>
       </c>
       <c r="E34" s="20" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="F34" s="21" t="n">
         <f aca="false">IF(E34="CRC",Proyección!$F$7,1)</f>
@@ -18589,7 +18772,7 @@
         <v>1</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>416</v>
+        <v>437</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -18659,7 +18842,7 @@
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="15" t="s">
-        <v>417</v>
+        <v>438</v>
       </c>
       <c r="C38" s="15"/>
       <c r="D38" s="15"/>
@@ -18677,7 +18860,7 @@
     </row>
     <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="18" t="s">
-        <v>418</v>
+        <v>439</v>
       </c>
       <c r="C39" s="18"/>
       <c r="D39" s="18"/>
@@ -18693,7 +18876,7 @@
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="41" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="3" t="s">
-        <v>419</v>
+        <v>440</v>
       </c>
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
@@ -18708,34 +18891,34 @@
     </row>
     <row r="42" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="2" t="s">
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>420</v>
+        <v>441</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>258</v>
+        <v>280</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>360</v>
+        <v>381</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>361</v>
+        <v>382</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>421</v>
+        <v>442</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>422</v>
+        <v>443</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>423</v>
+        <v>444</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>424</v>
+        <v>445</v>
       </c>
       <c r="L42" s="2"/>
     </row>
@@ -18813,7 +18996,7 @@
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="15" t="s">
-        <v>425</v>
+        <v>446</v>
       </c>
       <c r="C46" s="15"/>
       <c r="D46" s="15"/>
@@ -18831,7 +19014,7 @@
     </row>
     <row r="47" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="18" t="s">
-        <v>426</v>
+        <v>447</v>
       </c>
       <c r="C47" s="18"/>
       <c r="D47" s="18"/>
@@ -18847,7 +19030,7 @@
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="49" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B49" s="3" t="s">
-        <v>378</v>
+        <v>399</v>
       </c>
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
@@ -18862,7 +19045,7 @@
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="4" t="s">
-        <v>281</v>
+        <v>303</v>
       </c>
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
@@ -18875,7 +19058,7 @@
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="4" t="s">
-        <v>286</v>
+        <v>308</v>
       </c>
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
@@ -18888,7 +19071,7 @@
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="15" t="s">
-        <v>427</v>
+        <v>448</v>
       </c>
       <c r="C52" s="15"/>
       <c r="D52" s="15"/>
@@ -18954,12 +19137,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>428</v>
+        <v>449</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="18" t="s">
-        <v>429</v>
+        <v>450</v>
       </c>
       <c r="C2" s="18"/>
       <c r="D2" s="18"/>
@@ -18973,7 +19156,7 @@
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="3" t="s">
-        <v>430</v>
+        <v>451</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -18986,22 +19169,22 @@
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="2" t="s">
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>258</v>
+        <v>280</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>360</v>
+        <v>381</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>361</v>
+        <v>382</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>92</v>
@@ -19014,13 +19197,13 @@
         <v>1</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>270</v>
+        <v>292</v>
       </c>
       <c r="D6" s="19" t="n">
         <v>250000</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="F6" s="21" t="n">
         <f aca="false">IF(E6="CRC",Proyección!$F$7,1)</f>
@@ -19031,14 +19214,14 @@
         <v>250000</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>431</v>
+        <v>452</v>
       </c>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="4" t="s">
-        <v>299</v>
+        <v>321</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
@@ -19049,7 +19232,7 @@
         <v>0.0585725</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>432</v>
+        <v>453</v>
       </c>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
@@ -19057,7 +19240,7 @@
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="3" t="s">
-        <v>378</v>
+        <v>399</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
@@ -19070,7 +19253,7 @@
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="4" t="s">
-        <v>272</v>
+        <v>294</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -19083,7 +19266,7 @@
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="4" t="s">
-        <v>287</v>
+        <v>309</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
@@ -19097,7 +19280,7 @@
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="3" t="s">
-        <v>433</v>
+        <v>454</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
@@ -19110,28 +19293,28 @@
     </row>
     <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="2" t="s">
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>434</v>
+        <v>455</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>257</v>
+        <v>279</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>258</v>
+        <v>280</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>360</v>
+        <v>381</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>361</v>
+        <v>382</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>435</v>
+        <v>456</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>436</v>
+        <v>457</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>92</v>
@@ -19142,13 +19325,13 @@
         <v>1</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>437</v>
+        <v>458</v>
       </c>
       <c r="D15" s="19" t="n">
         <v>180000</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="F15" s="21" t="n">
         <f aca="false">IF(E15="CRC",Proyección!$F$7,1)</f>
@@ -19170,13 +19353,13 @@
         <v>2</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>438</v>
+        <v>459</v>
       </c>
       <c r="D16" s="19" t="n">
         <v>900000</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="F16" s="21" t="n">
         <f aca="false">IF(E16="CRC",Proyección!$F$7,1)</f>
@@ -19200,13 +19383,13 @@
         <v>3</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>439</v>
+        <v>460</v>
       </c>
       <c r="D17" s="19" t="n">
         <v>800000</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="F17" s="21" t="n">
         <f aca="false">IF(E17="CRC",Proyección!$F$7,1)</f>
@@ -19228,13 +19411,13 @@
         <v>4</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>440</v>
+        <v>461</v>
       </c>
       <c r="D18" s="19" t="n">
         <v>12000000</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="F18" s="21" t="n">
         <f aca="false">IF(E18="CRC",Proyección!$F$7,1)</f>
@@ -19250,7 +19433,7 @@
         <v>26666.6666666667</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>441</v>
+        <v>462</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19258,13 +19441,13 @@
         <v>5</v>
       </c>
       <c r="C19" s="23" t="s">
-        <v>442</v>
+        <v>463</v>
       </c>
       <c r="D19" s="19" t="n">
         <v>12000000</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="F19" s="21" t="n">
         <f aca="false">IF(E19="CRC",Proyección!$F$7,1)</f>
@@ -19280,7 +19463,7 @@
         <v>26666.6666666667</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>441</v>
+        <v>462</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19288,13 +19471,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>443</v>
+        <v>464</v>
       </c>
       <c r="D20" s="19" t="n">
         <v>12000000</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="F20" s="21" t="n">
         <f aca="false">IF(E20="CRC",Proyección!$F$7,1)</f>
@@ -19310,7 +19493,7 @@
         <v>26666.6666666667</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>441</v>
+        <v>462</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19381,7 +19564,7 @@
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="15" t="s">
-        <v>444</v>
+        <v>465</v>
       </c>
       <c r="C24" s="15"/>
       <c r="D24" s="15"/>
@@ -19441,12 +19624,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>445</v>
+        <v>466</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="18" t="s">
-        <v>446</v>
+        <v>467</v>
       </c>
       <c r="C2" s="18"/>
       <c r="D2" s="18"/>
@@ -19462,7 +19645,7 @@
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="3" t="s">
-        <v>447</v>
+        <v>468</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -19477,28 +19660,28 @@
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="2" t="s">
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>448</v>
+        <v>469</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>449</v>
+        <v>470</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>258</v>
+        <v>280</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>360</v>
+        <v>381</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>361</v>
+        <v>382</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>450</v>
+        <v>471</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>451</v>
+        <v>472</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>92</v>
@@ -19511,13 +19694,13 @@
         <v>1</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>452</v>
+        <v>473</v>
       </c>
       <c r="D6" s="19" t="n">
         <v>180000</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="F6" s="21" t="n">
         <f aca="false">IF(E6="CRC",Proyección!$F$7,1)</f>
@@ -19542,13 +19725,13 @@
         <v>2</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>453</v>
+        <v>474</v>
       </c>
       <c r="D7" s="19" t="n">
         <v>150000</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="F7" s="21" t="n">
         <f aca="false">IF(E7="CRC",Proyección!$F$7,1)</f>
@@ -19633,7 +19816,7 @@
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="4" t="s">
-        <v>454</v>
+        <v>475</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
@@ -19651,7 +19834,7 @@
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="4" t="s">
-        <v>455</v>
+        <v>476</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
@@ -19669,7 +19852,7 @@
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="4" t="s">
-        <v>456</v>
+        <v>477</v>
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
@@ -19687,7 +19870,7 @@
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="15" t="s">
-        <v>457</v>
+        <v>478</v>
       </c>
       <c r="C14" s="15"/>
       <c r="D14" s="15"/>
@@ -19706,7 +19889,7 @@
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="3" t="s">
-        <v>378</v>
+        <v>399</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -19721,7 +19904,7 @@
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="4" t="s">
-        <v>282</v>
+        <v>304</v>
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
@@ -19774,12 +19957,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>458</v>
+        <v>479</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="18" t="s">
-        <v>459</v>
+        <v>480</v>
       </c>
       <c r="C2" s="18"/>
       <c r="D2" s="18"/>
@@ -19793,7 +19976,7 @@
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="3" t="s">
-        <v>460</v>
+        <v>481</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -19806,29 +19989,29 @@
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="2" t="s">
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>420</v>
+        <v>441</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>258</v>
+        <v>280</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>360</v>
+        <v>381</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>361</v>
+        <v>382</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>329</v>
+        <v>350</v>
       </c>
       <c r="I5" s="2"/>
       <c r="J5" s="2" t="s">
-        <v>461</v>
+        <v>482</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19836,13 +20019,13 @@
         <v>1</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>462</v>
+        <v>483</v>
       </c>
       <c r="D6" s="19" t="n">
         <v>40000</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="F6" s="21" t="n">
         <f aca="false">IF(E6="CRC",Proyección!$F$7,1)</f>
@@ -19857,7 +20040,7 @@
       </c>
       <c r="I6" s="4"/>
       <c r="J6" s="4" t="s">
-        <v>463</v>
+        <v>484</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19919,7 +20102,7 @@
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="15" t="s">
-        <v>464</v>
+        <v>485</v>
       </c>
       <c r="C10" s="15"/>
       <c r="D10" s="15"/>
@@ -19935,7 +20118,7 @@
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="18" t="s">
-        <v>465</v>
+        <v>486</v>
       </c>
       <c r="C11" s="18"/>
       <c r="D11" s="18"/>
@@ -19949,7 +20132,7 @@
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="3" t="s">
-        <v>466</v>
+        <v>487</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
@@ -19962,25 +20145,25 @@
     </row>
     <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="2" t="s">
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>467</v>
+        <v>488</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>258</v>
+        <v>280</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>360</v>
+        <v>381</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>361</v>
+        <v>382</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>329</v>
+        <v>350</v>
       </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2" t="s">
@@ -19992,13 +20175,13 @@
         <v>1</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>468</v>
+        <v>489</v>
       </c>
       <c r="D15" s="19" t="n">
         <v>50000</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="F15" s="21" t="n">
         <f aca="false">IF(E15="CRC",Proyección!$F$7,1)</f>
@@ -20013,7 +20196,7 @@
       </c>
       <c r="I15" s="4"/>
       <c r="J15" s="4" t="s">
-        <v>469</v>
+        <v>490</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20075,7 +20258,7 @@
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="15" t="s">
-        <v>470</v>
+        <v>491</v>
       </c>
       <c r="C19" s="15"/>
       <c r="D19" s="15"/>
@@ -20092,7 +20275,7 @@
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="3" t="s">
-        <v>378</v>
+        <v>399</v>
       </c>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
@@ -20105,7 +20288,7 @@
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="4" t="s">
-        <v>471</v>
+        <v>492</v>
       </c>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
@@ -20118,7 +20301,7 @@
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="4" t="s">
-        <v>472</v>
+        <v>493</v>
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
@@ -20130,7 +20313,7 @@
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="15" t="s">
-        <v>473</v>
+        <v>494</v>
       </c>
       <c r="C24" s="15"/>
       <c r="D24" s="15"/>
@@ -20187,12 +20370,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>474</v>
+        <v>495</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="18" t="s">
-        <v>475</v>
+        <v>496</v>
       </c>
       <c r="C2" s="18"/>
       <c r="D2" s="18"/>
@@ -20209,13 +20392,13 @@
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="3" t="s">
-        <v>250</v>
+        <v>272</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="G4" s="3" t="s">
-        <v>476</v>
+        <v>497</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
@@ -20226,7 +20409,7 @@
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
-        <v>477</v>
+        <v>498</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
@@ -20238,19 +20421,19 @@
         <v>1</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>478</v>
+        <v>499</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>258</v>
+        <v>280</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>360</v>
+        <v>381</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>361</v>
+        <v>382</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>260</v>
+        <v>282</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>92</v>
@@ -20258,7 +20441,7 @@
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="4" t="s">
-        <v>479</v>
+        <v>500</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -20267,13 +20450,13 @@
         <v>0.039</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>283</v>
+        <v>305</v>
       </c>
       <c r="H6" s="19" t="n">
         <v>800000</v>
       </c>
       <c r="I6" s="20" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="J6" s="21" t="n">
         <f aca="false">IF(I6="CRC",Proyección!$F$7,1)</f>
@@ -20294,7 +20477,7 @@
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="4" t="s">
-        <v>480</v>
+        <v>501</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
@@ -20303,7 +20486,7 @@
         <v>14</v>
       </c>
       <c r="G7" s="18" t="s">
-        <v>481</v>
+        <v>502</v>
       </c>
       <c r="H7" s="18"/>
       <c r="I7" s="18"/>
@@ -20314,7 +20497,7 @@
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="4" t="s">
-        <v>482</v>
+        <v>503</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
@@ -20332,7 +20515,7 @@
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="4" t="s">
-        <v>483</v>
+        <v>504</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
@@ -20343,7 +20526,7 @@
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="4" t="s">
-        <v>484</v>
+        <v>505</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -20354,57 +20537,57 @@
     </row>
     <row r="11" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="2" t="s">
-        <v>485</v>
+        <v>506</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>486</v>
+        <v>507</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>487</v>
+        <v>508</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>488</v>
+        <v>509</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>489</v>
+        <v>510</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>329</v>
+        <v>350</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>490</v>
+        <v>511</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>491</v>
+        <v>512</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>492</v>
+        <v>513</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>493</v>
+        <v>514</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>494</v>
+        <v>515</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>495</v>
+        <v>516</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>400</v>
+        <v>421</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>401</v>
+        <v>422</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>496</v>
+        <v>517</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>497</v>
+        <v>518</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="4" t="s">
-        <v>498</v>
+        <v>519</v>
       </c>
       <c r="C12" s="8" t="n">
         <f aca="false">IF(O12="CRC",N12/Proyección!$F$7,N12)</f>
@@ -20415,7 +20598,7 @@
         <v>255</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>499</v>
+        <v>520</v>
       </c>
       <c r="F12" s="13" t="n">
         <f aca="false">MAX(1,N(Proyección!$F$20)-$E$9+1)</f>
@@ -20426,7 +20609,7 @@
         <v>2045</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>500</v>
+        <v>521</v>
       </c>
       <c r="I12" s="16" t="n">
         <v>100</v>
@@ -20450,14 +20633,14 @@
         <v>12000000</v>
       </c>
       <c r="O12" s="23" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="4" t="s">
-        <v>501</v>
+        <v>522</v>
       </c>
       <c r="C13" s="8" t="n">
         <f aca="false">IF(O13="CRC",N13/Proyección!$F$7,N13)</f>
@@ -20468,7 +20651,7 @@
         <v>90</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>502</v>
+        <v>523</v>
       </c>
       <c r="F13" s="13" t="n">
         <f aca="false">$E$8</f>
@@ -20479,7 +20662,7 @@
         <v>2040</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>503</v>
+        <v>524</v>
       </c>
       <c r="J13" s="8" t="n">
         <f aca="false">SUM(J19:J68)</f>
@@ -20500,14 +20683,14 @@
         <v>12000000</v>
       </c>
       <c r="O13" s="23" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="P13" s="4"/>
       <c r="Q13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="4" t="s">
-        <v>300</v>
+        <v>322</v>
       </c>
       <c r="C14" s="8" t="n">
         <f aca="false">IF(O14="CRC",N14/Proyección!$F$7,N14)</f>
@@ -20518,7 +20701,7 @@
         <v>333.333333333333</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>504</v>
+        <v>525</v>
       </c>
       <c r="F14" s="13" t="n">
         <f aca="false">MAX(1,N(Proyección!$F$20)-$E$9+1)</f>
@@ -20529,7 +20712,7 @@
         <v>2045</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>505</v>
+        <v>526</v>
       </c>
       <c r="I14" s="16" t="n">
         <v>100</v>
@@ -20553,109 +20736,109 @@
         <v>12000000</v>
       </c>
       <c r="O14" s="23" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="P14" s="19" t="n">
         <v>150000</v>
       </c>
       <c r="Q14" s="23" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="17" t="s">
-        <v>506</v>
+        <v>527</v>
       </c>
       <c r="C17" s="17"/>
       <c r="D17" s="17" t="s">
-        <v>498</v>
+        <v>519</v>
       </c>
       <c r="E17" s="17"/>
       <c r="F17" s="17"/>
       <c r="G17" s="17"/>
       <c r="H17" s="17"/>
       <c r="I17" s="17" t="s">
-        <v>501</v>
+        <v>522</v>
       </c>
       <c r="J17" s="17"/>
       <c r="K17" s="17"/>
       <c r="L17" s="17"/>
       <c r="M17" s="17"/>
       <c r="N17" s="17" t="s">
-        <v>300</v>
+        <v>322</v>
       </c>
       <c r="O17" s="17"/>
       <c r="P17" s="17"/>
       <c r="Q17" s="17"/>
       <c r="R17" s="17"/>
       <c r="S17" s="17" t="s">
-        <v>507</v>
+        <v>528</v>
       </c>
       <c r="T17" s="17"/>
       <c r="U17" s="17"/>
     </row>
     <row r="18" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="2" t="s">
-        <v>323</v>
+        <v>344</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>329</v>
+        <v>350</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>508</v>
+        <v>529</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>509</v>
+        <v>530</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>350</v>
+        <v>371</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>495</v>
+        <v>516</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>510</v>
+        <v>531</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>508</v>
+        <v>529</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>509</v>
+        <v>530</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>350</v>
+        <v>371</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>511</v>
+        <v>532</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>510</v>
+        <v>531</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>508</v>
+        <v>529</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>509</v>
+        <v>530</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>350</v>
+        <v>371</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>495</v>
+        <v>516</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>510</v>
+        <v>531</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>512</v>
+        <v>533</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>293</v>
+        <v>315</v>
       </c>
       <c r="U18" s="2" t="s">
-        <v>300</v>
+        <v>322</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24746,7 +24929,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>513</v>
+        <v>534</v>
       </c>
       <c r="B1" s="0" t="s">
         <v>79</v>
@@ -24755,40 +24938,40 @@
         <v>80</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>514</v>
+        <v>535</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>350</v>
+        <v>371</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>515</v>
+        <v>536</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>514</v>
+        <v>535</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>350</v>
+        <v>371</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>516</v>
+        <v>537</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>517</v>
+        <v>538</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>518</v>
+        <v>539</v>
       </c>
       <c r="R1" s="0" t="s">
-        <v>519</v>
+        <v>540</v>
       </c>
       <c r="U1" s="0" t="s">
-        <v>520</v>
+        <v>541</v>
       </c>
       <c r="V1" s="0" t="s">
-        <v>521</v>
+        <v>542</v>
       </c>
       <c r="W1" s="0" t="s">
-        <v>522</v>
+        <v>543</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24808,7 +24991,7 @@
         <v>0.05001</v>
       </c>
       <c r="H2" s="25" t="s">
-        <v>523</v>
+        <v>544</v>
       </c>
       <c r="I2" s="24" t="n">
         <v>0.05824</v>
@@ -24841,7 +25024,7 @@
         <v>6.25</v>
       </c>
       <c r="U2" s="25" t="s">
-        <v>524</v>
+        <v>545</v>
       </c>
       <c r="V2" s="26" t="n">
         <v>3.9</v>
@@ -24900,7 +25083,7 @@
         <v>10</v>
       </c>
       <c r="U3" s="25" t="s">
-        <v>525</v>
+        <v>546</v>
       </c>
       <c r="V3" s="26" t="n">
         <v>5</v>
@@ -24926,7 +25109,7 @@
         <v>0.050438</v>
       </c>
       <c r="H4" s="25" t="s">
-        <v>526</v>
+        <v>547</v>
       </c>
       <c r="I4" s="24" t="n">
         <v>0.104067</v>
@@ -24935,7 +25118,7 @@
         <v>0.067135</v>
       </c>
       <c r="U4" s="25" t="s">
-        <v>527</v>
+        <v>548</v>
       </c>
       <c r="V4" s="26" t="n">
         <v>3.3</v>
@@ -24952,7 +25135,7 @@
         <v>0.050652</v>
       </c>
       <c r="H5" s="25" t="s">
-        <v>528</v>
+        <v>549</v>
       </c>
       <c r="I5" s="24" t="n">
         <v>0.137651</v>
@@ -24961,7 +25144,7 @@
         <v>0.072835</v>
       </c>
       <c r="U5" s="25" t="s">
-        <v>529</v>
+        <v>550</v>
       </c>
       <c r="V5" s="26" t="n">
         <v>6.7</v>
@@ -24975,10 +25158,10 @@
         <v>39</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>530</v>
+        <v>551</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>531</v>
+        <v>552</v>
       </c>
       <c r="E6" s="24" t="n">
         <v>0.059984</v>
@@ -24987,7 +25170,7 @@
         <v>0.050866</v>
       </c>
       <c r="H6" s="25" t="s">
-        <v>532</v>
+        <v>553</v>
       </c>
       <c r="I6" s="24" t="n">
         <v>0.174735</v>
@@ -24996,7 +25179,7 @@
         <v>0.078535</v>
       </c>
       <c r="U6" s="25" t="s">
-        <v>533</v>
+        <v>554</v>
       </c>
       <c r="V6" s="26" t="n">
         <v>6.7</v>
@@ -25007,7 +25190,7 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>534</v>
+        <v>555</v>
       </c>
       <c r="B7" s="26" t="n">
         <v>3.09</v>
@@ -25031,7 +25214,7 @@
         <v>0.0585725</v>
       </c>
       <c r="U7" s="25" t="s">
-        <v>535</v>
+        <v>556</v>
       </c>
       <c r="V7" s="26" t="n">
         <v>0</v>
@@ -25048,7 +25231,7 @@
         <v>0.051294</v>
       </c>
       <c r="H8" s="25" t="s">
-        <v>536</v>
+        <v>557</v>
       </c>
       <c r="I8" s="24" t="n">
         <v>0.174735</v>
@@ -25057,7 +25240,7 @@
         <v>0.078535</v>
       </c>
       <c r="U8" s="25" t="s">
-        <v>537</v>
+        <v>558</v>
       </c>
       <c r="V8" s="26" t="n">
         <v>0</v>
@@ -25068,7 +25251,7 @@
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>523</v>
+        <v>544</v>
       </c>
       <c r="B9" s="0" t="n">
         <v>1</v>
@@ -25083,7 +25266,7 @@
         <v>0.051508</v>
       </c>
       <c r="H9" s="25" t="s">
-        <v>538</v>
+        <v>559</v>
       </c>
       <c r="I9" s="24" t="n">
         <v>0</v>
@@ -25117,7 +25300,7 @@
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>526</v>
+        <v>547</v>
       </c>
       <c r="B11" s="0" t="n">
         <v>5</v>
@@ -25134,7 +25317,7 @@
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>528</v>
+        <v>549</v>
       </c>
       <c r="B12" s="0" t="n">
         <v>7</v>
@@ -25151,7 +25334,7 @@
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>532</v>
+        <v>553</v>
       </c>
       <c r="B13" s="0" t="n">
         <v>9</v>

--- a/Ejemplo - proyeccion por flujo de caja.xlsx
+++ b/Ejemplo - proyeccion por flujo de caja.xlsx
@@ -540,7 +540,7 @@
     <t xml:space="preserve">Metodología de cálculo · Método</t>
   </si>
   <si>
-    <t xml:space="preserve">Se mueve una sola variable, con todo lo demás igual, hasta el punto en que el plan deja de alcanzar el objetivo: ningún año con gasto sin cubrir y saldo final real igual o mayor que la herencia.</t>
+    <t xml:space="preserve">Búsqueda por bisección, 40 pruebas por variable: en cada prueba se recalcula la proyección y se verifica el objetivo (ningún año sin cubrir y saldo final real igual o mayor que la herencia).</t>
   </si>
   <si>
     <t xml:space="preserve">Metodología de cálculo · Herencia</t>
@@ -4019,11 +4019,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="72667620"/>
-        <c:axId val="81828653"/>
+        <c:axId val="57063219"/>
+        <c:axId val="5136977"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="72667620"/>
+        <c:axId val="57063219"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="0.2"/>
@@ -4091,13 +4091,13 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="81828653"/>
+        <c:crossAx val="5136977"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="0.05"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="81828653"/>
+        <c:axId val="5136977"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -4174,7 +4174,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="72667620"/>
+        <c:crossAx val="57063219"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -5124,11 +5124,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="84236114"/>
-        <c:axId val="71457598"/>
+        <c:axId val="7921438"/>
+        <c:axId val="17914260"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="84236114"/>
+        <c:axId val="7921438"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="10"/>
@@ -5206,13 +5206,13 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="71457598"/>
+        <c:crossAx val="17914260"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="5"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="71457598"/>
+        <c:axId val="17914260"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="10"/>
@@ -5290,7 +5290,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="84236114"/>
+        <c:crossAx val="7921438"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="5"/>
@@ -6115,11 +6115,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="43701061"/>
-        <c:axId val="21361559"/>
+        <c:axId val="81611511"/>
+        <c:axId val="47921810"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="43701061"/>
+        <c:axId val="81611511"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6185,7 +6185,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="21361559"/>
+        <c:crossAx val="47921810"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6193,7 +6193,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="21361559"/>
+        <c:axId val="47921810"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6269,7 +6269,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="43701061"/>
+        <c:crossAx val="81611511"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>

--- a/Ejemplo - proyeccion por flujo de caja.xlsx
+++ b/Ejemplo - proyeccion por flujo de caja.xlsx
@@ -4019,11 +4019,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="57063219"/>
-        <c:axId val="5136977"/>
+        <c:axId val="2104817"/>
+        <c:axId val="75553874"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="57063219"/>
+        <c:axId val="2104817"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="0.2"/>
@@ -4091,13 +4091,13 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="5136977"/>
+        <c:crossAx val="75553874"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="0.05"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="5136977"/>
+        <c:axId val="75553874"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -4174,7 +4174,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="57063219"/>
+        <c:crossAx val="2104817"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -5124,11 +5124,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="7921438"/>
-        <c:axId val="17914260"/>
+        <c:axId val="12329141"/>
+        <c:axId val="24285885"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="7921438"/>
+        <c:axId val="12329141"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="10"/>
@@ -5206,13 +5206,13 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="17914260"/>
+        <c:crossAx val="24285885"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="5"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="17914260"/>
+        <c:axId val="24285885"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="10"/>
@@ -5290,7 +5290,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="7921438"/>
+        <c:crossAx val="12329141"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="5"/>
@@ -6115,11 +6115,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="81611511"/>
-        <c:axId val="47921810"/>
+        <c:axId val="88766834"/>
+        <c:axId val="6384378"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="81611511"/>
+        <c:axId val="88766834"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6185,7 +6185,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="47921810"/>
+        <c:crossAx val="6384378"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6193,7 +6193,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="47921810"/>
+        <c:axId val="6384378"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6269,7 +6269,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="81611511"/>
+        <c:crossAx val="88766834"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>

--- a/Ejemplo - proyeccion por flujo de caja.xlsx
+++ b/Ejemplo - proyeccion por flujo de caja.xlsx
@@ -4019,11 +4019,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="2104817"/>
-        <c:axId val="75553874"/>
+        <c:axId val="95373475"/>
+        <c:axId val="18650145"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="2104817"/>
+        <c:axId val="95373475"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="0.2"/>
@@ -4091,13 +4091,13 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="75553874"/>
+        <c:crossAx val="18650145"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="0.05"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="75553874"/>
+        <c:axId val="18650145"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -4174,7 +4174,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2104817"/>
+        <c:crossAx val="95373475"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -5124,11 +5124,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="12329141"/>
-        <c:axId val="24285885"/>
+        <c:axId val="42676023"/>
+        <c:axId val="31339256"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="12329141"/>
+        <c:axId val="42676023"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="10"/>
@@ -5206,13 +5206,13 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="24285885"/>
+        <c:crossAx val="31339256"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="5"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="24285885"/>
+        <c:axId val="31339256"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="10"/>
@@ -5290,7 +5290,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="12329141"/>
+        <c:crossAx val="42676023"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="5"/>
@@ -6115,11 +6115,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="88766834"/>
-        <c:axId val="6384378"/>
+        <c:axId val="48782353"/>
+        <c:axId val="60407578"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="88766834"/>
+        <c:axId val="48782353"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6185,7 +6185,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="6384378"/>
+        <c:crossAx val="60407578"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6193,7 +6193,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="6384378"/>
+        <c:axId val="60407578"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6269,7 +6269,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="88766834"/>
+        <c:crossAx val="48782353"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
